--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE219"/>
+  <dimension ref="A1:AE218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 8924-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45159</v>
+        <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,14 +958,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>21.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -974,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -983,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -995,164 +1000,159 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 8924-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44614</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 16710-2025</t>
+          <t>A 33243-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45754</v>
+        <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1181,14 +1181,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>12.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1212,470 +1217,472 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Silversmygare
+Kopparödla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 16710-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45754</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gul dropplav
 Gulpudrad spiklav</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 16710-2025 artfynd.xlsx", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 16710-2025 karta.png", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 16710-2025 georefererad karta.tif", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 16710-2025 FSC-klagomål.docx", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 16710-2025 FSC-klagomål mail.docx", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 16710-2025 tillsynsbegäran.docx", "A 16710-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 16710-2025 tillsynsbegäran mail.docx", "A 16710-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 488-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45664</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Brun nållav
 Gulpudrad spiklav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 488-2025 artfynd.xlsx", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 488-2025 karta.png", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 488-2025 georefererad karta.tif", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 488-2025 FSC-klagomål.docx", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 488-2025 FSC-klagomål mail.docx", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 488-2025 tillsynsbegäran.docx", "A 488-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 488-2025 tillsynsbegäran mail.docx", "A 488-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 2569-2022</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>44579</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Stor vårtrattskivling</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2569-2022 artfynd.xlsx", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2569-2022 karta.png", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2569-2022 georefererad karta.tif", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2569-2022 FSC-klagomål.docx", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2569-2022 FSC-klagomål mail.docx", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2569-2022 tillsynsbegäran.docx", "A 2569-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2569-2022 tillsynsbegäran mail.docx", "A 2569-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 73609-2021</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>44552</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 73609-2021 artfynd.xlsx", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 73609-2021 karta.png", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 73609-2021 georefererad karta.tif", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 73609-2021 FSC-klagomål.docx", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 73609-2021 FSC-klagomål mail.docx", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 73609-2021 tillsynsbegäran.docx", "A 73609-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 73609-2021 tillsynsbegäran mail.docx", "A 73609-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29176-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45821</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1696,7 +1703,7 @@
         <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1795,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33243-2026</t>
+          <t>A 12709-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1805,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46246</v>
+        <v>45733</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,13 +1824,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1835,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,58 +1849,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
         <v/>
       </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+        <v/>
+      </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34738-2026</t>
+          <t>A 29176-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46258</v>
+        <v>45821</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,23 +1933,18 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1966,259 +1967,260 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 34738-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 25554-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45082</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.6</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 12709-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45733</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2239,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,7 +2314,7 @@
         <v>44454</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2368,7 +2370,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49026-2021</t>
+          <t>A 46431-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2382,10 +2384,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44453</v>
+        <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2398,7 +2400,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2458,7 +2460,7 @@
         <v>44460</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2514,7 +2516,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46431-2022</t>
+          <t>A 18500-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2528,10 +2530,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44846</v>
+        <v>44686</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2544,7 +2546,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2587,7 +2589,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18500-2022</t>
+          <t>A 66603-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,10 +2603,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44686</v>
+        <v>44519</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2617,7 +2619,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2660,7 +2662,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 66603-2021</t>
+          <t>A 28167-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,10 +2676,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44519</v>
+        <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2690,7 +2692,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2733,7 +2735,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28167-2022</t>
+          <t>A 48636-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2747,10 +2749,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44746</v>
+        <v>44855</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2763,7 +2765,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2806,7 +2808,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48636-2022</t>
+          <t>A 60681-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2820,10 +2822,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44855</v>
+        <v>44496</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2836,7 +2838,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2879,7 +2881,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60681-2021</t>
+          <t>A 2640-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,10 +2895,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44496</v>
+        <v>44580</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2909,7 +2911,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2952,7 +2954,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2640-2022</t>
+          <t>A 52568-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2962,14 +2964,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44580</v>
+        <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2982,7 +2984,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3025,7 +3027,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52568-2021</t>
+          <t>A 52572-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,7 +3044,7 @@
         <v>44466</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3055,7 +3057,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3098,7 +3100,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52572-2021</t>
+          <t>A 26333-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,10 +3114,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44466</v>
+        <v>44735</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3128,7 +3130,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3171,7 +3173,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 26333-2022</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3185,10 +3187,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44735</v>
+        <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3201,7 +3203,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3244,7 +3246,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3254,14 +3256,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44883</v>
+        <v>44614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3273,8 +3275,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3317,7 +3324,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3331,10 +3338,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44614</v>
+        <v>44746</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3346,13 +3353,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>9.9</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3395,7 +3397,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3409,10 +3411,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44746</v>
+        <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,8 +3426,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3468,7 +3475,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3482,10 +3489,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44538</v>
+        <v>44652</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,13 +3504,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3546,7 +3548,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3560,10 +3562,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3576,7 +3578,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3619,7 +3621,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3633,10 +3635,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44621</v>
+        <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3649,7 +3651,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3692,7 +3694,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3706,10 +3708,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44525</v>
+        <v>44616</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,8 +3723,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3782,7 +3789,7 @@
         <v>44795</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3838,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 49365-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3852,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44616</v>
+        <v>44454</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,13 +3874,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3916,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49365-2021</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3930,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44454</v>
+        <v>45625</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3946,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3989,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4003,10 +4005,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44861</v>
+        <v>45625</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4019,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4062,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4076,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44893</v>
+        <v>45335</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4092,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4135,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4149,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45393</v>
+        <v>45002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4164,13 +4166,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4213,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4223,14 +4220,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45317</v>
+        <v>44797</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4243,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4286,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4296,14 +4293,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44797</v>
+        <v>45247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4316,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4359,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4373,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44880</v>
+        <v>45280</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4389,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4432,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4446,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45097</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4462,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4505,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4519,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44819</v>
+        <v>44580</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4535,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4578,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4592,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44879</v>
+        <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4608,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4651,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4665,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45280</v>
+        <v>45727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4681,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4724,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4738,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45272</v>
+        <v>45533</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4754,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4797,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4811,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45820</v>
+        <v>45735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4827,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4870,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4884,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45820</v>
+        <v>45737</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4900,7 +4897,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4943,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4957,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45597</v>
+        <v>45555</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4973,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5016,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5030,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45820</v>
+        <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5046,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5089,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5103,10 +5100,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45821</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5119,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5162,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5176,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44614</v>
+        <v>44897</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5191,13 +5188,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5240,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5254,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>46013</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5270,7 +5262,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5313,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5327,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45247</v>
+        <v>46012</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5343,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5386,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5400,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46070</v>
+        <v>46012</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5416,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5459,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5473,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46070</v>
+        <v>46012</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5489,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5532,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5546,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45594</v>
+        <v>45636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5562,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5605,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5619,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45436</v>
+        <v>45629</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5635,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5678,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5692,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45597</v>
+        <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5708,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5751,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5765,10 +5757,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45559</v>
+        <v>44746</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5781,7 +5773,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5841,7 +5833,7 @@
         <v>45790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5897,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5911,10 +5903,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45569</v>
+        <v>46034</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5927,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5970,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5984,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45728</v>
+        <v>46034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6043,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6057,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45727</v>
+        <v>45597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6073,7 +6065,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6116,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6130,10 +6122,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46072</v>
+        <v>45821</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6145,13 +6137,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6194,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6204,14 +6191,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45411</v>
+        <v>45820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6224,7 +6211,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6267,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6281,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45744</v>
+        <v>45820</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6297,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6340,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6354,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45869</v>
+        <v>45820</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6370,7 +6357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6413,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6427,10 +6414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45729</v>
+        <v>46037</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6443,7 +6430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6486,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6500,10 +6487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45273</v>
+        <v>45260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6516,7 +6503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6559,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6573,10 +6560,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45917</v>
+        <v>45825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6589,7 +6576,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6632,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6646,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45917</v>
+        <v>45258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6662,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6705,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6719,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>44738</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6778,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6792,10 +6779,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45624</v>
+        <v>45273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6808,7 +6795,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6851,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6865,10 +6852,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45567</v>
+        <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6881,7 +6868,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6924,7 +6911,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6938,10 +6925,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45881</v>
+        <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6954,7 +6941,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6997,7 +6984,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7007,14 +6994,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45146</v>
+        <v>45411</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7027,7 +7014,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7070,7 +7057,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7084,10 +7071,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45639</v>
+        <v>46059</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7100,7 +7087,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7143,7 +7130,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7157,10 +7144,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45881</v>
+        <v>46062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7173,7 +7160,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7216,7 +7203,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7226,14 +7213,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45930</v>
+        <v>45727</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7246,7 +7233,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7289,7 +7276,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7303,10 +7290,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45629</v>
+        <v>45728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7319,7 +7306,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7362,7 +7349,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7372,14 +7359,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45931</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7391,13 +7378,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7440,7 +7422,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7454,10 +7436,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45162</v>
+        <v>45931</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7469,8 +7451,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7513,7 +7500,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7527,10 +7514,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46085</v>
+        <v>46070</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7586,7 +7573,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7596,14 +7583,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46084</v>
+        <v>44832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,13 +7602,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7664,7 +7646,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7678,10 +7660,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45636</v>
+        <v>46070</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7694,7 +7676,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7737,7 +7719,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7751,10 +7733,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46085</v>
+        <v>46072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7766,8 +7748,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7810,7 +7797,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7824,10 +7811,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46086</v>
+        <v>45869</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7840,7 +7827,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7883,7 +7870,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7897,10 +7884,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46086</v>
+        <v>45624</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7913,7 +7900,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7956,7 +7943,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7970,10 +7957,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45679</v>
+        <v>45597</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7986,7 +7973,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8029,7 +8016,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8043,10 +8030,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45035</v>
+        <v>45729</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8059,7 +8046,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8102,7 +8089,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8116,10 +8103,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45727</v>
+        <v>45744</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8132,7 +8119,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8175,7 +8162,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8189,10 +8176,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46087</v>
+        <v>44953</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8204,13 +8191,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8253,7 +8235,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8267,10 +8249,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45946</v>
+        <v>45881</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8283,7 +8265,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8326,7 +8308,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8340,10 +8322,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46090</v>
+        <v>45881</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8356,7 +8338,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8399,7 +8381,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8409,14 +8391,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45629</v>
+        <v>46084</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8428,8 +8410,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8472,7 +8459,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8486,10 +8473,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45947</v>
+        <v>45639</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8502,7 +8489,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8545,7 +8532,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8559,10 +8546,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8575,7 +8562,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13.5</v>
+        <v>8.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8618,7 +8605,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8632,10 +8619,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45947</v>
+        <v>46086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8648,7 +8635,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8691,7 +8678,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8705,10 +8692,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46100</v>
+        <v>46085</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8721,7 +8708,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8764,7 +8751,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8778,10 +8765,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46106</v>
+        <v>46085</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,13 +8780,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8842,7 +8824,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8856,10 +8838,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46108</v>
+        <v>45947</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8871,13 +8853,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8920,7 +8897,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8934,10 +8911,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46108</v>
+        <v>45253</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8950,7 +8927,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8993,7 +8970,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9007,10 +8984,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45337</v>
+        <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9023,7 +9000,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9066,7 +9043,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9080,10 +9057,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45509</v>
+        <v>45946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9096,7 +9073,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9139,7 +9116,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9153,10 +9130,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45436</v>
+        <v>46087</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9168,8 +9145,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9212,7 +9194,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9226,10 +9208,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46000</v>
+        <v>46090</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9242,7 +9224,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9285,7 +9267,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9299,10 +9281,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>45146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9315,7 +9297,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9358,7 +9340,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9372,10 +9354,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>46094</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9388,7 +9370,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9431,7 +9413,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9445,10 +9427,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46002</v>
+        <v>46100</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9461,7 +9443,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9504,7 +9486,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9518,10 +9500,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45548</v>
+        <v>46106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9533,8 +9515,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9577,7 +9564,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9591,10 +9578,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46013</v>
+        <v>45272</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9607,7 +9594,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9650,7 +9637,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9664,10 +9651,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45679</v>
+        <v>46108</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,8 +9666,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9723,7 +9715,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9737,10 +9729,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46012</v>
+        <v>46108</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9753,7 +9745,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9796,7 +9788,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9810,10 +9802,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46012</v>
+        <v>45257</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9826,7 +9818,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9869,7 +9861,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9883,10 +9875,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46012</v>
+        <v>45281</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9899,7 +9891,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9942,7 +9934,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9956,10 +9948,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44965</v>
+        <v>44847</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9972,7 +9964,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10015,7 +10007,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10029,10 +10021,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46034</v>
+        <v>45317</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10045,7 +10037,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10088,7 +10080,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10102,10 +10094,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46034</v>
+        <v>45365</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10118,7 +10110,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10161,7 +10153,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10175,10 +10167,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46037</v>
+        <v>44965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10191,7 +10183,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10234,7 +10226,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10248,10 +10240,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45335</v>
+        <v>44965</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10264,7 +10256,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10307,7 +10299,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10321,10 +10313,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45170</v>
+        <v>44861</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10337,7 +10329,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10380,7 +10372,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10394,10 +10386,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45281</v>
+        <v>45625</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10410,7 +10402,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10453,7 +10445,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10467,10 +10459,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45111</v>
+        <v>44819</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10483,7 +10475,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10526,7 +10518,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10540,10 +10532,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45789</v>
+        <v>45252</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10556,7 +10548,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10599,7 +10591,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10613,10 +10605,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45625</v>
+        <v>45251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10629,7 +10621,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10672,7 +10664,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10686,10 +10678,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46059</v>
+        <v>45253</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10702,7 +10694,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10745,7 +10737,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10755,14 +10747,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46062</v>
+        <v>45299</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10775,7 +10767,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10818,7 +10810,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10832,10 +10824,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44778</v>
+        <v>46000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10848,7 +10840,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10891,7 +10883,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10905,10 +10897,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45146</v>
+        <v>45321</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10921,7 +10913,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10964,7 +10956,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10978,10 +10970,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45530</v>
+        <v>45789</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10994,7 +10986,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11037,7 +11029,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11051,10 +11043,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45146</v>
+        <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11067,7 +11059,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11110,7 +11102,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11124,10 +11116,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45075</v>
+        <v>46002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11140,7 +11132,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11183,7 +11175,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11197,10 +11189,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45398</v>
+        <v>46002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11213,7 +11205,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11256,7 +11248,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11270,10 +11262,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45625</v>
+        <v>45365</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11286,7 +11278,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11329,7 +11321,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11343,10 +11335,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45625</v>
+        <v>45035</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11359,7 +11351,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11402,7 +11394,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11416,10 +11408,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45337</v>
+        <v>44977</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11432,7 +11424,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11475,7 +11467,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11489,10 +11481,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44580</v>
+        <v>45111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11505,7 +11497,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11548,7 +11540,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11562,10 +11554,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45821</v>
+        <v>44999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11578,7 +11570,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11621,7 +11613,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11635,10 +11627,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45170</v>
+        <v>44978</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11651,7 +11643,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11694,7 +11686,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11708,10 +11700,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45947</v>
+        <v>45629</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11724,7 +11716,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11767,7 +11759,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11781,10 +11773,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45702</v>
+        <v>44778</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11797,7 +11789,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11840,7 +11832,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11854,10 +11846,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45763</v>
+        <v>45679</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11870,7 +11862,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11913,7 +11905,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11927,10 +11919,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45253</v>
+        <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11943,7 +11935,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11986,7 +11978,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12000,10 +11992,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46174</v>
+        <v>45111</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12016,7 +12008,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12059,7 +12051,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12073,10 +12065,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46174</v>
+        <v>44614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12088,8 +12080,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12132,7 +12129,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12146,10 +12143,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45251</v>
+        <v>45821</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12162,7 +12159,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12205,7 +12202,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12219,10 +12216,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44746</v>
+        <v>45702</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12278,7 +12275,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12292,10 +12289,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45714</v>
+        <v>45947</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12308,7 +12305,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12351,7 +12348,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12365,10 +12362,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44738</v>
+        <v>46174</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12381,7 +12378,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12424,7 +12421,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12438,10 +12435,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45728</v>
+        <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12454,7 +12451,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12497,7 +12494,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12507,14 +12504,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45299</v>
+        <v>45720</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12527,7 +12524,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12570,7 +12567,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12584,10 +12581,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44861</v>
+        <v>44978</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12600,7 +12597,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12643,7 +12640,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12657,10 +12654,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45531</v>
+        <v>45573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12673,7 +12670,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>14</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12716,7 +12713,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12726,14 +12723,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45296</v>
+        <v>46245</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12746,7 +12743,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12789,7 +12786,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12803,10 +12800,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44847</v>
+        <v>46247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12818,8 +12815,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12862,7 +12864,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12876,10 +12878,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45448</v>
+        <v>46252</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12891,8 +12893,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12935,7 +12942,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12949,10 +12956,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45720</v>
+        <v>45705</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12965,7 +12972,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13008,7 +13015,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13022,10 +13029,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44953</v>
+        <v>45337</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13038,7 +13045,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13081,7 +13088,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13095,10 +13102,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44978</v>
+        <v>46258</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13110,8 +13117,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13154,7 +13166,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13168,10 +13180,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45155</v>
+        <v>46258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13184,7 +13196,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13227,7 +13239,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13237,14 +13249,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13300,7 +13312,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13317,7 +13329,7 @@
         <v>45705</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13330,7 +13342,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13373,7 +13385,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13387,10 +13399,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46247</v>
+        <v>45398</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13402,13 +13414,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13451,7 +13458,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13461,14 +13468,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44977</v>
+        <v>45369</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13481,7 +13488,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13524,7 +13531,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13538,10 +13545,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44977</v>
+        <v>46275</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13554,7 +13561,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13597,7 +13604,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13611,10 +13618,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44746</v>
+        <v>45337</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13627,7 +13634,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13670,7 +13677,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13684,10 +13691,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46252</v>
+        <v>45075</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13699,13 +13706,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13748,7 +13750,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13762,10 +13764,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45513</v>
+        <v>45548</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13778,7 +13780,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>10.2</v>
+        <v>3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13821,7 +13823,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13835,10 +13837,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45237</v>
+        <v>45559</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13851,7 +13853,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13894,7 +13896,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13908,10 +13910,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44978</v>
+        <v>44893</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13924,7 +13926,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13967,7 +13969,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13981,10 +13983,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46258</v>
+        <v>45679</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13996,13 +13998,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14045,7 +14042,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14059,10 +14056,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44999</v>
+        <v>45509</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14075,7 +14072,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14118,7 +14115,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14132,10 +14129,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45573</v>
+        <v>45763</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14148,7 +14145,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14191,7 +14188,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14205,10 +14202,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45281</v>
+        <v>44880</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14221,7 +14218,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14264,7 +14261,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14278,10 +14275,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45001</v>
+        <v>45296</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14294,7 +14291,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14337,7 +14334,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14351,10 +14348,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46258</v>
+        <v>45530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14367,7 +14364,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14410,7 +14407,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14424,10 +14421,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46259</v>
+        <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14440,7 +14437,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14483,7 +14480,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14497,10 +14494,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45111</v>
+        <v>45436</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14513,7 +14510,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14556,7 +14553,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14570,10 +14567,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45365</v>
+        <v>45393</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14585,8 +14582,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14629,7 +14631,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14643,10 +14645,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45365</v>
+        <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14659,7 +14661,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14702,7 +14704,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14716,10 +14718,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45146</v>
+        <v>45714</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14732,7 +14734,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14775,7 +14777,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14789,10 +14791,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45257</v>
+        <v>45001</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14805,7 +14807,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14848,7 +14850,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14862,10 +14864,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45252</v>
+        <v>45594</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14878,7 +14880,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14921,7 +14923,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14931,14 +14933,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45369</v>
+        <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14951,7 +14953,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14994,7 +14996,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15008,10 +15010,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45471</v>
+        <v>44861</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15024,7 +15026,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15067,7 +15069,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15081,10 +15083,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44832</v>
+        <v>44977</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15097,7 +15099,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15140,7 +15142,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15154,10 +15156,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44965</v>
+        <v>44977</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15170,7 +15172,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15213,7 +15215,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15227,10 +15229,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45258</v>
+        <v>45170</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15243,7 +15245,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15286,7 +15288,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15300,10 +15302,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45260</v>
+        <v>45513</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15316,7 +15318,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>10.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15359,7 +15361,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15373,10 +15375,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45321</v>
+        <v>45146</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15389,7 +15391,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15432,7 +15434,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15446,10 +15448,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45097</v>
+        <v>45146</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15462,7 +15464,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15505,7 +15507,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15519,10 +15521,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45621</v>
+        <v>45471</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15535,7 +15537,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15578,7 +15580,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15592,10 +15594,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45575</v>
+        <v>45621</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15608,7 +15610,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15651,7 +15653,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15665,10 +15667,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45705</v>
+        <v>45567</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15681,7 +15683,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15724,7 +15726,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15738,10 +15740,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45002</v>
+        <v>45155</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15754,7 +15756,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15797,7 +15799,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15811,10 +15813,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46275</v>
+        <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15827,7 +15829,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15870,7 +15872,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15884,10 +15886,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45393</v>
+        <v>45448</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15899,13 +15901,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15948,7 +15945,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15962,10 +15959,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45713</v>
+        <v>45146</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15978,7 +15975,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16021,7 +16018,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16035,10 +16032,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45720</v>
+        <v>45393</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16050,8 +16047,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16094,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16108,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45728</v>
+        <v>45170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16124,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16167,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16181,10 +16183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45721</v>
+        <v>45728</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16197,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>11.8</v>
+        <v>2.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16240,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16254,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45737</v>
+        <v>45575</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16270,7 +16272,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16313,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16327,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45533</v>
+        <v>44746</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16343,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16386,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16400,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45735</v>
+        <v>45569</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16416,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16459,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16473,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44897</v>
+        <v>45436</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16489,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16532,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16546,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45555</v>
+        <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16562,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16605,7 +16607,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16619,10 +16621,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45695</v>
+        <v>45721</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16635,7 +16637,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>11.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16678,7 +16680,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16692,10 +16694,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45567</v>
+        <v>45713</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16708,7 +16710,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16751,24 +16753,24 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>S 1882-2020</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45812</v>
+        <v>44075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16781,7 +16783,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16824,7 +16826,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>S 1882-2020</t>
+          <t>S 5185-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16834,14 +16836,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44075</v>
+        <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16854,7 +16856,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16897,7 +16899,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>S 5185-2022</t>
+          <t>S 4944-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16911,83 +16913,83 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>0</v>
+      </c>
+      <c r="V217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>S 5191-2022</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="n">
         <v>44823</v>
       </c>
-      <c r="E217" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>2</v>
-      </c>
-      <c r="J217" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" t="n">
-        <v>0</v>
-      </c>
-      <c r="O217" t="n">
-        <v>0</v>
-      </c>
-      <c r="P217" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" t="n">
-        <v>0</v>
-      </c>
-      <c r="T217" t="n">
-        <v>0</v>
-      </c>
-      <c r="U217" t="n">
-        <v>0</v>
-      </c>
-      <c r="V217" s="2" t="inlineStr"/>
-    </row>
-    <row r="218" ht="15" customHeight="1">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>S 4944-2024</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>45625</v>
-      </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17000,7 +17002,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17039,79 +17041,6 @@
         <v>0</v>
       </c>
       <c r="V218" s="2" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>S 5191-2022</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D219" s="1" t="n">
-        <v>44823</v>
-      </c>
-      <c r="E219" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I219" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J219" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="P219" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" t="n">
-        <v>0</v>
-      </c>
-      <c r="U219" t="n">
-        <v>0</v>
-      </c>
-      <c r="V219" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE218"/>
+  <dimension ref="A1:AE216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 33243-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45159</v>
+        <v>46246</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1070,23 +1070,28 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>21.1</v>
+        <v>12.7</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1098,169 +1103,164 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Silversmygare
+Kopparödla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33243-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Silversmygare
-Kopparödla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2637-2022</t>
+          <t>A 29176-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44580</v>
+        <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1743,168 +1743,164 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2637-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44580</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12709-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45733</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 29176-2025</t>
+          <t>A 25554-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1914,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45821</v>
+        <v>45082</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1930,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1970,39 +1966,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2022,7 @@
         <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2115,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25554-2023</t>
+          <t>A 12709-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2133,10 +2129,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45082</v>
+        <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2149,19 +2145,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2176,48 +2172,52 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
         <v/>
       </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+        <v/>
+      </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49378-2021</t>
+          <t>A 51196-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,14 +2307,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44454</v>
+        <v>44460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51196-2021</t>
+          <t>A 18500-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44460</v>
+        <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18500-2022</t>
+          <t>A 66603-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44686</v>
+        <v>44519</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 66603-2021</t>
+          <t>A 28167-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44519</v>
+        <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28167-2022</t>
+          <t>A 48636-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44746</v>
+        <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48636-2022</t>
+          <t>A 60681-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44855</v>
+        <v>44496</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60681-2021</t>
+          <t>A 2640-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44496</v>
+        <v>44580</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2640-2022</t>
+          <t>A 52568-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2891,14 +2891,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44580</v>
+        <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2954,7 +2954,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52568-2021</t>
+          <t>A 52572-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2971,7 +2971,7 @@
         <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52572-2021</t>
+          <t>A 26333-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44466</v>
+        <v>44735</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26333-2022</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3110,14 +3110,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44735</v>
+        <v>44525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44883</v>
+        <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3256,14 +3256,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44614</v>
+        <v>44883</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3275,13 +3275,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>9.9</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3324,7 +3319,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44746</v>
+        <v>44614</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3353,8 +3348,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>9.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44538</v>
+        <v>44861</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3426,13 +3426,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3475,7 +3470,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3489,10 +3484,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44652</v>
+        <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3505,7 +3500,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3548,7 +3543,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3562,10 +3557,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44621</v>
+        <v>44538</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3577,8 +3572,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3621,7 +3621,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44525</v>
+        <v>44893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>44616</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44795</v>
+        <v>44652</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49365-2021</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44454</v>
+        <v>44795</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45625</v>
+        <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45625</v>
+        <v>45251</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45335</v>
+        <v>44746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45002</v>
+        <v>45714</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4220,14 +4220,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44797</v>
+        <v>45393</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4239,8 +4239,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4288,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45247</v>
+        <v>45881</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4361,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45280</v>
+        <v>45639</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4391,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4434,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45097</v>
+        <v>45881</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4464,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44580</v>
+        <v>44738</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4537,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4580,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4585,14 +4590,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45728</v>
+        <v>44797</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4610,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4653,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4683,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4721,7 +4726,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45533</v>
+        <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4756,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45735</v>
+        <v>44880</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4824,7 +4829,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4877,14 +4882,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45737</v>
+        <v>45299</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45555</v>
+        <v>44861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45695</v>
+        <v>45597</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5043,7 +5048,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5091,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5100,10 +5105,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>46085</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5164,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44897</v>
+        <v>45253</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5194,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5237,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5242,14 +5247,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5261,8 +5266,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5315,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5329,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46012</v>
+        <v>46085</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5345,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5388,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5402,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46012</v>
+        <v>46086</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5418,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5461,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5475,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46012</v>
+        <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5491,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5534,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5548,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45636</v>
+        <v>46087</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5553,8 +5563,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5612,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5626,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45629</v>
+        <v>45790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5642,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5685,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5699,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45812</v>
+        <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5715,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5758,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5757,10 +5772,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44746</v>
+        <v>45531</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5773,7 +5788,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5831,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5845,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45790</v>
+        <v>44819</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5861,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5904,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,10 +5918,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46034</v>
+        <v>46094</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5934,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>13.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5977,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5991,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46034</v>
+        <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6035,7 +6050,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6064,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45597</v>
+        <v>46100</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6065,7 +6080,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6123,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6122,10 +6137,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45821</v>
+        <v>45296</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6153,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6196,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6210,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45820</v>
+        <v>45280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6211,7 +6226,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6254,7 +6269,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6283,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45820</v>
+        <v>45272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6299,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6342,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6356,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45820</v>
+        <v>46106</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6356,8 +6371,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6420,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6414,10 +6434,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46037</v>
+        <v>45917</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6430,7 +6450,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6473,7 +6493,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6487,10 +6507,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45260</v>
+        <v>45917</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6503,7 +6523,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6546,7 +6566,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6560,10 +6580,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45825</v>
+        <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6575,8 +6595,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6644,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6658,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45258</v>
+        <v>44847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6674,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6717,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6731,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44738</v>
+        <v>46108</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6747,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6790,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,10 +6804,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45273</v>
+        <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6795,7 +6820,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6863,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6852,10 +6877,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45917</v>
+        <v>44614</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6867,8 +6892,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6911,7 +6941,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6921,14 +6951,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45917</v>
+        <v>45930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6941,7 +6971,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6984,7 +7014,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6994,14 +7024,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45411</v>
+        <v>45247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7044,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7057,7 +7087,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7071,10 +7101,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46059</v>
+        <v>45931</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7086,8 +7116,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7130,7 +7165,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7144,10 +7179,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46062</v>
+        <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7195,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7203,7 +7238,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7217,10 +7252,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45727</v>
+        <v>45436</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7268,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7276,7 +7311,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7290,10 +7325,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45728</v>
+        <v>45597</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7306,7 +7341,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7349,7 +7384,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7359,14 +7394,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45930</v>
+        <v>45946</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7414,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7422,7 +7457,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7436,10 +7471,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45931</v>
+        <v>45559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7451,13 +7486,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7500,7 +7530,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7514,10 +7544,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46070</v>
+        <v>44953</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7530,7 +7560,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7573,7 +7603,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7587,10 +7617,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44832</v>
+        <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7603,7 +7633,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7646,7 +7676,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7660,10 +7690,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46070</v>
+        <v>45947</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7676,7 +7706,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7719,7 +7749,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7733,10 +7763,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46072</v>
+        <v>45569</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7748,13 +7778,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7797,7 +7822,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7807,14 +7832,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45869</v>
+        <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7827,7 +7852,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7870,7 +7895,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7884,10 +7909,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45624</v>
+        <v>45273</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7900,7 +7925,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7943,7 +7968,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7957,10 +7982,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45597</v>
+        <v>44977</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7973,7 +7998,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8016,7 +8041,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8030,10 +8055,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45729</v>
+        <v>45567</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8046,7 +8071,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8089,7 +8114,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8103,10 +8128,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45744</v>
+        <v>45146</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8119,7 +8144,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8162,7 +8187,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8176,10 +8201,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44953</v>
+        <v>45789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8192,7 +8217,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8235,7 +8260,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8249,10 +8274,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45881</v>
+        <v>44978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8265,7 +8290,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8308,7 +8333,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8322,10 +8347,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45881</v>
+        <v>45625</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8338,7 +8363,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8381,7 +8406,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8391,14 +8416,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46084</v>
+        <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8410,13 +8435,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8459,7 +8479,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8473,10 +8493,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45639</v>
+        <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8489,7 +8509,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8532,7 +8552,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8546,10 +8566,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46086</v>
+        <v>45155</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8562,7 +8582,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8605,7 +8625,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8619,10 +8639,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46086</v>
+        <v>45636</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8635,7 +8655,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8678,7 +8698,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8692,10 +8712,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46085</v>
+        <v>45679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8708,7 +8728,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8751,7 +8771,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8765,10 +8785,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46085</v>
+        <v>45035</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,7 +8801,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8824,7 +8844,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8838,10 +8858,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45947</v>
+        <v>45727</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8854,7 +8874,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8897,7 +8917,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8911,10 +8931,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45253</v>
+        <v>45705</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8927,7 +8947,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8970,7 +8990,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8984,10 +9004,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45947</v>
+        <v>45629</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9000,7 +9020,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9043,7 +9063,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9057,10 +9077,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45946</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9073,7 +9093,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9116,7 +9136,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9130,10 +9150,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46087</v>
+        <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9145,13 +9165,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9194,7 +9209,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9208,10 +9223,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46090</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9224,7 +9239,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9267,7 +9282,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9281,10 +9296,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45146</v>
+        <v>46002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9297,7 +9312,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9340,7 +9355,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9354,10 +9369,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46094</v>
+        <v>44977</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9370,7 +9385,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9413,7 +9428,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9427,10 +9442,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46100</v>
+        <v>44977</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9443,7 +9458,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9486,7 +9501,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9500,10 +9515,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46106</v>
+        <v>44746</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9515,13 +9530,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9564,7 +9574,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9578,10 +9588,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45272</v>
+        <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9594,7 +9604,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9637,7 +9647,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9651,10 +9661,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46108</v>
+        <v>45821</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9666,13 +9676,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9715,7 +9720,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9729,10 +9734,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46108</v>
+        <v>46013</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9745,7 +9750,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9788,7 +9793,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9802,10 +9807,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45257</v>
+        <v>46012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9818,7 +9823,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9861,7 +9866,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9875,10 +9880,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45281</v>
+        <v>46012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9891,7 +9896,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9934,7 +9939,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9948,10 +9953,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44847</v>
+        <v>46012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9964,7 +9969,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10007,7 +10012,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10021,10 +10026,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45317</v>
+        <v>45509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10037,7 +10042,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10080,7 +10085,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10094,10 +10099,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45365</v>
+        <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10110,7 +10115,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10153,7 +10158,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10167,10 +10172,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44965</v>
+        <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10183,7 +10188,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10226,7 +10231,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10240,10 +10245,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44965</v>
+        <v>45436</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10256,7 +10261,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10299,7 +10304,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10313,10 +10318,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44861</v>
+        <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10329,7 +10334,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10372,7 +10377,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10386,10 +10391,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45625</v>
+        <v>46037</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10402,7 +10407,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10445,7 +10450,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10459,10 +10464,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44819</v>
+        <v>46174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10475,7 +10480,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10518,7 +10523,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10532,10 +10537,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45252</v>
+        <v>46174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10548,7 +10553,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10591,7 +10596,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10605,10 +10610,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45251</v>
+        <v>45548</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10621,7 +10626,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10664,7 +10669,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10678,10 +10683,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45253</v>
+        <v>45679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10694,7 +10699,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10737,7 +10742,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10747,14 +10752,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45299</v>
+        <v>46059</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10767,7 +10772,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10810,7 +10815,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10824,10 +10829,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46000</v>
+        <v>46062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10840,7 +10845,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10883,7 +10888,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10897,10 +10902,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45321</v>
+        <v>44965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10913,7 +10918,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10956,7 +10961,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10970,10 +10975,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45789</v>
+        <v>46070</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10986,7 +10991,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11029,7 +11034,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11043,10 +11048,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46002</v>
+        <v>46070</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11059,7 +11064,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11102,7 +11107,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11116,10 +11121,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46002</v>
+        <v>46072</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11131,8 +11136,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11175,7 +11185,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11189,10 +11199,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46002</v>
+        <v>45513</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11205,7 +11215,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11248,7 +11258,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11262,10 +11272,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45365</v>
+        <v>45237</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11278,7 +11288,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11321,7 +11331,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11335,10 +11345,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45035</v>
+        <v>45335</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11351,7 +11361,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11394,7 +11404,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11408,10 +11418,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44977</v>
+        <v>44978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11424,7 +11434,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11467,7 +11477,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11481,10 +11491,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45111</v>
+        <v>45170</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11497,7 +11507,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11540,7 +11550,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11554,10 +11564,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44999</v>
+        <v>45281</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11570,7 +11580,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11613,7 +11623,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11627,10 +11637,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44978</v>
+        <v>44999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11643,7 +11653,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11686,7 +11696,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11700,10 +11710,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45629</v>
+        <v>45720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11716,7 +11726,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11759,7 +11769,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11773,10 +11783,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44778</v>
+        <v>45111</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11789,7 +11799,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11832,7 +11842,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11846,10 +11856,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45679</v>
+        <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11862,7 +11872,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11905,7 +11915,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11919,10 +11929,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45162</v>
+        <v>45281</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11935,7 +11945,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11978,7 +11988,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11992,10 +12002,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45111</v>
+        <v>45001</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12008,7 +12018,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12051,7 +12061,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12065,10 +12075,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44614</v>
+        <v>45111</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12080,13 +12090,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12129,7 +12134,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12143,10 +12148,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45821</v>
+        <v>44778</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12159,7 +12164,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12202,7 +12207,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12212,14 +12217,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45702</v>
+        <v>46245</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12275,7 +12280,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12289,10 +12294,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45947</v>
+        <v>45146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12305,7 +12310,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12353,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12362,10 +12367,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46174</v>
+        <v>45530</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12378,7 +12383,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12421,7 +12426,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12435,10 +12440,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46174</v>
+        <v>46247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12450,8 +12455,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12494,7 +12504,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12508,10 +12518,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45720</v>
+        <v>45146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12524,7 +12534,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12567,7 +12577,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12581,10 +12591,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44978</v>
+        <v>45365</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12597,7 +12607,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12640,7 +12650,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12654,10 +12664,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45573</v>
+        <v>45365</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12670,7 +12680,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12713,7 +12723,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12723,14 +12733,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46245</v>
+        <v>45075</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,7 +12753,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12786,7 +12796,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12800,10 +12810,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46247</v>
+        <v>45398</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12815,13 +12825,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12864,7 +12869,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12878,10 +12883,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46252</v>
+        <v>45625</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12893,13 +12898,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12942,7 +12942,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45705</v>
+        <v>45625</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13015,7 +13015,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13032,7 +13032,7 @@
         <v>45337</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13088,7 +13088,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46258</v>
+        <v>44580</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13117,13 +13117,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13166,7 +13161,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13180,10 +13175,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13195,8 +13190,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13239,7 +13239,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13253,10 +13253,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46259</v>
+        <v>45170</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13326,10 +13326,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45705</v>
+        <v>45146</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13385,7 +13385,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13399,10 +13399,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45398</v>
+        <v>46258</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13414,8 +13414,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13458,7 +13463,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13468,14 +13473,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45369</v>
+        <v>46258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13488,7 +13493,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13531,7 +13536,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13545,10 +13550,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13561,7 +13566,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13604,7 +13609,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13618,10 +13623,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45337</v>
+        <v>45257</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13634,7 +13639,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13677,7 +13682,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13691,10 +13696,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45075</v>
+        <v>45702</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13707,7 +13712,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13750,7 +13755,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13764,10 +13769,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45548</v>
+        <v>45252</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13780,7 +13785,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13823,7 +13828,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13833,14 +13838,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45559</v>
+        <v>45369</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13853,7 +13858,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13896,7 +13901,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13910,10 +13915,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44893</v>
+        <v>45763</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13926,7 +13931,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13969,7 +13974,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13983,10 +13988,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45679</v>
+        <v>45471</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13999,7 +14004,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14042,7 +14047,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14056,10 +14061,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45509</v>
+        <v>44832</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14072,7 +14077,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14115,7 +14120,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14129,10 +14134,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45763</v>
+        <v>44965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14145,7 +14150,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14188,7 +14193,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14202,10 +14207,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44880</v>
+        <v>45258</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14218,7 +14223,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14261,7 +14266,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14275,10 +14280,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45296</v>
+        <v>45260</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14291,7 +14296,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14334,7 +14339,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14348,10 +14353,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45530</v>
+        <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14364,7 +14369,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14407,7 +14412,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14421,10 +14426,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45531</v>
+        <v>45097</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14437,7 +14442,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>14</v>
+        <v>3.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14480,7 +14485,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14494,10 +14499,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45436</v>
+        <v>45621</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14510,7 +14515,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14553,7 +14558,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14567,10 +14572,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45393</v>
+        <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14582,13 +14587,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14631,7 +14631,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14645,10 +14645,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45237</v>
+        <v>45705</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14704,7 +14704,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45714</v>
+        <v>45002</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14777,7 +14777,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14791,10 +14791,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45001</v>
+        <v>46275</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14864,10 +14864,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45594</v>
+        <v>45393</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14879,8 +14879,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14923,7 +14928,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14937,10 +14942,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45281</v>
+        <v>45713</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14953,7 +14958,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14996,7 +15001,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15010,10 +15015,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44861</v>
+        <v>45720</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15026,7 +15031,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15069,7 +15074,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15083,10 +15088,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44977</v>
+        <v>45728</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15099,7 +15104,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15142,7 +15147,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15156,10 +15161,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44977</v>
+        <v>45721</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15172,7 +15177,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.3</v>
+        <v>11.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15215,7 +15220,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15229,10 +15234,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45170</v>
+        <v>45737</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15245,7 +15250,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15288,7 +15293,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15302,10 +15307,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45513</v>
+        <v>45533</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15318,7 +15323,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>10.2</v>
+        <v>4.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15361,7 +15366,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15375,10 +15380,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45146</v>
+        <v>45735</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15391,7 +15396,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15434,7 +15439,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15448,10 +15453,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45146</v>
+        <v>44897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15464,7 +15469,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15507,7 +15512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15521,10 +15526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45471</v>
+        <v>45555</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15537,7 +15542,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15580,7 +15585,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15594,10 +15599,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45621</v>
+        <v>45695</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15610,7 +15615,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15653,7 +15658,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15670,7 +15675,7 @@
         <v>45567</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15683,7 +15688,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15726,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15740,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45155</v>
+        <v>45812</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15756,7 +15761,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15799,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15813,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44879</v>
+        <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15829,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15872,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15886,10 +15891,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45448</v>
+        <v>45820</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15902,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15945,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15959,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45146</v>
+        <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15975,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16018,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16032,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45393</v>
+        <v>45821</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16047,13 +16052,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45170</v>
+        <v>45825</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16186,7 +16186,7 @@
         <v>45728</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45575</v>
+        <v>45727</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16315,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44746</v>
+        <v>45744</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45569</v>
+        <v>45869</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45436</v>
+        <v>45729</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45720</v>
+        <v>45624</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16607,24 +16607,24 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>S 1882-2020</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45721</v>
+        <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>11.8</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16680,24 +16680,24 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>S 5185-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45713</v>
+        <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16753,7 +16753,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>S 1882-2020</t>
+          <t>S 4944-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16763,14 +16763,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44075</v>
+        <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
       </c>
       <c r="V215" s="2" t="inlineStr"/>
     </row>
-    <row r="216" ht="15" customHeight="1">
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>S 5185-2022</t>
+          <t>S 5191-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16895,152 +16895,6 @@
         <v>0</v>
       </c>
       <c r="V216" s="2" t="inlineStr"/>
-    </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>S 4944-2024</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E217" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J217" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" t="n">
-        <v>0</v>
-      </c>
-      <c r="O217" t="n">
-        <v>0</v>
-      </c>
-      <c r="P217" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" t="n">
-        <v>0</v>
-      </c>
-      <c r="T217" t="n">
-        <v>0</v>
-      </c>
-      <c r="U217" t="n">
-        <v>0</v>
-      </c>
-      <c r="V217" s="2" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>S 5191-2022</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>44823</v>
-      </c>
-      <c r="E218" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I218" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J218" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" t="n">
-        <v>0</v>
-      </c>
-      <c r="O218" t="n">
-        <v>0</v>
-      </c>
-      <c r="P218" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" t="n">
-        <v>0</v>
-      </c>
-      <c r="T218" t="n">
-        <v>0</v>
-      </c>
-      <c r="U218" t="n">
-        <v>0</v>
-      </c>
-      <c r="V218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33243-2026</t>
+          <t>A 37767-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46246</v>
+        <v>45159</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1070,28 +1070,23 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>12.7</v>
+        <v>21.1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1103,164 +1098,169 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Pärluggla
+Sotlav
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33243-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Silversmygare
 Kopparödla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 37767-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Pärluggla
-Sotlav
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 29176-2025</t>
+          <t>A 2637-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45821</v>
+        <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1743,160 +1743,160 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29176-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2637-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44580</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45082</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44460</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44519</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44496</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44580</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44735</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3110,14 +3110,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44525</v>
+        <v>44883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45253</v>
+        <v>44614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3202,8 +3202,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3246,7 +3251,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3256,14 +3261,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44883</v>
+        <v>44746</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3276,7 +3281,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3319,7 +3324,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3333,10 +3338,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44614</v>
+        <v>44538</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,7 +3359,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3397,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3411,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44861</v>
+        <v>44652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3427,7 +3432,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3470,7 +3475,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3484,10 +3489,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44746</v>
+        <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3505,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3543,7 +3548,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44538</v>
+        <v>44525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3572,13 +3577,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3621,7 +3621,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44893</v>
+        <v>44616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3650,8 +3650,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3694,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3708,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44616</v>
+        <v>44795</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3723,13 +3728,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44652</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44795</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44621</v>
+        <v>45335</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4001,14 +4001,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45251</v>
+        <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44746</v>
+        <v>45280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45714</v>
+        <v>45247</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45393</v>
+        <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4239,13 +4239,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4288,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45881</v>
+        <v>45097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4318,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4361,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45639</v>
+        <v>44580</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4391,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4434,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45881</v>
+        <v>45727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4464,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44738</v>
+        <v>45636</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4537,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4590,14 +4585,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44797</v>
+        <v>45629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4667,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45728</v>
+        <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4726,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45317</v>
+        <v>45567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4756,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4799,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44880</v>
+        <v>44746</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4829,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4882,14 +4877,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45299</v>
+        <v>44897</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4902,7 +4897,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44861</v>
+        <v>45597</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4975,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5018,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45597</v>
+        <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5048,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5091,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5105,10 +5100,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46085</v>
+        <v>45258</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5121,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5164,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5178,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45253</v>
+        <v>44738</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5194,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5237,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5247,14 +5242,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46084</v>
+        <v>45812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5266,13 +5261,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5315,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5329,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46085</v>
+        <v>45273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5345,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5388,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5402,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46086</v>
+        <v>45790</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5418,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5461,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5475,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46086</v>
+        <v>45821</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5534,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5548,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46087</v>
+        <v>45820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5563,13 +5553,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5612,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5626,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45790</v>
+        <v>45820</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5642,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5685,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5699,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46090</v>
+        <v>46034</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5715,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5758,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5772,10 +5757,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45531</v>
+        <v>46034</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5788,7 +5773,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5831,7 +5816,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5845,10 +5830,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44819</v>
+        <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5861,7 +5846,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5904,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5914,14 +5899,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46094</v>
+        <v>45411</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5934,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13.5</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5977,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5991,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44879</v>
+        <v>45825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6007,7 +5992,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6050,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6064,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46100</v>
+        <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6080,7 +6065,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6123,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6137,10 +6122,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45296</v>
+        <v>45917</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6153,7 +6138,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6196,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6210,10 +6195,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45280</v>
+        <v>45917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6226,7 +6211,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6269,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6283,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45272</v>
+        <v>45597</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6299,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6342,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6356,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46106</v>
+        <v>44953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6371,13 +6356,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6420,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6434,10 +6414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45917</v>
+        <v>46037</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6450,7 +6430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6493,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6507,10 +6487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45917</v>
+        <v>45727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6523,7 +6503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6566,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6580,10 +6560,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46108</v>
+        <v>45728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6595,13 +6575,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6644,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6658,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44847</v>
+        <v>45253</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6674,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6717,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6731,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46108</v>
+        <v>45146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6747,7 +6722,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6790,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6800,14 +6775,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45448</v>
+        <v>45930</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6820,7 +6795,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6863,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6877,10 +6852,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44614</v>
+        <v>45931</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6898,7 +6873,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6941,7 +6916,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6951,14 +6926,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6971,7 +6946,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7014,7 +6989,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7028,10 +7003,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45247</v>
+        <v>45624</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7044,7 +7019,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7087,7 +7062,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7101,10 +7076,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45931</v>
+        <v>45729</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7116,13 +7091,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7165,7 +7135,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7179,10 +7149,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45594</v>
+        <v>45744</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7195,7 +7165,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7238,7 +7208,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7252,10 +7222,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45436</v>
+        <v>45881</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7268,7 +7238,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7311,7 +7281,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7325,10 +7295,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45597</v>
+        <v>45881</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7341,7 +7311,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7384,7 +7354,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7398,10 +7368,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7414,7 +7384,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7457,7 +7427,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7471,10 +7441,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45559</v>
+        <v>45639</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7487,7 +7457,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7530,7 +7500,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7544,10 +7514,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44953</v>
+        <v>45947</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7560,7 +7530,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7603,7 +7573,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7617,10 +7587,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45947</v>
+        <v>45946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7633,7 +7603,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7676,7 +7646,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7690,10 +7660,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45947</v>
+        <v>45272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7749,7 +7719,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7763,10 +7733,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45569</v>
+        <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7779,7 +7749,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7822,7 +7792,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7832,14 +7802,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45411</v>
+        <v>45281</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7852,7 +7822,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7895,7 +7865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7909,10 +7879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45273</v>
+        <v>46059</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7925,7 +7895,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7968,7 +7938,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7982,10 +7952,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44977</v>
+        <v>44847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7998,7 +7968,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8041,7 +8011,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8055,10 +8025,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45567</v>
+        <v>46062</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8071,7 +8041,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8114,7 +8084,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8128,10 +8098,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45146</v>
+        <v>45317</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8144,7 +8114,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8187,7 +8157,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8201,10 +8171,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45789</v>
+        <v>45365</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8217,7 +8187,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8260,7 +8230,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8274,10 +8244,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44978</v>
+        <v>44965</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8290,7 +8260,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8333,7 +8303,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8347,10 +8317,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45625</v>
+        <v>44965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8363,7 +8333,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8406,7 +8376,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8420,10 +8390,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45629</v>
+        <v>44861</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8436,7 +8406,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8479,7 +8449,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8493,10 +8463,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45162</v>
+        <v>46070</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8509,7 +8479,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8552,7 +8522,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8566,10 +8536,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45155</v>
+        <v>46070</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8582,7 +8552,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8625,7 +8595,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8639,10 +8609,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45636</v>
+        <v>46072</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8654,8 +8624,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8698,7 +8673,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8712,10 +8687,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45679</v>
+        <v>44819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8728,7 +8703,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8771,7 +8746,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8785,10 +8760,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45035</v>
+        <v>45252</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8801,7 +8776,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8844,7 +8819,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8858,10 +8833,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45727</v>
+        <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8874,7 +8849,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8917,7 +8892,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8931,10 +8906,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45705</v>
+        <v>45253</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8947,7 +8922,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8990,7 +8965,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9000,14 +8975,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45629</v>
+        <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9020,7 +8995,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9063,7 +9038,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9073,14 +9048,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>46084</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9092,8 +9067,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9136,7 +9116,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9150,10 +9130,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46002</v>
+        <v>45321</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9166,7 +9146,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9209,7 +9189,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9223,10 +9203,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>46086</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9239,7 +9219,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9282,7 +9262,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9296,10 +9276,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>46086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9312,7 +9292,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9355,7 +9335,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9369,10 +9349,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44977</v>
+        <v>46085</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9385,7 +9365,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9428,7 +9408,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9442,10 +9422,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44977</v>
+        <v>46085</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9458,7 +9438,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9501,7 +9481,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9515,10 +9495,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44746</v>
+        <v>45365</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9531,7 +9511,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9574,7 +9554,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9588,10 +9568,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45337</v>
+        <v>46000</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9604,7 +9584,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9647,7 +9627,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9661,10 +9641,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45821</v>
+        <v>45035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9677,7 +9657,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9720,7 +9700,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9734,10 +9714,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46013</v>
+        <v>44977</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9750,7 +9730,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9793,7 +9773,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9807,10 +9787,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46012</v>
+        <v>46087</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9822,8 +9802,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9866,7 +9851,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9880,10 +9865,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46012</v>
+        <v>45111</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9896,7 +9881,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9939,7 +9924,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9953,10 +9938,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46012</v>
+        <v>46090</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9969,7 +9954,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10012,7 +9997,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10026,10 +10011,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45509</v>
+        <v>46002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10042,7 +10027,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10085,7 +10070,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10099,10 +10084,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46034</v>
+        <v>46002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10115,7 +10100,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10158,7 +10143,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10172,10 +10157,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46034</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10188,7 +10173,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10231,7 +10216,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10245,10 +10230,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45436</v>
+        <v>44999</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10261,7 +10246,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10304,7 +10289,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10318,10 +10303,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45947</v>
+        <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10334,7 +10319,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10377,7 +10362,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10391,10 +10376,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46037</v>
+        <v>45629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10407,7 +10392,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10450,7 +10435,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10464,10 +10449,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46174</v>
+        <v>46013</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10480,7 +10465,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10523,7 +10508,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10537,10 +10522,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46174</v>
+        <v>46012</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10553,7 +10538,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10596,7 +10581,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10610,10 +10595,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45548</v>
+        <v>46012</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10626,7 +10611,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10669,7 +10654,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10683,10 +10668,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45679</v>
+        <v>46012</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10699,7 +10684,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10742,7 +10727,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10756,10 +10741,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46059</v>
+        <v>44778</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10772,7 +10757,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10815,7 +10800,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10829,10 +10814,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46062</v>
+        <v>46094</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10845,7 +10830,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10888,7 +10873,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10902,10 +10887,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44965</v>
+        <v>46100</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10918,7 +10903,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10961,7 +10946,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10975,10 +10960,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46070</v>
+        <v>45679</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10991,7 +10976,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11034,7 +11019,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11048,10 +11033,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46070</v>
+        <v>46106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11063,8 +11048,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11107,7 +11097,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11121,10 +11111,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46072</v>
+        <v>45162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11136,13 +11126,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11185,7 +11170,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11199,10 +11184,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45513</v>
+        <v>45111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11215,7 +11200,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11258,7 +11243,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11272,10 +11257,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45237</v>
+        <v>46108</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11287,8 +11272,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11331,7 +11321,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11345,10 +11335,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45335</v>
+        <v>46108</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11361,7 +11351,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11404,7 +11394,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11418,10 +11408,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44978</v>
+        <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11433,8 +11423,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11477,7 +11472,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11491,10 +11486,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45170</v>
+        <v>45702</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11502,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11550,7 +11545,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11564,10 +11559,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45281</v>
+        <v>44978</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11575,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11623,7 +11618,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11637,10 +11632,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44999</v>
+        <v>45573</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11648,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11696,7 +11691,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11710,10 +11705,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45720</v>
+        <v>45705</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11721,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11769,7 +11764,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11783,10 +11778,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45111</v>
+        <v>45337</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11799,7 +11794,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11842,7 +11837,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11856,10 +11851,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45573</v>
+        <v>45625</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11872,7 +11867,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11915,7 +11910,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11929,10 +11924,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45281</v>
+        <v>45705</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11945,7 +11940,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11988,7 +11983,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12002,10 +11997,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45001</v>
+        <v>45789</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12018,7 +12013,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12061,7 +12056,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12075,10 +12070,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45111</v>
+        <v>45398</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12091,7 +12086,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12134,7 +12129,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12144,14 +12139,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44778</v>
+        <v>45369</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12164,7 +12159,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12207,7 +12202,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12217,14 +12212,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46245</v>
+        <v>45337</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12237,7 +12232,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12280,7 +12275,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12294,10 +12289,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45146</v>
+        <v>45075</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12310,7 +12305,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12353,7 +12348,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12367,10 +12362,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45530</v>
+        <v>45548</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12383,7 +12378,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12426,7 +12421,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12440,10 +12435,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46247</v>
+        <v>45821</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12455,13 +12450,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12504,7 +12494,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12518,10 +12508,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45146</v>
+        <v>45559</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12534,7 +12524,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12577,7 +12567,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12591,10 +12581,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45365</v>
+        <v>44893</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12607,7 +12597,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12650,7 +12640,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12664,10 +12654,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45365</v>
+        <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12680,7 +12670,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12723,7 +12713,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12737,10 +12727,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45075</v>
+        <v>45679</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12753,7 +12743,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12796,7 +12786,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12810,10 +12800,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45398</v>
+        <v>45509</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12826,7 +12816,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12869,7 +12859,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12883,10 +12873,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45625</v>
+        <v>46174</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12899,7 +12889,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12942,7 +12932,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12956,10 +12946,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45625</v>
+        <v>46174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12972,7 +12962,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13015,7 +13005,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13029,10 +13019,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45337</v>
+        <v>45763</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,7 +13035,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13088,7 +13078,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13102,10 +13092,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44580</v>
+        <v>44880</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13118,7 +13108,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13161,7 +13151,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13175,10 +13165,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46252</v>
+        <v>45296</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13190,13 +13180,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13239,7 +13224,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13253,10 +13238,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45170</v>
+        <v>45530</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13269,7 +13254,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13312,7 +13297,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13326,10 +13311,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45146</v>
+        <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13342,7 +13327,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13385,7 +13370,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13399,10 +13384,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46258</v>
+        <v>45436</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13414,13 +13399,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13463,7 +13443,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13477,10 +13457,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46258</v>
+        <v>45393</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13492,8 +13472,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>4.1</v>
+        <v>7.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13536,7 +13521,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13550,10 +13535,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46259</v>
+        <v>45720</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13566,7 +13551,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13609,7 +13594,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13623,10 +13608,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45257</v>
+        <v>45237</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13639,7 +13624,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13682,7 +13667,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13692,14 +13677,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45702</v>
+        <v>46245</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13712,7 +13697,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13755,7 +13740,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13769,10 +13754,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45252</v>
+        <v>46247</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13784,8 +13769,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13828,7 +13818,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13838,14 +13828,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45369</v>
+        <v>45714</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13858,7 +13848,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13901,7 +13891,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13915,10 +13905,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45763</v>
+        <v>45001</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13931,7 +13921,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13974,7 +13964,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13988,10 +13978,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45471</v>
+        <v>45594</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14004,7 +13994,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14047,7 +14037,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14061,10 +14051,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44832</v>
+        <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14077,7 +14067,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14120,7 +14110,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14134,10 +14124,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44965</v>
+        <v>46252</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14149,8 +14139,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14193,7 +14188,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14207,10 +14202,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45258</v>
+        <v>44861</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14223,7 +14218,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14266,7 +14261,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14280,10 +14275,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45260</v>
+        <v>44977</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14296,7 +14291,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14339,7 +14334,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14353,10 +14348,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45321</v>
+        <v>44977</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14369,7 +14364,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14412,7 +14407,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14426,10 +14421,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45097</v>
+        <v>45170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14442,7 +14437,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14485,7 +14480,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14499,10 +14494,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45621</v>
+        <v>46258</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14514,8 +14509,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14558,7 +14558,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14572,10 +14572,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45575</v>
+        <v>45513</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14631,7 +14631,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14645,10 +14645,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45705</v>
+        <v>45146</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14704,7 +14704,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45002</v>
+        <v>45146</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14777,7 +14777,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14791,10 +14791,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46275</v>
+        <v>45471</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14864,10 +14864,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45393</v>
+        <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14879,13 +14879,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14928,7 +14923,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14942,10 +14937,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45713</v>
+        <v>46258</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14958,7 +14953,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15001,7 +14996,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15015,10 +15010,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45720</v>
+        <v>46259</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15031,7 +15026,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15074,7 +15069,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15088,10 +15083,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45728</v>
+        <v>45567</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15104,7 +15099,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15147,7 +15142,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15161,10 +15156,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45721</v>
+        <v>45155</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15177,7 +15172,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>11.8</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15220,7 +15215,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15234,10 +15229,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45737</v>
+        <v>44879</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15293,7 +15288,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15307,10 +15302,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45533</v>
+        <v>45448</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15323,7 +15318,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15366,7 +15361,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15380,10 +15375,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45735</v>
+        <v>45146</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15396,7 +15391,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15439,7 +15434,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15453,10 +15448,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44897</v>
+        <v>45393</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15468,8 +15463,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15512,7 +15512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15526,10 +15526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45555</v>
+        <v>45170</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15585,7 +15585,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15599,10 +15599,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45695</v>
+        <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15658,7 +15658,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45567</v>
+        <v>45575</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45812</v>
+        <v>44746</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45820</v>
+        <v>45569</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15891,10 +15891,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45820</v>
+        <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45820</v>
+        <v>45436</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45821</v>
+        <v>45720</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45825</v>
+        <v>45721</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.6</v>
+        <v>11.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45728</v>
+        <v>45713</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16315,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45744</v>
+        <v>45533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45869</v>
+        <v>45735</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45729</v>
+        <v>45737</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45624</v>
+        <v>45555</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8924-2022</t>
+          <t>A 37767-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44614</v>
+        <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,19 +958,14 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -979,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -988,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1000,267 +995,272 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Pärluggla
+Sotlav
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 33243-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Silversmygare
+Kopparödla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 8924-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44614</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Åkergroda
 Vanlig groda
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 37767-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Pärluggla
-Sotlav
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33243-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Silversmygare
-Kopparödla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45821</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25554-2023</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45082</v>
+        <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,17 +1929,22 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1954,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,155 +1968,150 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51196-2021</t>
+          <t>A 46431-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44460</v>
+        <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46431-2022</t>
+          <t>A 51196-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44846</v>
+        <v>44460</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44519</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44496</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44580</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44735</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44746</v>
+        <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3280,8 +3280,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3324,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44538</v>
+        <v>44746</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3353,13 +3358,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>44652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44795</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44861</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45625</v>
+        <v>44893</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45335</v>
+        <v>45393</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3947,8 +3947,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3996,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4001,14 +4006,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44797</v>
+        <v>45317</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4026,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4069,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4074,14 +4079,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45280</v>
+        <v>44797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4099,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45247</v>
+        <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4172,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4215,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45002</v>
+        <v>45597</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4288,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45097</v>
+        <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4361,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44580</v>
+        <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4391,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4434,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45727</v>
+        <v>44879</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4464,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45636</v>
+        <v>45280</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4537,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4580,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4594,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45629</v>
+        <v>45272</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4610,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4653,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45695</v>
+        <v>45820</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4683,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4721,7 +4726,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45567</v>
+        <v>45820</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4756,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44746</v>
+        <v>45820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4867,7 +4872,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44897</v>
+        <v>45821</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45597</v>
+        <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45260</v>
+        <v>44614</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5042,8 +5047,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5096,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5100,10 +5110,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45258</v>
+        <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5126,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5169,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5183,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44738</v>
+        <v>45825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5199,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5242,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5246,10 +5256,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45812</v>
+        <v>46072</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5261,8 +5271,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5320,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5334,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45273</v>
+        <v>45247</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5350,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5393,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5407,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45790</v>
+        <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5423,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5466,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5480,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45821</v>
+        <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5496,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5539,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5553,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45820</v>
+        <v>45597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5554,7 +5569,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5612,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5626,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45820</v>
+        <v>45559</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5642,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5685,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5699,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46034</v>
+        <v>46085</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5715,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5758,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5753,14 +5768,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46034</v>
+        <v>46084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5772,8 +5787,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5836,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5850,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45820</v>
+        <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5866,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5909,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5899,14 +5919,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45411</v>
+        <v>46086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5939,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>8.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5982,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5996,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45825</v>
+        <v>46086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5992,7 +6012,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6035,7 +6055,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6069,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44832</v>
+        <v>46087</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6064,8 +6084,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6133,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6122,10 +6147,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45917</v>
+        <v>45569</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6163,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6206,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6220,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45917</v>
+        <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6254,7 +6279,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6293,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45597</v>
+        <v>46094</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6309,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6352,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6366,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44953</v>
+        <v>45728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6357,7 +6382,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6425,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6410,14 +6435,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46037</v>
+        <v>45411</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6430,7 +6455,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6490,7 +6515,7 @@
         <v>45727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6546,7 +6571,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6560,10 +6585,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45728</v>
+        <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6576,7 +6601,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6644,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6658,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45253</v>
+        <v>45273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6674,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6717,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6731,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45146</v>
+        <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6747,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6790,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6775,14 +6800,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45930</v>
+        <v>46106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6794,8 +6819,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6868,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6852,10 +6882,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45931</v>
+        <v>45567</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6867,13 +6897,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6916,7 +6941,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6930,10 +6955,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45869</v>
+        <v>46108</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6945,8 +6970,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6989,7 +7019,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7003,10 +7033,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45624</v>
+        <v>46108</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7019,7 +7049,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7062,7 +7092,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7076,10 +7106,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45729</v>
+        <v>45744</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7092,7 +7122,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7135,7 +7165,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7149,10 +7179,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45744</v>
+        <v>45146</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7165,7 +7195,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7208,7 +7238,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7222,10 +7252,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45881</v>
+        <v>45869</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7238,7 +7268,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7281,7 +7311,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7295,10 +7325,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45881</v>
+        <v>45729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7311,7 +7341,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7354,7 +7384,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7368,10 +7398,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45947</v>
+        <v>45790</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7384,7 +7414,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7427,7 +7457,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7441,10 +7471,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45639</v>
+        <v>45624</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7457,7 +7487,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7500,7 +7530,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7514,10 +7544,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45947</v>
+        <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7573,7 +7603,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7587,10 +7617,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45946</v>
+        <v>45162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7603,7 +7633,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7646,7 +7676,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7660,10 +7690,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45272</v>
+        <v>45881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7676,7 +7706,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7719,7 +7749,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7733,10 +7763,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45257</v>
+        <v>45639</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7749,7 +7779,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7792,7 +7822,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7806,10 +7836,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45281</v>
+        <v>45881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7822,7 +7852,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7865,7 +7895,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7879,10 +7909,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46059</v>
+        <v>45636</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7895,7 +7925,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7938,7 +7968,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7952,10 +7982,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44847</v>
+        <v>45679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7968,7 +7998,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8011,7 +8041,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8025,10 +8055,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46062</v>
+        <v>45035</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8041,7 +8071,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8084,7 +8114,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8098,10 +8128,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45317</v>
+        <v>45727</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8114,7 +8144,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8157,7 +8187,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8171,10 +8201,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45365</v>
+        <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8187,7 +8217,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8230,7 +8260,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8244,10 +8274,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44965</v>
+        <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8260,7 +8290,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8303,7 +8333,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8317,10 +8347,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44965</v>
+        <v>45917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8333,7 +8363,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8376,7 +8406,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8390,10 +8420,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44861</v>
+        <v>45337</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8406,7 +8436,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8449,7 +8479,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8463,10 +8493,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46070</v>
+        <v>45509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8479,7 +8509,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8522,7 +8552,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8536,10 +8566,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46070</v>
+        <v>45789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8552,7 +8582,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8595,7 +8625,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8609,10 +8639,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46072</v>
+        <v>45625</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8624,13 +8654,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8673,7 +8698,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8687,10 +8712,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44819</v>
+        <v>45436</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8703,7 +8728,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8746,7 +8771,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8756,14 +8781,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45252</v>
+        <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8776,7 +8801,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8819,7 +8844,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8833,10 +8858,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45251</v>
+        <v>45931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8848,8 +8873,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8892,7 +8922,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8906,10 +8936,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45253</v>
+        <v>45548</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8922,7 +8952,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8965,7 +8995,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8975,14 +9005,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45299</v>
+        <v>45679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8995,7 +9025,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9038,7 +9068,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9048,14 +9078,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46084</v>
+        <v>45821</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9067,13 +9097,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9116,7 +9141,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9130,10 +9155,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45321</v>
+        <v>44965</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9146,7 +9171,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9189,7 +9214,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9203,10 +9228,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46086</v>
+        <v>45335</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9219,7 +9244,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9262,7 +9287,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9276,10 +9301,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46086</v>
+        <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9292,7 +9317,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9335,7 +9360,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9349,10 +9374,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46085</v>
+        <v>45170</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9365,7 +9390,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9408,7 +9433,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9422,10 +9447,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46085</v>
+        <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9438,7 +9463,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9481,7 +9506,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9495,10 +9520,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45365</v>
+        <v>45281</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9511,7 +9536,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9554,7 +9579,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9568,10 +9593,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46000</v>
+        <v>45111</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9609,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9627,7 +9652,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9641,10 +9666,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45035</v>
+        <v>45947</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9682,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9700,7 +9725,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9714,10 +9739,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44977</v>
+        <v>46174</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9730,7 +9755,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9773,7 +9798,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9787,10 +9812,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46087</v>
+        <v>46174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9802,13 +9827,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9851,7 +9871,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9865,10 +9885,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45111</v>
+        <v>44778</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9881,7 +9901,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9924,7 +9944,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9938,10 +9958,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46090</v>
+        <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9954,7 +9974,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9997,7 +10017,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10011,10 +10031,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46002</v>
+        <v>45146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10027,7 +10047,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10070,7 +10090,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10084,10 +10104,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>45530</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10100,7 +10120,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10143,7 +10163,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10157,10 +10177,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10173,7 +10193,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10216,7 +10236,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10230,10 +10250,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44999</v>
+        <v>45075</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10246,7 +10266,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10289,7 +10309,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10303,10 +10323,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44978</v>
+        <v>45398</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10319,7 +10339,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10362,7 +10382,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10376,10 +10396,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10392,7 +10412,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10435,7 +10455,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10449,10 +10469,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46013</v>
+        <v>45625</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10465,7 +10485,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10508,7 +10528,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10522,10 +10542,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46012</v>
+        <v>45337</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10538,7 +10558,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10581,7 +10601,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10595,10 +10615,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46012</v>
+        <v>44580</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10611,7 +10631,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10654,7 +10674,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10668,10 +10688,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46012</v>
+        <v>45720</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10684,7 +10704,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10727,7 +10747,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10741,10 +10761,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44778</v>
+        <v>45170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10757,7 +10777,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10800,7 +10820,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10810,14 +10830,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46094</v>
+        <v>46245</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10830,7 +10850,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10873,7 +10893,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10887,10 +10907,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46100</v>
+        <v>46247</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10902,8 +10922,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10946,7 +10971,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10960,10 +10985,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45679</v>
+        <v>45702</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10976,7 +11001,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11019,7 +11044,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11033,10 +11058,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46106</v>
+        <v>45763</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11046,11 +11071,6 @@
       <c r="G137" t="inlineStr">
         <is>
           <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -11097,7 +11117,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11111,10 +11131,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45162</v>
+        <v>45253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11127,7 +11147,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11170,7 +11190,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11184,10 +11204,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45111</v>
+        <v>46252</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11199,8 +11219,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11243,7 +11268,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11257,10 +11282,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46108</v>
+        <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11272,13 +11297,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11321,7 +11341,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11335,10 +11355,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46108</v>
+        <v>44746</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11351,7 +11371,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11394,7 +11414,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11408,10 +11428,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44614</v>
+        <v>45714</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11421,11 +11441,6 @@
       <c r="G142" t="inlineStr">
         <is>
           <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -11472,7 +11487,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11486,10 +11501,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45702</v>
+        <v>46258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11501,8 +11516,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11545,7 +11565,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11559,10 +11579,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44978</v>
+        <v>44738</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11575,7 +11595,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11618,7 +11638,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11632,10 +11652,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45573</v>
+        <v>45728</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11691,7 +11711,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11701,14 +11721,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45705</v>
+        <v>45299</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11721,7 +11741,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11764,7 +11784,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11778,10 +11798,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45337</v>
+        <v>46258</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11794,7 +11814,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11837,7 +11857,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11851,10 +11871,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45625</v>
+        <v>46259</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11867,7 +11887,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11910,7 +11930,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11924,10 +11944,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45705</v>
+        <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11940,7 +11960,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11983,7 +12003,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11997,10 +12017,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45789</v>
+        <v>44861</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12013,7 +12033,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12056,7 +12076,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12070,10 +12090,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45398</v>
+        <v>46002</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12086,7 +12106,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12129,7 +12149,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12139,14 +12159,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45369</v>
+        <v>46002</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12159,7 +12179,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12202,7 +12222,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12216,10 +12236,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45337</v>
+        <v>46002</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,7 +12252,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12275,7 +12295,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12289,10 +12309,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45075</v>
+        <v>45531</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12305,7 +12325,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12368,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12362,10 +12382,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45548</v>
+        <v>45296</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12378,7 +12398,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12421,7 +12441,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12435,10 +12455,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45821</v>
+        <v>44847</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12451,7 +12471,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12494,7 +12514,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12508,10 +12528,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45559</v>
+        <v>45448</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12524,7 +12544,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12567,7 +12587,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12581,10 +12601,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44893</v>
+        <v>46013</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12597,7 +12617,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12640,7 +12660,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12654,10 +12674,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45947</v>
+        <v>46012</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12670,7 +12690,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12713,7 +12733,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12727,10 +12747,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45679</v>
+        <v>46012</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,7 +12763,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12786,7 +12806,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12800,10 +12820,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45509</v>
+        <v>46012</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12816,7 +12836,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12859,7 +12879,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12873,10 +12893,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46174</v>
+        <v>44953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12889,7 +12909,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12932,7 +12952,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12946,10 +12966,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46174</v>
+        <v>46275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12962,7 +12982,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13005,7 +13025,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13019,10 +13039,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45763</v>
+        <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13035,7 +13055,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13078,7 +13098,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13092,10 +13112,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44880</v>
+        <v>45155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13108,7 +13128,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13151,7 +13171,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13165,10 +13185,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45296</v>
+        <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13181,7 +13201,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13224,7 +13244,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13238,10 +13258,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45530</v>
+        <v>46034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13254,7 +13274,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13297,7 +13317,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13311,10 +13331,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45531</v>
+        <v>45705</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13327,7 +13347,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13370,7 +13390,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13384,10 +13404,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45436</v>
+        <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13400,7 +13420,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13443,7 +13463,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13457,10 +13477,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45393</v>
+        <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13472,13 +13492,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13521,7 +13536,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13535,10 +13550,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45720</v>
+        <v>44746</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13551,7 +13566,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13594,7 +13609,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13608,10 +13623,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45237</v>
+        <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13624,7 +13639,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13667,7 +13682,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13677,14 +13692,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46245</v>
+        <v>45513</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13697,7 +13712,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13740,7 +13755,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13754,10 +13769,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46247</v>
+        <v>45237</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13769,13 +13784,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13818,7 +13828,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13832,10 +13842,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45714</v>
+        <v>44978</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13848,7 +13858,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13891,7 +13901,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13905,10 +13915,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45001</v>
+        <v>44999</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13921,7 +13931,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13964,7 +13974,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13978,10 +13988,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45594</v>
+        <v>45573</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13994,7 +14004,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14037,7 +14047,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14051,10 +14061,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45281</v>
+        <v>46059</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14067,7 +14077,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14110,7 +14120,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14124,10 +14134,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46252</v>
+        <v>45281</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14139,13 +14149,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14188,7 +14193,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14202,10 +14207,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44861</v>
+        <v>46062</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14218,7 +14223,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14261,7 +14266,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14275,10 +14280,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44977</v>
+        <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14291,7 +14296,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14334,7 +14339,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14348,10 +14353,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44977</v>
+        <v>45111</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14364,7 +14369,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14407,7 +14412,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14421,10 +14426,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45170</v>
+        <v>45365</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14437,7 +14442,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14480,7 +14485,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14494,10 +14499,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46258</v>
+        <v>45365</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14509,13 +14514,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14558,7 +14558,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14572,10 +14572,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45513</v>
+        <v>45146</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>10.2</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14631,7 +14631,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14645,10 +14645,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45146</v>
+        <v>45257</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14704,7 +14704,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45146</v>
+        <v>45252</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14777,7 +14777,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14787,14 +14787,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45471</v>
+        <v>45369</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14864,10 +14864,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45621</v>
+        <v>45471</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14937,10 +14937,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46258</v>
+        <v>44832</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14996,7 +14996,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15010,10 +15010,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46259</v>
+        <v>44965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15069,7 +15069,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15083,10 +15083,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45567</v>
+        <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15142,7 +15142,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15156,10 +15156,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45155</v>
+        <v>45260</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15215,7 +15215,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44879</v>
+        <v>45321</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15288,7 +15288,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15302,10 +15302,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45448</v>
+        <v>45097</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15361,7 +15361,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45146</v>
+        <v>45621</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15448,10 +15448,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45393</v>
+        <v>45575</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15463,13 +15463,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15512,7 +15507,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15526,10 +15521,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45170</v>
+        <v>45705</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15542,7 +15537,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15585,7 +15580,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15599,10 +15594,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45728</v>
+        <v>45002</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15615,7 +15610,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15658,7 +15653,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15672,10 +15667,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45575</v>
+        <v>45393</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15687,8 +15682,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44746</v>
+        <v>45713</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45569</v>
+        <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15891,10 +15891,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46275</v>
+        <v>45728</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45436</v>
+        <v>45721</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45720</v>
+        <v>45737</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45721</v>
+        <v>45533</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>11.8</v>
+        <v>4.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45713</v>
+        <v>45735</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45728</v>
+        <v>44897</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45533</v>
+        <v>45555</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45735</v>
+        <v>45695</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45737</v>
+        <v>45567</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45555</v>
+        <v>45812</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 8924-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45159</v>
+        <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,14 +958,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>21.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -974,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -983,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -995,272 +1000,267 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 33243-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>46246</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>12.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Silversmygare
 Kopparödla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 8924-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44614</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45821</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34738-2026</t>
+          <t>A 25554-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46258</v>
+        <v>45082</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,23 +1929,18 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1959,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1968,150 +1963,155 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 34738-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 25554-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45082</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44460</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44519</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44496</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44580</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44735</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44538</v>
+        <v>44746</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3280,13 +3280,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3329,7 +3324,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44746</v>
+        <v>44538</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3358,8 +3353,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>44652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44795</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44861</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44893</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45393</v>
+        <v>45335</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3947,13 +3947,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3996,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4006,14 +4001,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45317</v>
+        <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4026,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4069,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4079,14 +4074,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44797</v>
+        <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4099,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4142,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44880</v>
+        <v>45280</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4172,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4215,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45597</v>
+        <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4288,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45253</v>
+        <v>45097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4318,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4361,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44819</v>
+        <v>44580</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4391,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4434,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44879</v>
+        <v>45727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4464,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45280</v>
+        <v>45636</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4537,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4594,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45272</v>
+        <v>45629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4667,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45820</v>
+        <v>44746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4726,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45820</v>
+        <v>45597</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4756,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4799,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45820</v>
+        <v>45258</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4829,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45821</v>
+        <v>44738</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4902,7 +4897,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46070</v>
+        <v>45273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4975,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5018,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44614</v>
+        <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5047,13 +5042,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5096,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5106,14 +5096,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46070</v>
+        <v>45411</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5126,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5169,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5183,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45825</v>
+        <v>44832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5199,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5242,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5256,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46072</v>
+        <v>45597</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5271,13 +5261,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5320,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5334,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45247</v>
+        <v>44953</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5350,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5393,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5407,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45594</v>
+        <v>45253</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5423,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5466,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5480,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45436</v>
+        <v>45146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5496,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5539,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5553,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45597</v>
+        <v>45257</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5569,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5612,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5626,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45559</v>
+        <v>45272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5642,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5685,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5699,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46085</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5715,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5758,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5768,14 +5753,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46084</v>
+        <v>45317</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,13 +5772,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5836,7 +5816,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5850,10 +5830,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46085</v>
+        <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5866,7 +5846,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5909,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5923,10 +5903,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46086</v>
+        <v>45365</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5939,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.1</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5982,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5996,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46086</v>
+        <v>44965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6012,7 +5992,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6055,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6069,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46087</v>
+        <v>44965</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6084,13 +6064,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6133,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6147,10 +6122,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45569</v>
+        <v>44861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6163,7 +6138,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6206,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6220,10 +6195,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46090</v>
+        <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6236,7 +6211,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6279,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6293,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46094</v>
+        <v>44819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6309,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6352,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6366,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45728</v>
+        <v>45252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6382,7 +6357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6425,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6435,14 +6410,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45411</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6455,7 +6430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6498,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6512,10 +6487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45727</v>
+        <v>45253</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6528,7 +6503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6571,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6581,14 +6556,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46100</v>
+        <v>45299</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6601,7 +6576,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6644,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6658,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45273</v>
+        <v>45321</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6674,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6717,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6731,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>45790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6747,7 +6722,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6790,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6804,10 +6779,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46106</v>
+        <v>45365</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6819,13 +6794,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6868,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6882,10 +6852,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45567</v>
+        <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6898,7 +6868,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6941,7 +6911,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6955,10 +6925,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46108</v>
+        <v>45035</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6970,13 +6940,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7019,7 +6984,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7033,10 +6998,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46108</v>
+        <v>44977</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7049,7 +7014,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7092,7 +7057,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7106,10 +7071,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45744</v>
+        <v>45111</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7122,7 +7087,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>9.4</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7165,7 +7130,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7179,10 +7144,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45146</v>
+        <v>44999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7195,7 +7160,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7238,7 +7203,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7252,10 +7217,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45869</v>
+        <v>44978</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7268,7 +7233,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7311,7 +7276,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7325,10 +7290,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45729</v>
+        <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7341,7 +7306,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7384,7 +7349,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7398,10 +7363,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45790</v>
+        <v>45917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7414,7 +7379,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7457,7 +7422,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7471,10 +7436,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45624</v>
+        <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7487,7 +7452,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7530,7 +7495,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7544,10 +7509,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45629</v>
+        <v>44778</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7603,7 +7568,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7617,10 +7582,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45162</v>
+        <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7633,7 +7598,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7676,7 +7641,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7686,14 +7651,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45881</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7706,7 +7671,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7749,7 +7714,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7763,10 +7728,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45639</v>
+        <v>45162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7779,7 +7744,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7822,7 +7787,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7836,10 +7801,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45881</v>
+        <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7851,8 +7816,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7895,7 +7865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7909,10 +7879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45636</v>
+        <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7925,7 +7895,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7968,7 +7938,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7982,10 +7952,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45679</v>
+        <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7997,8 +7967,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8041,7 +8016,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8055,10 +8030,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45035</v>
+        <v>45702</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8071,7 +8046,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8114,7 +8089,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8128,10 +8103,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45727</v>
+        <v>45947</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8144,7 +8119,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8187,7 +8162,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8201,10 +8176,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45629</v>
+        <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8217,7 +8192,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8260,7 +8235,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8274,10 +8249,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45917</v>
+        <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8290,7 +8265,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8333,7 +8308,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8347,10 +8322,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45917</v>
+        <v>44978</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8363,7 +8338,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8406,7 +8381,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8420,10 +8395,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45337</v>
+        <v>45573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8436,7 +8411,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8479,7 +8454,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8493,10 +8468,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45509</v>
+        <v>45705</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8509,7 +8484,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8552,7 +8527,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8566,10 +8541,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45789</v>
+        <v>45337</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8582,7 +8557,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8625,7 +8600,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8639,10 +8614,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45625</v>
+        <v>45821</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8655,7 +8630,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8698,7 +8673,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8712,10 +8687,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45436</v>
+        <v>45705</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8728,7 +8703,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8771,7 +8746,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8781,14 +8756,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45930</v>
+        <v>45398</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8801,7 +8776,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8844,7 +8819,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8854,14 +8829,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45931</v>
+        <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8873,13 +8848,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8922,7 +8892,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8936,10 +8906,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45548</v>
+        <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8952,7 +8922,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8995,7 +8965,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9009,10 +8979,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45679</v>
+        <v>45337</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9025,7 +8995,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9068,7 +9038,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9082,10 +9052,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45821</v>
+        <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9098,7 +9068,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9141,7 +9111,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9155,10 +9125,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44965</v>
+        <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9171,7 +9141,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9214,7 +9184,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9228,10 +9198,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45335</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9244,7 +9214,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9287,7 +9257,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9301,10 +9271,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45947</v>
+        <v>45075</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9317,7 +9287,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9360,7 +9330,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9374,10 +9344,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45170</v>
+        <v>45947</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9390,7 +9360,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9433,7 +9403,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9447,10 +9417,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45946</v>
+        <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9463,7 +9433,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9506,7 +9476,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9520,10 +9490,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45281</v>
+        <v>46012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9536,7 +9506,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9579,7 +9549,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9593,10 +9563,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45111</v>
+        <v>46012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9609,7 +9579,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9652,7 +9622,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9666,10 +9636,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45947</v>
+        <v>46012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9682,7 +9652,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9725,7 +9695,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9739,10 +9709,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46174</v>
+        <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9755,7 +9725,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9798,7 +9768,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9812,10 +9782,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46174</v>
+        <v>45559</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9828,7 +9798,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9871,7 +9841,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9885,10 +9855,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44778</v>
+        <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9901,7 +9871,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9944,7 +9914,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9958,10 +9928,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45947</v>
+        <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9974,7 +9944,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10017,7 +9987,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10031,10 +10001,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45146</v>
+        <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10047,7 +10017,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10090,7 +10060,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10104,10 +10074,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45530</v>
+        <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10120,7 +10090,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10163,7 +10133,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10177,10 +10147,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45146</v>
+        <v>46174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10193,7 +10163,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10236,7 +10206,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10250,10 +10220,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45075</v>
+        <v>46037</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10266,7 +10236,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10309,7 +10279,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10323,10 +10293,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45398</v>
+        <v>45679</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10339,7 +10309,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10382,7 +10352,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10396,10 +10366,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45625</v>
+        <v>45509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10412,7 +10382,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10455,7 +10425,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10469,10 +10439,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45625</v>
+        <v>45763</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10485,7 +10455,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10528,7 +10498,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10542,10 +10512,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45337</v>
+        <v>46059</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10558,7 +10528,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10601,7 +10571,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10615,10 +10585,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44580</v>
+        <v>46062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10631,7 +10601,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10674,7 +10644,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10688,10 +10658,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45720</v>
+        <v>46070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10704,7 +10674,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10747,7 +10717,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10761,10 +10731,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45170</v>
+        <v>46070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10777,7 +10747,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10820,7 +10790,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10830,14 +10800,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46245</v>
+        <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10849,8 +10819,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10893,7 +10868,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10907,10 +10882,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46247</v>
+        <v>44880</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10922,13 +10897,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10971,7 +10941,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10985,10 +10955,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45702</v>
+        <v>45296</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11001,7 +10971,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11044,7 +11014,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11054,14 +11024,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45763</v>
+        <v>46084</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11073,8 +11043,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11117,7 +11092,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11131,10 +11106,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45253</v>
+        <v>46086</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11147,7 +11122,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11190,7 +11165,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11204,10 +11179,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46252</v>
+        <v>46086</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11219,13 +11194,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11268,7 +11238,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11282,10 +11252,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45251</v>
+        <v>46085</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11298,7 +11268,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11341,7 +11311,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11355,10 +11325,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44746</v>
+        <v>46085</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11371,7 +11341,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11414,7 +11384,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11428,10 +11398,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45714</v>
+        <v>45530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11444,7 +11414,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11487,7 +11457,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11501,10 +11471,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46258</v>
+        <v>45531</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11516,13 +11486,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11565,7 +11530,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11579,10 +11544,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44738</v>
+        <v>46087</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11594,8 +11559,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11638,7 +11608,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11652,10 +11622,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45728</v>
+        <v>46090</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11668,7 +11638,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11711,7 +11681,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11721,14 +11691,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45299</v>
+        <v>46094</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11741,7 +11711,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11784,7 +11754,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11798,10 +11768,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46258</v>
+        <v>45436</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11814,7 +11784,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11857,7 +11827,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11871,10 +11841,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46259</v>
+        <v>46100</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11887,7 +11857,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11930,7 +11900,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11944,10 +11914,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46000</v>
+        <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11959,8 +11929,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12003,7 +11978,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12017,10 +11992,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44861</v>
+        <v>45720</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12033,7 +12008,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12076,7 +12051,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12090,10 +12065,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46002</v>
+        <v>46108</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12105,8 +12080,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12149,7 +12129,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12163,10 +12143,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46002</v>
+        <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12178,8 +12158,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>7.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12222,7 +12207,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12236,10 +12221,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46002</v>
+        <v>46108</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12252,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12295,7 +12280,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12309,10 +12294,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45531</v>
+        <v>45237</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12325,7 +12310,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12368,7 +12353,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12382,10 +12367,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45296</v>
+        <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12398,7 +12383,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12441,7 +12426,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12455,10 +12440,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44847</v>
+        <v>45001</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12471,7 +12456,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12514,7 +12499,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12528,10 +12513,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45448</v>
+        <v>45594</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12544,7 +12529,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12587,7 +12572,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12601,10 +12586,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46013</v>
+        <v>45281</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12617,7 +12602,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12660,7 +12645,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12674,10 +12659,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46012</v>
+        <v>44861</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12690,7 +12675,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12733,7 +12718,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12743,14 +12728,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46012</v>
+        <v>46245</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12763,7 +12748,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12806,7 +12791,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12820,10 +12805,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46012</v>
+        <v>44977</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12836,7 +12821,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12879,7 +12864,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12893,10 +12878,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44953</v>
+        <v>44977</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12894,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12952,7 +12937,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12966,10 +12951,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46275</v>
+        <v>45170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12982,7 +12967,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13025,7 +13010,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13039,10 +13024,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44978</v>
+        <v>46247</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13054,8 +13039,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13098,7 +13088,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13112,10 +13102,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45155</v>
+        <v>45513</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13128,7 +13118,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13171,7 +13161,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13185,10 +13175,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46034</v>
+        <v>45146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13244,7 +13234,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13258,10 +13248,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46034</v>
+        <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13274,7 +13264,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13317,7 +13307,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13331,10 +13321,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45705</v>
+        <v>45471</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13347,7 +13337,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13390,7 +13380,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13404,10 +13394,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44977</v>
+        <v>45621</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13420,7 +13410,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13463,7 +13453,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13477,10 +13467,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44977</v>
+        <v>46252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13492,8 +13482,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13536,7 +13531,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13550,10 +13545,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44746</v>
+        <v>45567</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13566,7 +13561,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13609,7 +13604,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13623,10 +13618,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46037</v>
+        <v>45155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13639,7 +13634,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13682,7 +13677,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13696,10 +13691,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45513</v>
+        <v>44879</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13712,7 +13707,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13755,7 +13750,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13769,10 +13764,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45237</v>
+        <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13785,7 +13780,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13828,7 +13823,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13842,10 +13837,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44978</v>
+        <v>45146</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13858,7 +13853,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13901,7 +13896,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13915,10 +13910,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44999</v>
+        <v>45393</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13930,8 +13925,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13974,7 +13974,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13988,10 +13988,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45573</v>
+        <v>45170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14047,7 +14047,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14061,10 +14061,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46059</v>
+        <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14076,8 +14076,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14120,7 +14125,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14134,10 +14139,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45281</v>
+        <v>45728</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14150,7 +14155,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14193,7 +14198,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14207,10 +14212,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46062</v>
+        <v>45575</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14223,7 +14228,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14266,7 +14271,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14280,10 +14285,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45001</v>
+        <v>46258</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14296,7 +14301,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14339,7 +14344,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14353,10 +14358,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45111</v>
+        <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14369,7 +14374,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14412,7 +14417,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14426,10 +14431,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45365</v>
+        <v>44746</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14442,7 +14447,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14485,7 +14490,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14499,10 +14504,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45365</v>
+        <v>45569</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14515,7 +14520,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14558,7 +14563,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14572,10 +14577,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45146</v>
+        <v>45436</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14588,7 +14593,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14631,7 +14636,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14645,10 +14650,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45257</v>
+        <v>46275</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14661,7 +14666,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14704,7 +14709,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14718,10 +14723,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45252</v>
+        <v>45720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14734,7 +14739,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14777,7 +14782,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14787,14 +14792,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45369</v>
+        <v>45721</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14807,7 +14812,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>11.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14850,7 +14855,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14864,10 +14869,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45471</v>
+        <v>45713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14880,7 +14885,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14923,7 +14928,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14937,10 +14942,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44832</v>
+        <v>45728</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14953,7 +14958,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14996,7 +15001,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15010,10 +15015,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44965</v>
+        <v>45533</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15026,7 +15031,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15069,7 +15074,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15083,10 +15088,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45258</v>
+        <v>45735</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15099,7 +15104,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15142,7 +15147,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15156,10 +15161,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45260</v>
+        <v>45737</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15172,7 +15177,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15215,7 +15220,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15229,10 +15234,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45321</v>
+        <v>45555</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15245,7 +15250,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15288,7 +15293,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15302,10 +15307,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45097</v>
+        <v>45695</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15318,7 +15323,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15361,7 +15366,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15375,10 +15380,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45621</v>
+        <v>45567</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15391,7 +15396,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15434,7 +15439,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15448,10 +15453,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45575</v>
+        <v>44897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15507,7 +15512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15521,10 +15526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45705</v>
+        <v>45812</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15537,7 +15542,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15580,7 +15585,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15594,10 +15599,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45002</v>
+        <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15610,7 +15615,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15653,7 +15658,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15667,10 +15672,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45393</v>
+        <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15682,13 +15687,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45713</v>
+        <v>45820</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45720</v>
+        <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15891,10 +15891,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45728</v>
+        <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45721</v>
+        <v>45727</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>11.8</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45737</v>
+        <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45533</v>
+        <v>45869</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45735</v>
+        <v>45624</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44897</v>
+        <v>45729</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16315,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45555</v>
+        <v>45744</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45695</v>
+        <v>45881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45567</v>
+        <v>45881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45812</v>
+        <v>45639</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45159</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45821</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45082</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44460</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44686</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44519</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44496</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44580</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44466</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44735</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44883</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44746</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44538</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44795</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45335</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45280</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44580</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45727</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45636</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45597</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45258</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44738</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45411</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45597</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44953</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45253</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>45257</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45317</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45365</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44965</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45253</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45299</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45321</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45365</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45035</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44977</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45111</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>44999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44978</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44778</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>45702</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>45947</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44978</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45705</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45337</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45821</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45705</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45398</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45337</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45075</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45947</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>46012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>46012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>46012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45559</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>46174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>46037</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45679</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>45509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45763</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46059</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>46062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>46070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>46070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44880</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45296</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46084</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>46086</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>46086</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>46085</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>46085</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45531</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46087</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>46090</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>46094</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45436</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>46100</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45720</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>46108</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>46108</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45237</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45001</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45594</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45281</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44861</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>46245</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44977</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44977</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>46247</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45513</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>45146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>45471</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45621</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>46252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45567</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44879</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45146</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45393</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45728</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45575</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>46258</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44746</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45569</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45436</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>46275</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45721</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>45728</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45533</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45735</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>45737</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45555</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45695</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45567</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45812</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45820</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45727</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45869</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45624</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45729</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45744</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45639</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45159</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45821</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25554-2023</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45082</v>
+        <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,17 +1929,22 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1954,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,155 +1968,150 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51196-2021</t>
+          <t>A 18500-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44460</v>
+        <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18500-2022</t>
+          <t>A 66603-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44686</v>
+        <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 66603-2021</t>
+          <t>A 28167-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44519</v>
+        <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28167-2022</t>
+          <t>A 48636-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44746</v>
+        <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 48636-2022</t>
+          <t>A 60681-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44855</v>
+        <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60681-2021</t>
+          <t>A 2640-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44496</v>
+        <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2640-2022</t>
+          <t>A 52568-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,14 +2818,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44580</v>
+        <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52568-2021</t>
+          <t>A 52572-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2954,7 +2954,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52572-2021</t>
+          <t>A 26333-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44466</v>
+        <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26333-2022</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44735</v>
+        <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3110,14 +3110,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44883</v>
+        <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3129,8 +3129,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3173,7 +3178,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44614</v>
+        <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3202,13 +3207,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>9.9</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44746</v>
+        <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3280,8 +3280,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3324,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44538</v>
+        <v>44652</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3353,13 +3358,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44621</v>
+        <v>44525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44525</v>
+        <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3577,8 +3577,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3621,7 +3626,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3635,10 +3640,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44616</v>
+        <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3650,13 +3655,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44795</v>
+        <v>45625</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3789,7 +3789,7 @@
         <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45625</v>
+        <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3928,14 +3928,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45335</v>
+        <v>44797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4001,14 +4001,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44797</v>
+        <v>45280</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45280</v>
+        <v>45002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45002</v>
+        <v>45097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45097</v>
+        <v>44580</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44580</v>
+        <v>45727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45727</v>
+        <v>45636</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45629</v>
+        <v>44746</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44746</v>
+        <v>45260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
         <v>45597</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45258</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44738</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5023,14 +5023,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45260</v>
+        <v>45411</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5096,14 +5096,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45411</v>
+        <v>44832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44832</v>
+        <v>45597</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45597</v>
+        <v>44953</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44953</v>
+        <v>45253</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45253</v>
+        <v>45146</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45146</v>
+        <v>45624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45257</v>
+        <v>45729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45272</v>
+        <v>45744</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>9.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>45272</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45317</v>
+        <v>45257</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5816,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44847</v>
+        <v>45881</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45365</v>
+        <v>45881</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44965</v>
+        <v>45281</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6035,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44965</v>
+        <v>45639</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44861</v>
+        <v>44847</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45625</v>
+        <v>45317</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44819</v>
+        <v>45365</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45252</v>
+        <v>45790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45251</v>
+        <v>45625</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6473,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6487,10 +6487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45253</v>
+        <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45299</v>
+        <v>44965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45321</v>
+        <v>44861</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45790</v>
+        <v>45789</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45365</v>
+        <v>45917</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45789</v>
+        <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45035</v>
+        <v>44819</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44977</v>
+        <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45111</v>
+        <v>45251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7130,7 +7130,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44999</v>
+        <v>45253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7213,14 +7213,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44978</v>
+        <v>45299</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45629</v>
+        <v>45321</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45917</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45917</v>
+        <v>45931</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7451,8 +7451,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7495,7 +7500,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7509,10 +7514,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44778</v>
+        <v>45365</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7525,7 +7530,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7568,7 +7573,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7582,10 +7587,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45679</v>
+        <v>45035</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7598,7 +7603,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7641,7 +7646,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7651,14 +7656,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>44977</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7671,7 +7676,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7714,7 +7719,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45162</v>
+        <v>45111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7744,7 +7749,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7787,7 +7792,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7801,10 +7806,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45931</v>
+        <v>44999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7816,13 +7821,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7865,7 +7865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45111</v>
+        <v>45821</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44614</v>
+        <v>44978</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7967,13 +7967,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8016,7 +8011,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8030,10 +8025,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45702</v>
+        <v>45629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8046,7 +8041,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8089,7 +8084,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8103,10 +8098,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45947</v>
+        <v>44778</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8119,7 +8114,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8162,7 +8157,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8179,7 +8174,7 @@
         <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8192,7 +8187,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8235,7 +8230,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8249,10 +8244,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8265,7 +8260,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8308,7 +8303,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8322,10 +8317,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44978</v>
+        <v>45946</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8338,7 +8333,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8381,7 +8376,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8395,10 +8390,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45573</v>
+        <v>45679</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8411,7 +8406,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8454,7 +8449,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8468,10 +8463,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45705</v>
+        <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8527,7 +8522,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8541,10 +8536,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45337</v>
+        <v>45111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8557,7 +8552,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8600,7 +8595,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8614,10 +8609,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45821</v>
+        <v>44614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8629,8 +8624,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45705</v>
+        <v>45702</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45398</v>
+        <v>45947</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45369</v>
+        <v>44978</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46000</v>
+        <v>46174</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8965,7 +8965,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45337</v>
+        <v>46174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46002</v>
+        <v>45573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9111,7 +9111,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9201,7 +9201,7 @@
         <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45075</v>
+        <v>46002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45947</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46013</v>
+        <v>45705</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9476,7 +9476,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46012</v>
+        <v>45337</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9549,7 +9549,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9622,7 +9622,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9639,7 +9639,7 @@
         <v>46012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9695,7 +9695,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45548</v>
+        <v>46012</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9768,7 +9768,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45559</v>
+        <v>46012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9841,7 +9841,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46174</v>
+        <v>45705</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9931,7 +9931,7 @@
         <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44893</v>
+        <v>45398</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10133,7 +10133,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46174</v>
+        <v>46037</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10206,7 +10206,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10216,14 +10216,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46037</v>
+        <v>45369</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10293,10 +10293,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45679</v>
+        <v>46059</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10352,7 +10352,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45509</v>
+        <v>46062</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10425,7 +10425,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45763</v>
+        <v>45337</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10498,7 +10498,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46059</v>
+        <v>45720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10571,7 +10571,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46062</v>
+        <v>45075</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10661,7 +10661,7 @@
         <v>46070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>46070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44880</v>
+        <v>45548</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10941,7 +10941,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10951,14 +10951,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45296</v>
+        <v>46084</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10970,8 +10970,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11014,7 +11019,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11024,14 +11029,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11043,13 +11048,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11109,7 +11109,7 @@
         <v>46086</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11165,7 +11165,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11179,10 +11179,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11255,7 +11255,7 @@
         <v>46085</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11311,7 +11311,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11325,10 +11325,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11340,8 +11340,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11384,7 +11389,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11398,10 +11403,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45530</v>
+        <v>46090</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11414,7 +11419,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11457,7 +11462,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11471,10 +11476,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45531</v>
+        <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11487,7 +11492,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11530,7 +11535,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11544,10 +11549,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11559,13 +11564,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11608,7 +11608,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46090</v>
+        <v>44893</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>13.5</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11754,7 +11754,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45436</v>
+        <v>46106</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11783,8 +11783,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11827,7 +11832,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11841,10 +11846,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46100</v>
+        <v>46247</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11856,8 +11861,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11900,7 +11910,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11914,10 +11924,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11935,7 +11945,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11978,7 +11988,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11992,10 +12002,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45720</v>
+        <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12008,7 +12018,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12051,7 +12061,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12065,10 +12075,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46108</v>
+        <v>45679</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12080,13 +12090,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12129,7 +12134,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12143,10 +12148,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45393</v>
+        <v>45509</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12158,13 +12163,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46108</v>
+        <v>45763</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45237</v>
+        <v>44880</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45714</v>
+        <v>45296</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45001</v>
+        <v>46252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12455,8 +12455,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12499,7 +12504,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12513,10 +12518,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45594</v>
+        <v>45530</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12529,7 +12534,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12572,7 +12577,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12586,10 +12591,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45281</v>
+        <v>45531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12602,7 +12607,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12645,7 +12650,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12659,10 +12664,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44861</v>
+        <v>45436</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12675,7 +12680,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12718,7 +12723,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12728,14 +12733,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12747,8 +12752,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12791,7 +12801,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12805,10 +12815,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44977</v>
+        <v>45393</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12820,8 +12830,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12864,7 +12879,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12878,10 +12893,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44977</v>
+        <v>46258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12894,7 +12909,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12937,7 +12952,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12951,10 +12966,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45170</v>
+        <v>46259</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12967,7 +12982,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13010,7 +13025,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13024,10 +13039,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46247</v>
+        <v>45237</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13039,13 +13054,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13088,7 +13098,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13102,10 +13112,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45513</v>
+        <v>45714</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13118,7 +13128,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13161,7 +13171,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13175,10 +13185,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45146</v>
+        <v>45001</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13191,7 +13201,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13234,7 +13244,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13248,10 +13258,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45146</v>
+        <v>45594</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13264,7 +13274,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13307,7 +13317,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13321,10 +13331,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45471</v>
+        <v>45281</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13337,7 +13347,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13380,7 +13390,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13394,10 +13404,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45621</v>
+        <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13410,7 +13420,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13453,7 +13463,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13467,10 +13477,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46252</v>
+        <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13482,13 +13492,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13531,7 +13536,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13545,10 +13550,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45567</v>
+        <v>44977</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13561,7 +13566,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13604,7 +13609,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13618,10 +13623,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45155</v>
+        <v>45170</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13634,7 +13639,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13677,7 +13682,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13691,10 +13696,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44879</v>
+        <v>46275</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13707,7 +13712,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13750,7 +13755,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13764,10 +13769,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45448</v>
+        <v>45513</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13780,7 +13785,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13823,7 +13828,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13840,7 +13845,7 @@
         <v>45146</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13853,7 +13858,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13896,7 +13901,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13910,10 +13915,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45393</v>
+        <v>45146</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13925,13 +13930,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13974,7 +13974,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13988,10 +13988,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45170</v>
+        <v>45471</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14047,7 +14047,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14061,10 +14061,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46258</v>
+        <v>45621</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14076,13 +14076,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14125,7 +14120,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14139,10 +14134,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45728</v>
+        <v>45567</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14155,7 +14150,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14198,7 +14193,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14212,10 +14207,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45575</v>
+        <v>45155</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14228,7 +14223,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14271,7 +14266,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14285,10 +14280,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46258</v>
+        <v>44879</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14301,7 +14296,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14344,7 +14339,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14358,10 +14353,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46259</v>
+        <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14374,7 +14369,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14417,7 +14412,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14431,10 +14426,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44746</v>
+        <v>45146</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14447,7 +14442,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14490,7 +14485,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14504,10 +14499,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45569</v>
+        <v>45393</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14519,8 +14514,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14563,7 +14563,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14577,10 +14577,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45436</v>
+        <v>45170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14636,7 +14636,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14650,10 +14650,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46275</v>
+        <v>45728</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14709,7 +14709,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45720</v>
+        <v>45575</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14796,10 +14796,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45721</v>
+        <v>44746</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45713</v>
+        <v>45569</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14928,7 +14928,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14942,10 +14942,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45728</v>
+        <v>46282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15001,7 +15001,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15011,14 +15011,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45533</v>
+        <v>46245</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15074,7 +15074,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15088,10 +15088,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45735</v>
+        <v>45436</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15147,7 +15147,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15161,10 +15161,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45737</v>
+        <v>45720</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15220,7 +15220,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45555</v>
+        <v>45721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.5</v>
+        <v>11.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15293,7 +15293,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45695</v>
+        <v>45713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15366,7 +15366,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45567</v>
+        <v>45728</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15439,7 +15439,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44897</v>
+        <v>45533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15512,7 +15512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15526,10 +15526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45812</v>
+        <v>45735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15585,7 +15585,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15599,10 +15599,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45821</v>
+        <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15658,7 +15658,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45820</v>
+        <v>45555</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45820</v>
+        <v>45695</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45820</v>
+        <v>45567</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15891,10 +15891,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45825</v>
+        <v>44897</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45727</v>
+        <v>45812</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45728</v>
+        <v>45821</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16110,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45869</v>
+        <v>45820</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45624</v>
+        <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45729</v>
+        <v>45820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16315,7 +16315,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16329,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45744</v>
+        <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45881</v>
+        <v>45727</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45881</v>
+        <v>45728</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45639</v>
+        <v>45869</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8924-2022</t>
+          <t>A 37767-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44614</v>
+        <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,19 +958,14 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -979,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -988,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1000,267 +995,272 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Pärluggla
+Sotlav
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 33243-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Silversmygare
+Kopparödla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 8924-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44614</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Åkergroda
 Vanlig groda
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 37767-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Pärluggla
-Sotlav
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33243-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Silversmygare
-Kopparödla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2637-2022</t>
+          <t>A 12709-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44580</v>
+        <v>45733</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1749,264 +1749,263 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2637-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44580</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 29176-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45821</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2027,7 +2026,7 @@
         <v>45082</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2115,7 +2114,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12709-2025</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2129,10 +2128,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45733</v>
+        <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2144,8 +2143,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2157,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2173,51 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44652</v>
+        <v>44795</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44621</v>
+        <v>45679</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44525</v>
+        <v>45035</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44616</v>
+        <v>44652</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3577,13 +3577,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3626,7 +3621,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3640,10 +3635,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44795</v>
+        <v>45727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3656,7 +3651,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3699,7 +3694,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3708,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45625</v>
+        <v>45629</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3724,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3767,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3781,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3797,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3840,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3854,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45335</v>
+        <v>44525</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3870,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3913,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3928,14 +3923,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44797</v>
+        <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3947,8 +3942,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45280</v>
+        <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45247</v>
+        <v>45337</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45002</v>
+        <v>44861</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45097</v>
+        <v>45509</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44580</v>
+        <v>45720</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45636</v>
+        <v>45721</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>11.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45629</v>
+        <v>44893</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44746</v>
+        <v>45737</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45260</v>
+        <v>45436</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45597</v>
+        <v>45533</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45258</v>
+        <v>45735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44738</v>
+        <v>45393</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4896,8 +4896,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45273</v>
+        <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45411</v>
+        <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5043,7 +5048,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5091,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5100,10 +5105,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44832</v>
+        <v>45555</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5164,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45597</v>
+        <v>45317</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5194,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5237,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5246,10 +5251,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44953</v>
+        <v>45695</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,7 +5267,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5310,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45253</v>
+        <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5383,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5397,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45146</v>
+        <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5413,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5456,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5470,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45624</v>
+        <v>45679</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5486,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5529,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5543,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45729</v>
+        <v>45567</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5554,7 +5559,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5602,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5616,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45744</v>
+        <v>45790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5632,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>9.4</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5675,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5689,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45272</v>
+        <v>44965</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5705,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5757,10 +5762,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45257</v>
+        <v>45597</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5773,7 +5778,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45881</v>
+        <v>45253</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5851,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5894,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,10 +5908,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45881</v>
+        <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5924,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5967,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5981,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45281</v>
+        <v>44819</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5992,7 +5997,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6035,7 +6040,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6054,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45639</v>
+        <v>45170</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6065,7 +6070,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6113,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6122,10 +6127,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44847</v>
+        <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6143,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6186,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6200,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45317</v>
+        <v>45917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6211,7 +6216,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6254,7 +6259,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6273,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45365</v>
+        <v>45917</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6289,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6332,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6346,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45790</v>
+        <v>45111</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6357,7 +6362,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6405,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6414,10 +6419,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45625</v>
+        <v>44879</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6430,7 +6435,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6473,7 +6478,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6487,10 +6492,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44965</v>
+        <v>44778</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6503,7 +6508,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6546,7 +6551,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6556,14 +6561,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44965</v>
+        <v>45930</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6576,7 +6581,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6624,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6638,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44861</v>
+        <v>45280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6654,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6697,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6711,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45789</v>
+        <v>45272</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6727,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6770,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45917</v>
+        <v>45931</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6794,8 +6799,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6848,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6852,10 +6862,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45917</v>
+        <v>45812</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6868,7 +6878,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6911,7 +6921,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6925,10 +6935,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44819</v>
+        <v>45146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6941,7 +6951,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6984,7 +6994,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6998,10 +7008,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45252</v>
+        <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7024,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7057,7 +7067,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7071,10 +7081,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45251</v>
+        <v>45146</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7087,7 +7097,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7130,7 +7140,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7144,10 +7154,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45253</v>
+        <v>45075</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7170,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7203,7 +7213,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7213,14 +7223,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45299</v>
+        <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7243,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7276,7 +7286,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7290,10 +7300,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45321</v>
+        <v>44614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7305,8 +7315,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7349,7 +7364,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7359,14 +7374,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45930</v>
+        <v>45398</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7394,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7422,7 +7437,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7436,10 +7451,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45931</v>
+        <v>45625</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7451,13 +7466,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7500,7 +7510,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7514,10 +7524,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45365</v>
+        <v>45625</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7530,7 +7540,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7573,7 +7583,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7587,10 +7597,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45035</v>
+        <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7603,7 +7613,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7646,7 +7656,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7660,10 +7670,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44977</v>
+        <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7676,7 +7686,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7719,7 +7729,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7733,10 +7743,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45111</v>
+        <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7749,7 +7759,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7792,7 +7802,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7806,10 +7816,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44999</v>
+        <v>45337</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7822,7 +7832,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7865,7 +7875,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7879,10 +7889,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45821</v>
+        <v>44580</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7895,7 +7905,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7938,7 +7948,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7952,10 +7962,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44978</v>
+        <v>45594</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7968,7 +7978,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8011,7 +8021,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8025,10 +8035,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45629</v>
+        <v>45436</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8041,7 +8051,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8084,7 +8094,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8098,10 +8108,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44778</v>
+        <v>45597</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8114,7 +8124,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8157,7 +8167,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8171,10 +8181,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45947</v>
+        <v>45559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8187,7 +8197,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8230,7 +8240,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8244,10 +8254,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45947</v>
+        <v>45170</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8260,7 +8270,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8303,7 +8313,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8317,10 +8327,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45946</v>
+        <v>45820</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8333,7 +8343,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8376,7 +8386,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8390,10 +8400,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45679</v>
+        <v>45820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8406,7 +8416,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8449,7 +8459,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8463,10 +8473,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45162</v>
+        <v>45569</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8479,7 +8489,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8522,7 +8532,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8532,14 +8542,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45111</v>
+        <v>45411</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8552,7 +8562,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8595,7 +8605,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8609,10 +8619,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44614</v>
+        <v>45820</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8624,13 +8634,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8673,7 +8678,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8687,10 +8692,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45702</v>
+        <v>45273</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8703,7 +8708,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8746,7 +8751,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8760,10 +8765,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45947</v>
+        <v>45702</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8776,7 +8781,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8819,7 +8824,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8833,10 +8838,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44978</v>
+        <v>44977</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8849,7 +8854,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8892,7 +8897,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8906,10 +8911,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46174</v>
+        <v>45567</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8965,7 +8970,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46174</v>
+        <v>45821</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8995,7 +9000,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9038,7 +9043,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9052,10 +9057,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45573</v>
+        <v>45763</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9068,7 +9073,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9111,7 +9116,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9125,10 +9130,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46000</v>
+        <v>45146</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9141,7 +9146,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9184,7 +9189,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9198,10 +9203,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>45253</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9214,7 +9219,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9257,7 +9262,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9271,10 +9276,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>45629</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9287,7 +9292,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9330,7 +9335,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9344,10 +9349,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>45162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9360,7 +9365,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9403,7 +9408,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9417,10 +9422,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45705</v>
+        <v>45825</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9433,7 +9438,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9476,7 +9481,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9490,10 +9495,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45337</v>
+        <v>45251</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9506,7 +9511,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9549,7 +9554,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9563,10 +9568,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46013</v>
+        <v>44746</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9579,7 +9584,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9622,7 +9627,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9636,10 +9641,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46012</v>
+        <v>45714</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9652,7 +9657,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9695,7 +9700,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9709,10 +9714,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46012</v>
+        <v>45636</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9725,7 +9730,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9768,7 +9773,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9782,10 +9787,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46012</v>
+        <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9798,7 +9803,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9841,7 +9846,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9855,10 +9860,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45705</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9871,7 +9876,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9914,7 +9919,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9928,10 +9933,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46034</v>
+        <v>44738</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9944,7 +9949,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9987,7 +9992,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10004,7 +10009,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10017,7 +10022,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10060,7 +10065,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10074,10 +10079,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45398</v>
+        <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10090,7 +10095,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10133,7 +10138,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10147,10 +10152,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46037</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10163,7 +10168,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10206,7 +10211,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10216,14 +10221,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45369</v>
+        <v>46002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10236,7 +10241,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10279,7 +10284,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10293,10 +10298,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46059</v>
+        <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10309,7 +10314,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10352,7 +10357,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10362,14 +10367,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46062</v>
+        <v>45299</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10387,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10425,7 +10430,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10439,10 +10444,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45337</v>
+        <v>46037</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10460,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10498,7 +10503,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10512,10 +10517,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45720</v>
+        <v>44861</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10533,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10571,7 +10576,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10585,10 +10590,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45075</v>
+        <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10601,7 +10606,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10644,7 +10649,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10658,10 +10663,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46070</v>
+        <v>46012</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10674,7 +10679,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10717,7 +10722,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10731,10 +10736,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46070</v>
+        <v>46012</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10747,7 +10752,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10790,7 +10795,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46072</v>
+        <v>46012</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10819,13 +10824,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45548</v>
+        <v>45531</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10941,7 +10941,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10951,14 +10951,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46084</v>
+        <v>45296</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10970,13 +10970,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11019,7 +11014,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11033,10 +11028,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46086</v>
+        <v>46282</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11049,7 +11044,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11092,7 +11087,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11106,10 +11101,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46086</v>
+        <v>44847</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11122,7 +11117,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11165,7 +11160,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11179,10 +11174,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46085</v>
+        <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11195,7 +11190,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11238,7 +11233,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11252,10 +11247,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46085</v>
+        <v>46062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11268,7 +11263,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11311,7 +11306,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11325,10 +11320,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46087</v>
+        <v>45448</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11340,13 +11335,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11389,7 +11379,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11403,10 +11393,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46090</v>
+        <v>46070</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11419,7 +11409,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11462,7 +11452,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11476,10 +11466,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45559</v>
+        <v>46070</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11492,7 +11482,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11535,7 +11525,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11549,10 +11539,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46094</v>
+        <v>46072</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11564,8 +11554,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>13.5</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11608,7 +11603,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11622,10 +11617,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44893</v>
+        <v>44953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11638,7 +11633,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11681,7 +11676,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11695,10 +11690,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46100</v>
+        <v>46085</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11711,7 +11706,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11754,7 +11749,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11768,10 +11763,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46106</v>
+        <v>44978</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11783,13 +11778,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11832,7 +11822,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11842,14 +11832,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11861,13 +11851,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11910,7 +11895,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11920,14 +11905,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46108</v>
+        <v>46084</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11941,11 +11926,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11988,7 +11973,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12002,10 +11987,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12018,7 +12003,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12061,7 +12046,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12075,10 +12060,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45679</v>
+        <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12091,7 +12076,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12134,7 +12119,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12148,10 +12133,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45509</v>
+        <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12164,7 +12149,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12207,7 +12192,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12221,10 +12206,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45763</v>
+        <v>46087</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12236,8 +12221,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12280,7 +12270,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12294,10 +12284,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44880</v>
+        <v>45155</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12310,7 +12300,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12353,7 +12343,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12367,10 +12357,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45296</v>
+        <v>46090</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12383,7 +12373,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12426,7 +12416,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12440,10 +12430,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46252</v>
+        <v>45705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12455,13 +12445,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12504,7 +12489,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12518,10 +12503,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45530</v>
+        <v>46094</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12534,7 +12519,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>13.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12577,7 +12562,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12591,10 +12576,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45531</v>
+        <v>45728</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12607,7 +12592,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12650,7 +12635,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12664,10 +12649,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45436</v>
+        <v>45727</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12680,7 +12665,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12723,7 +12708,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12737,10 +12722,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>44977</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12752,13 +12737,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12801,7 +12781,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12815,10 +12795,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45393</v>
+        <v>44977</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12830,13 +12810,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12879,7 +12854,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12893,10 +12868,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46258</v>
+        <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12884,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12952,7 +12927,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12966,10 +12941,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46259</v>
+        <v>46100</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12982,7 +12957,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13025,7 +13000,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13039,10 +13014,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45237</v>
+        <v>46106</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13054,8 +13029,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13098,7 +13078,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13112,10 +13092,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45714</v>
+        <v>46108</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13127,8 +13107,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13171,7 +13156,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13185,10 +13170,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45001</v>
+        <v>46108</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13201,7 +13186,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13244,7 +13229,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13258,10 +13243,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45594</v>
+        <v>45513</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13274,7 +13259,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13317,7 +13302,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13331,10 +13316,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45281</v>
+        <v>45237</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13347,7 +13332,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13390,7 +13375,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13404,10 +13389,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44861</v>
+        <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13420,7 +13405,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13463,7 +13448,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13477,10 +13462,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44977</v>
+        <v>45744</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13493,7 +13478,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13536,7 +13521,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13550,10 +13535,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44977</v>
+        <v>45869</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13566,7 +13551,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13609,7 +13594,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13623,10 +13608,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45170</v>
+        <v>45729</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13639,7 +13624,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13682,7 +13667,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13696,10 +13681,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46275</v>
+        <v>44999</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13712,7 +13697,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13755,7 +13740,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13769,10 +13754,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45513</v>
+        <v>45573</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13785,7 +13770,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>10.2</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13828,7 +13813,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13842,10 +13827,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45146</v>
+        <v>45281</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13858,7 +13843,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13901,7 +13886,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13915,10 +13900,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45146</v>
+        <v>45001</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13931,7 +13916,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13974,7 +13959,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13988,10 +13973,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45471</v>
+        <v>45624</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14004,7 +13989,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14047,7 +14032,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14061,10 +14046,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45621</v>
+        <v>45111</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14077,7 +14062,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14120,7 +14105,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14134,10 +14119,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45567</v>
+        <v>45365</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14150,7 +14135,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14193,7 +14178,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14207,10 +14192,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45155</v>
+        <v>45365</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14223,7 +14208,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14266,7 +14251,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14280,10 +14265,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44879</v>
+        <v>45881</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14296,7 +14281,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14339,7 +14324,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14353,10 +14338,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45448</v>
+        <v>45639</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14369,7 +14354,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14412,7 +14397,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14426,10 +14411,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45146</v>
+        <v>45881</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14442,7 +14427,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14485,7 +14470,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14499,10 +14484,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45393</v>
+        <v>45146</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14514,13 +14499,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14563,7 +14543,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14577,10 +14557,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45170</v>
+        <v>45257</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14593,7 +14573,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14636,7 +14616,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14650,10 +14630,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45728</v>
+        <v>45252</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14666,7 +14646,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14709,7 +14689,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14719,14 +14699,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45575</v>
+        <v>45369</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14739,7 +14719,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14782,7 +14762,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14796,10 +14776,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44746</v>
+        <v>45471</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14812,7 +14792,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14855,7 +14835,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14869,10 +14849,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45569</v>
+        <v>44832</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14885,7 +14865,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14928,7 +14908,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38922-2026</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14942,10 +14922,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46282</v>
+        <v>45789</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14958,7 +14938,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15001,7 +14981,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15011,14 +14991,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46245</v>
+        <v>44965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15031,7 +15011,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15074,7 +15054,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15088,10 +15068,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45436</v>
+        <v>45625</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15104,7 +15084,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15147,7 +15127,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15161,10 +15141,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45720</v>
+        <v>45258</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15177,7 +15157,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15220,7 +15200,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15234,10 +15214,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45721</v>
+        <v>45260</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15250,7 +15230,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>11.8</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15293,7 +15273,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15307,10 +15287,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45713</v>
+        <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15323,7 +15303,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15366,7 +15346,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15380,10 +15360,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45728</v>
+        <v>45097</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15396,7 +15376,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15439,7 +15419,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15453,10 +15433,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45533</v>
+        <v>45621</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15469,7 +15449,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15512,7 +15492,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15526,10 +15506,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45735</v>
+        <v>45575</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15585,7 +15565,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15599,10 +15579,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45737</v>
+        <v>45705</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15615,7 +15595,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15658,7 +15638,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15672,10 +15652,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45555</v>
+        <v>45002</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15688,7 +15668,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15711,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15725,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45695</v>
+        <v>45393</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15760,8 +15740,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15789,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15803,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45567</v>
+        <v>45821</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15819,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15862,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15891,10 +15876,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44897</v>
+        <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15892,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15935,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15949,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45812</v>
+        <v>46174</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15965,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16022,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45821</v>
+        <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16053,7 +16038,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16096,7 +16081,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16110,10 +16095,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45820</v>
+        <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16126,7 +16111,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16169,7 +16154,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16183,10 +16168,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45820</v>
+        <v>46247</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16198,8 +16183,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16242,7 +16232,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16256,10 +16246,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45820</v>
+        <v>46252</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16271,8 +16261,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16315,7 +16310,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16329,10 +16324,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45825</v>
+        <v>46258</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16344,8 +16339,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16388,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45727</v>
+        <v>46258</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45728</v>
+        <v>46259</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16534,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45869</v>
+        <v>46275</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE216"/>
+  <dimension ref="A1:AE218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 8924-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45159</v>
+        <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,14 +958,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>21.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -974,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -983,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -995,272 +1000,267 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 33243-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>46246</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>12.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Silversmygare
 Kopparödla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 33243-2026 artfynd.xlsx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 33243-2026 karta.png", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 33243-2026 georefererad karta.tif", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 33243-2026 FSC-klagomål.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 33243-2026 FSC-klagomål mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 33243-2026 tillsynsbegäran.docx", "A 33243-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 33243-2026 tillsynsbegäran mail.docx", "A 33243-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 8924-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44614</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12709-2025</t>
+          <t>A 2637-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45733</v>
+        <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1749,478 +1749,478 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29176-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 34738-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 12709-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2637-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44580</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 29176-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45821</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 25554-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45082</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44795</v>
+        <v>44652</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45679</v>
+        <v>44621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45035</v>
+        <v>44525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44652</v>
+        <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3577,8 +3577,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3621,7 +3626,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3635,10 +3640,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45727</v>
+        <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3651,7 +3656,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3694,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3708,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3724,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3767,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3781,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44621</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3797,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3840,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3854,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44525</v>
+        <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3870,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3913,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3923,14 +3928,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44616</v>
+        <v>44797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3942,13 +3947,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45713</v>
+        <v>45280</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45337</v>
+        <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44861</v>
+        <v>45002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45509</v>
+        <v>45097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45720</v>
+        <v>44580</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45728</v>
+        <v>45727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45721</v>
+        <v>45636</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.8</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44893</v>
+        <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45737</v>
+        <v>44746</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45436</v>
+        <v>45597</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45533</v>
+        <v>45260</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45735</v>
+        <v>45258</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45393</v>
+        <v>44738</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4896,13 +4896,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44897</v>
+        <v>45273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4975,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5018,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44797</v>
+        <v>45411</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5048,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5091,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5105,10 +5100,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45555</v>
+        <v>44832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5121,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5164,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5178,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45317</v>
+        <v>45597</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5194,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5237,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5251,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45695</v>
+        <v>45253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5267,7 +5262,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5310,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5324,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44880</v>
+        <v>45146</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5383,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5397,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45548</v>
+        <v>45869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5413,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5456,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45679</v>
+        <v>44953</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5486,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5529,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5543,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45567</v>
+        <v>45624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5559,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5602,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5616,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45790</v>
+        <v>45729</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5632,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5675,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5689,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44965</v>
+        <v>45744</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5705,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5748,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45597</v>
+        <v>45272</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5778,7 +5773,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5821,7 +5816,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5835,10 +5830,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45253</v>
+        <v>45257</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5851,7 +5846,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5894,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5908,10 +5903,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45335</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5924,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5967,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5981,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44819</v>
+        <v>45881</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5997,7 +5992,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6040,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45170</v>
+        <v>45881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6070,7 +6065,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6113,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6127,10 +6122,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45281</v>
+        <v>45639</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6143,7 +6138,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6186,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6200,10 +6195,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45917</v>
+        <v>44847</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6216,7 +6211,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6259,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6273,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45917</v>
+        <v>45790</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6289,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6332,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6346,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45111</v>
+        <v>45317</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6362,7 +6357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6405,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6419,10 +6414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44879</v>
+        <v>45365</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6435,7 +6430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6478,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6492,10 +6487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44778</v>
+        <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6508,7 +6503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6551,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6561,14 +6556,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45930</v>
+        <v>44965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6581,7 +6576,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6624,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6638,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45280</v>
+        <v>45625</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6654,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6697,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6711,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45272</v>
+        <v>44861</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6727,7 +6722,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6770,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6784,10 +6779,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45931</v>
+        <v>44819</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6799,13 +6794,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6848,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6862,10 +6852,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45812</v>
+        <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6878,7 +6868,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6921,7 +6911,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6935,10 +6925,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45146</v>
+        <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6951,7 +6941,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6994,7 +6984,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7008,10 +6998,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45530</v>
+        <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7024,7 +7014,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7067,7 +7057,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7081,10 +7071,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45146</v>
+        <v>45251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7097,7 +7087,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7140,7 +7130,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7154,10 +7144,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45075</v>
+        <v>45253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7170,7 +7160,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7213,7 +7203,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7223,14 +7213,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45946</v>
+        <v>45299</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7243,7 +7233,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7286,7 +7276,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7300,10 +7290,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44614</v>
+        <v>45321</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7315,13 +7305,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7364,7 +7349,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7378,10 +7363,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45398</v>
+        <v>45365</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7394,7 +7379,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7437,7 +7422,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7447,14 +7432,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45625</v>
+        <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7467,7 +7452,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7510,7 +7495,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7524,10 +7509,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45625</v>
+        <v>45035</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7540,7 +7525,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7583,7 +7568,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7597,10 +7582,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45947</v>
+        <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7612,8 +7597,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7656,7 +7646,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7670,10 +7660,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45247</v>
+        <v>44977</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7686,7 +7676,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7729,7 +7719,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7743,10 +7733,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45947</v>
+        <v>45111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7759,7 +7749,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7802,7 +7792,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7816,10 +7806,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45337</v>
+        <v>44999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7832,7 +7822,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7875,7 +7865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7889,10 +7879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44580</v>
+        <v>44978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7905,7 +7895,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7948,7 +7938,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7962,10 +7952,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45594</v>
+        <v>45629</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7978,7 +7968,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8021,7 +8011,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8035,10 +8025,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45436</v>
+        <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8051,7 +8041,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8094,7 +8084,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8108,10 +8098,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45597</v>
+        <v>45789</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8124,7 +8114,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8167,7 +8157,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8181,10 +8171,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45559</v>
+        <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8197,7 +8187,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8240,7 +8230,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8254,10 +8244,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45170</v>
+        <v>45947</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8270,7 +8260,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8313,7 +8303,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8327,10 +8317,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45820</v>
+        <v>45946</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8343,7 +8333,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8386,7 +8376,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8400,10 +8390,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45820</v>
+        <v>45679</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8416,7 +8406,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8459,7 +8449,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8473,10 +8463,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45569</v>
+        <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8489,7 +8479,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8532,7 +8522,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8542,14 +8532,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45411</v>
+        <v>45111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8562,7 +8552,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8605,7 +8595,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8619,10 +8609,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45820</v>
+        <v>44614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8634,8 +8624,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8678,7 +8673,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8692,10 +8687,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45273</v>
+        <v>45702</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8708,7 +8703,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8751,7 +8746,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8765,10 +8760,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45702</v>
+        <v>44978</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,7 +8776,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8824,7 +8819,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8838,10 +8833,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44977</v>
+        <v>45573</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8854,7 +8849,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8897,7 +8892,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8911,10 +8906,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45567</v>
+        <v>45705</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8927,7 +8922,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8970,7 +8965,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8987,7 +8982,7 @@
         <v>45821</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9000,7 +8995,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9043,7 +9038,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9057,10 +9052,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45763</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9073,7 +9068,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9116,7 +9111,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9130,10 +9125,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45146</v>
+        <v>45337</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9146,7 +9141,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9189,7 +9184,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9203,10 +9198,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45253</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9219,7 +9214,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9262,7 +9257,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9276,10 +9271,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45629</v>
+        <v>46002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9292,7 +9287,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9335,7 +9330,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9349,10 +9344,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45162</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9365,7 +9360,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9408,7 +9403,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9422,10 +9417,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45825</v>
+        <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9438,7 +9433,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9481,7 +9476,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9495,10 +9490,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45251</v>
+        <v>46012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9511,7 +9506,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9554,7 +9549,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44746</v>
+        <v>46012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9579,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9627,7 +9622,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9641,10 +9636,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45714</v>
+        <v>46012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9652,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9700,7 +9695,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9714,10 +9709,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45636</v>
+        <v>45705</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9730,7 +9725,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9773,7 +9768,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9787,10 +9782,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46000</v>
+        <v>45398</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9803,7 +9798,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9846,7 +9841,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9860,10 +9855,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9876,7 +9871,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9919,7 +9914,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9933,10 +9928,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44738</v>
+        <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9949,7 +9944,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9992,7 +9987,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10006,10 +10001,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46034</v>
+        <v>46037</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10022,7 +10017,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10065,7 +10060,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10075,14 +10070,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46034</v>
+        <v>45369</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10095,7 +10090,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10138,7 +10133,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10152,10 +10147,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45337</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10168,7 +10163,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10211,7 +10206,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10225,10 +10220,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46002</v>
+        <v>45947</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10284,7 +10279,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10298,10 +10293,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45728</v>
+        <v>45075</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10314,7 +10309,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10357,7 +10352,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10367,14 +10362,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45299</v>
+        <v>46059</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10387,7 +10382,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10430,7 +10425,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10444,10 +10439,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46037</v>
+        <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10460,7 +10455,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10503,7 +10498,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10517,10 +10512,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44861</v>
+        <v>45548</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10533,7 +10528,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10576,7 +10571,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10590,10 +10585,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46013</v>
+        <v>46070</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10606,7 +10601,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10649,7 +10644,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10663,10 +10658,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46012</v>
+        <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10674,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10722,7 +10717,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10736,10 +10731,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46012</v>
+        <v>46070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10752,7 +10747,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10795,7 +10790,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46012</v>
+        <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10824,8 +10819,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45531</v>
+        <v>46174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10941,7 +10941,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45296</v>
+        <v>45559</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38922-2026</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46282</v>
+        <v>44893</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11097,14 +11097,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44847</v>
+        <v>46084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11116,8 +11116,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11160,7 +11165,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11174,10 +11179,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11190,7 +11195,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11233,7 +11238,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11247,10 +11252,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46062</v>
+        <v>46086</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11306,7 +11311,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11320,10 +11325,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45448</v>
+        <v>46085</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11336,7 +11341,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11379,7 +11384,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11393,10 +11398,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46070</v>
+        <v>46085</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11409,7 +11414,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11452,7 +11457,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11466,10 +11471,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46070</v>
+        <v>46087</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11481,8 +11486,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11525,7 +11535,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11539,10 +11549,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46072</v>
+        <v>46090</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11554,13 +11564,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11603,7 +11608,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11617,10 +11622,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44953</v>
+        <v>46094</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11633,7 +11638,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>13.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11676,7 +11681,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11690,10 +11695,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46085</v>
+        <v>45679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11706,7 +11711,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11749,7 +11754,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11763,10 +11768,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44978</v>
+        <v>46100</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11779,7 +11784,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11822,7 +11827,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11832,14 +11837,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46245</v>
+        <v>45509</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11852,7 +11857,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11895,7 +11900,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11905,14 +11910,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46084</v>
+        <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11926,11 +11931,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11973,7 +11978,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11987,10 +11992,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46085</v>
+        <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12002,8 +12007,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12046,7 +12056,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12060,10 +12070,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12076,7 +12086,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12119,7 +12129,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12133,10 +12143,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46086</v>
+        <v>45763</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12149,7 +12159,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12192,7 +12202,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12206,10 +12216,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46087</v>
+        <v>44880</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12221,13 +12231,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12270,7 +12275,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12284,10 +12289,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45155</v>
+        <v>45296</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12300,7 +12305,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12343,7 +12348,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12357,10 +12362,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46090</v>
+        <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12373,7 +12378,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12416,7 +12421,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12430,10 +12435,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45705</v>
+        <v>45530</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12446,7 +12451,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12489,7 +12494,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12503,10 +12508,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46094</v>
+        <v>45531</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12519,7 +12524,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12562,7 +12567,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12576,10 +12581,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45728</v>
+        <v>45436</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12592,7 +12597,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12635,7 +12640,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12649,10 +12654,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45727</v>
+        <v>45393</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12664,8 +12669,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12708,7 +12718,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12722,10 +12732,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44977</v>
+        <v>45237</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12738,7 +12748,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12781,7 +12791,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12795,10 +12805,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44977</v>
+        <v>46252</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12810,8 +12820,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12854,7 +12869,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12868,10 +12883,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44746</v>
+        <v>45714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12884,7 +12899,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12927,7 +12942,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12941,10 +12956,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46100</v>
+        <v>45001</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12957,7 +12972,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13000,7 +13015,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13014,10 +13029,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46106</v>
+        <v>45594</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13029,13 +13044,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13078,7 +13088,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13092,10 +13102,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46108</v>
+        <v>45281</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13107,13 +13117,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13156,7 +13161,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13170,10 +13175,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46108</v>
+        <v>44861</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13186,7 +13191,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13229,7 +13234,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13243,10 +13248,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45513</v>
+        <v>46258</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13258,8 +13263,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13302,7 +13312,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13316,10 +13326,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45237</v>
+        <v>44977</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13332,7 +13342,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13375,7 +13385,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13389,10 +13399,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44978</v>
+        <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13405,7 +13415,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13448,7 +13458,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13462,10 +13472,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45744</v>
+        <v>45170</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13478,7 +13488,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13521,7 +13531,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13535,10 +13545,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45869</v>
+        <v>46258</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13551,7 +13561,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13594,7 +13604,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13608,10 +13618,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45729</v>
+        <v>46259</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13624,7 +13634,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13667,7 +13677,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13681,10 +13691,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44999</v>
+        <v>45513</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13697,7 +13707,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.8</v>
+        <v>10.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13740,7 +13750,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13754,10 +13764,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45573</v>
+        <v>45146</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13770,7 +13780,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13813,7 +13823,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13827,10 +13837,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45281</v>
+        <v>45146</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13843,7 +13853,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13886,7 +13896,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13900,10 +13910,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45001</v>
+        <v>45471</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13916,7 +13926,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13959,7 +13969,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13973,10 +13983,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13989,7 +13999,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14032,7 +14042,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14046,10 +14056,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45111</v>
+        <v>45567</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14062,7 +14072,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14105,7 +14115,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14119,10 +14129,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45365</v>
+        <v>45155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14135,7 +14145,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14178,7 +14188,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14192,10 +14202,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45365</v>
+        <v>44879</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14208,7 +14218,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14251,7 +14261,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14265,10 +14275,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45881</v>
+        <v>45448</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14281,7 +14291,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14324,7 +14334,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14338,10 +14348,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45639</v>
+        <v>45146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14354,7 +14364,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14397,7 +14407,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14411,10 +14421,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45881</v>
+        <v>45393</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14426,8 +14436,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14470,7 +14485,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14484,10 +14499,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45146</v>
+        <v>45170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14500,7 +14515,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14543,7 +14558,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14557,10 +14572,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45257</v>
+        <v>46275</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14573,7 +14588,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14616,7 +14631,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14630,10 +14645,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45252</v>
+        <v>45728</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14646,7 +14661,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14689,7 +14704,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14699,14 +14714,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45369</v>
+        <v>45575</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14719,7 +14734,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14762,7 +14777,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14776,10 +14791,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45471</v>
+        <v>44746</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14792,7 +14807,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14835,7 +14850,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14849,10 +14864,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44832</v>
+        <v>45569</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14865,7 +14880,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14908,7 +14923,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14922,10 +14937,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45789</v>
+        <v>45436</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14938,7 +14953,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14981,7 +14996,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14995,10 +15010,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44965</v>
+        <v>45720</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15011,7 +15026,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15054,7 +15069,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15068,10 +15083,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45625</v>
+        <v>45721</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15084,7 +15099,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.6</v>
+        <v>11.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15127,7 +15142,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15141,10 +15156,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45258</v>
+        <v>46282</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15157,7 +15172,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15200,7 +15215,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15214,10 +15229,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45260</v>
+        <v>45713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15230,7 +15245,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15273,7 +15288,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15287,10 +15302,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45321</v>
+        <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15303,7 +15318,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15346,7 +15361,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15360,10 +15375,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45097</v>
+        <v>46247</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15375,8 +15390,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15419,7 +15439,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15433,10 +15453,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45621</v>
+        <v>45533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15449,7 +15469,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15492,7 +15512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15506,10 +15526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45575</v>
+        <v>45735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15565,7 +15585,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15579,10 +15599,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45705</v>
+        <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15595,7 +15615,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15638,7 +15658,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15652,10 +15672,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45002</v>
+        <v>45555</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15668,7 +15688,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15711,7 +15731,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15725,10 +15745,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45393</v>
+        <v>45695</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15740,13 +15760,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15789,7 +15804,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15803,10 +15818,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45821</v>
+        <v>45567</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15819,7 +15834,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15862,7 +15877,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15872,14 +15887,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45947</v>
+        <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15892,7 +15907,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15935,7 +15950,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15949,10 +15964,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46174</v>
+        <v>44897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15965,7 +15980,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16008,7 +16023,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 39502-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16022,10 +16037,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46174</v>
+        <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16037,8 +16052,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16081,7 +16101,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 39519-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16095,10 +16115,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45720</v>
+        <v>46289</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16110,8 +16130,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16154,7 +16179,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16168,10 +16193,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46247</v>
+        <v>45812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16183,13 +16208,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16232,7 +16252,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16246,10 +16266,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46252</v>
+        <v>45821</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16261,13 +16281,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16310,7 +16325,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16324,10 +16339,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46258</v>
+        <v>45820</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16339,13 +16354,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16388,7 +16398,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16402,10 +16412,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46258</v>
+        <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16428,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16471,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16485,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46259</v>
+        <v>45820</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16491,7 +16501,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16534,7 +16544,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16548,10 +16558,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46275</v>
+        <v>45825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16564,7 +16574,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16607,24 +16617,24 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>S 1882-2020</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44075</v>
+        <v>45727</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16637,7 +16647,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16680,24 +16690,24 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>S 5185-2022</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44823</v>
+        <v>45728</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16710,7 +16720,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16753,7 +16763,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>S 4944-2024</t>
+          <t>S 1882-2020</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16763,14 +16773,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45625</v>
+        <v>44075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16783,7 +16793,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16823,10 +16833,10 @@
       </c>
       <c r="V215" s="2" t="inlineStr"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>S 5191-2022</t>
+          <t>S 5185-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16843,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16856,45 +16866,191 @@
         </is>
       </c>
       <c r="I216" t="n">
+        <v>2</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217" ht="15" customHeight="1">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>S 4944-2024</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>0</v>
+      </c>
+      <c r="V217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>S 5191-2022</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>44823</v>
+      </c>
+      <c r="E218" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
         <v>0.9</v>
       </c>
-      <c r="J216" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" t="n">
-        <v>0</v>
-      </c>
-      <c r="U216" t="n">
-        <v>0</v>
-      </c>
-      <c r="V216" s="2" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>0</v>
+      </c>
+      <c r="V218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8924-2022</t>
+          <t>A 37767-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44614</v>
+        <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,19 +958,14 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -979,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -988,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1000,155 +995,160 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Pärluggla
+Sotlav
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 8924-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44614</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Åkergroda
 Vanlig groda
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 37767-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Pärluggla
-Sotlav
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2637-2022</t>
+          <t>A 29176-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44580</v>
+        <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1743,164 +1743,164 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 2637-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44580</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 29176-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45821</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25554-2023</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45082</v>
+        <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,17 +1929,22 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1954,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,155 +1968,150 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44652</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45625</v>
+        <v>44861</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44893</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45335</v>
+        <v>45393</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3874,8 +3874,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3923,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3928,14 +3933,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44797</v>
+        <v>45317</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3948,7 +3953,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3996,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4001,14 +4006,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45280</v>
+        <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4026,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4069,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4083,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45247</v>
+        <v>44880</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4099,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45002</v>
+        <v>45737</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4172,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4215,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45097</v>
+        <v>46012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4288,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44580</v>
+        <v>46012</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4361,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45727</v>
+        <v>46012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4391,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4434,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45636</v>
+        <v>45533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4464,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45629</v>
+        <v>45597</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4537,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4580,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4594,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44746</v>
+        <v>45735</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4610,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4653,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45597</v>
+        <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,7 +4683,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4721,7 +4726,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45260</v>
+        <v>44897</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4756,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45258</v>
+        <v>45555</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4824,7 +4829,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44738</v>
+        <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45273</v>
+        <v>46034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5023,14 +5028,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45411</v>
+        <v>46034</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5043,7 +5048,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5091,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5100,10 +5105,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44832</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5164,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45597</v>
+        <v>44819</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5194,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5237,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5246,10 +5251,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45253</v>
+        <v>46037</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,7 +5267,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5310,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45146</v>
+        <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5383,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5397,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45869</v>
+        <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5413,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5456,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5470,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44953</v>
+        <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5486,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5529,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5543,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45624</v>
+        <v>45272</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5554,7 +5559,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5602,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5616,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45729</v>
+        <v>46059</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5632,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5675,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5689,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45744</v>
+        <v>46062</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5705,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5757,10 +5762,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45272</v>
+        <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5773,7 +5778,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45257</v>
+        <v>45917</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5851,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5894,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,10 +5908,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5924,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5967,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5981,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45881</v>
+        <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5992,7 +5997,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6035,7 +6040,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6054,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45881</v>
+        <v>46072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6064,8 +6069,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6118,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6118,14 +6128,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45639</v>
+        <v>45930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6148,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6191,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6205,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44847</v>
+        <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6210,8 +6220,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6254,7 +6269,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6283,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45790</v>
+        <v>46085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6299,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6342,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6356,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45317</v>
+        <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6357,7 +6372,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6415,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6414,10 +6429,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45365</v>
+        <v>45931</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6429,8 +6444,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6473,7 +6493,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6483,14 +6503,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44965</v>
+        <v>46084</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6502,8 +6522,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6546,7 +6571,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6560,10 +6585,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44965</v>
+        <v>46085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6576,7 +6601,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6644,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6658,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45625</v>
+        <v>46086</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6674,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6717,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6731,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44861</v>
+        <v>46086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6747,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6790,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,10 +6804,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44819</v>
+        <v>46087</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6794,8 +6819,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6868,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6852,10 +6882,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45917</v>
+        <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6868,7 +6898,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6911,7 +6941,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6925,10 +6955,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45917</v>
+        <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6941,7 +6971,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6984,7 +7014,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6998,10 +7028,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45252</v>
+        <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7044,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7057,7 +7087,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7071,10 +7101,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45251</v>
+        <v>45597</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7087,7 +7117,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7130,7 +7160,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7144,10 +7174,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45253</v>
+        <v>45559</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7190,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7203,7 +7233,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7213,14 +7243,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45299</v>
+        <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7263,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7276,7 +7306,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7290,10 +7320,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45321</v>
+        <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7306,7 +7336,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7349,7 +7379,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7363,10 +7393,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45365</v>
+        <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7409,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7422,7 +7452,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7432,14 +7462,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45930</v>
+        <v>45569</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7452,7 +7482,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7495,7 +7525,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7509,10 +7539,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45035</v>
+        <v>45947</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7525,7 +7555,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7568,7 +7598,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7582,10 +7612,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45931</v>
+        <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7597,13 +7627,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7646,7 +7671,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7660,10 +7685,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44977</v>
+        <v>46106</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7675,8 +7700,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7719,7 +7749,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7733,10 +7763,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45111</v>
+        <v>46108</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7748,8 +7778,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7792,7 +7827,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7802,14 +7837,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44999</v>
+        <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7822,7 +7857,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7865,7 +7900,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7879,10 +7914,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44978</v>
+        <v>46108</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7895,7 +7930,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7938,7 +7973,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7952,10 +7987,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45629</v>
+        <v>45812</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7968,7 +8003,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8011,7 +8046,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8025,10 +8060,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44778</v>
+        <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8041,7 +8076,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8084,7 +8119,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8098,10 +8133,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45789</v>
+        <v>44977</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8114,7 +8149,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8157,7 +8192,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8171,10 +8206,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45947</v>
+        <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8230,7 +8265,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8244,10 +8279,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45947</v>
+        <v>45146</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8260,7 +8295,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8303,7 +8338,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8317,10 +8352,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45946</v>
+        <v>45629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8333,7 +8368,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8376,7 +8411,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8390,10 +8425,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45679</v>
+        <v>45162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8406,7 +8441,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8449,7 +8484,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8463,10 +8498,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45162</v>
+        <v>45636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8479,7 +8514,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8522,7 +8557,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8536,10 +8571,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45111</v>
+        <v>45679</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8552,7 +8587,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8595,7 +8630,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8609,10 +8644,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44614</v>
+        <v>45035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8624,13 +8659,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8673,7 +8703,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8687,10 +8717,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45702</v>
+        <v>45727</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8703,7 +8733,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8746,7 +8776,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8760,10 +8790,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44978</v>
+        <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8776,7 +8806,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8819,7 +8849,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8833,10 +8863,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45573</v>
+        <v>46000</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8892,7 +8922,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8906,10 +8936,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45705</v>
+        <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8922,7 +8952,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8965,7 +8995,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8979,10 +9009,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45821</v>
+        <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8995,7 +9025,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9038,7 +9068,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9052,10 +9082,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9068,7 +9098,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9111,7 +9141,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9125,10 +9155,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45337</v>
+        <v>45820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9141,7 +9171,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9184,7 +9214,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9198,10 +9228,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9214,7 +9244,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9257,7 +9287,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9271,10 +9301,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9287,7 +9317,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9330,7 +9360,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9344,10 +9374,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>45337</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9360,7 +9390,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9403,7 +9433,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9417,10 +9447,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46013</v>
+        <v>45820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9433,7 +9463,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9476,7 +9506,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9490,10 +9520,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46012</v>
+        <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9506,7 +9536,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9549,7 +9579,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9563,10 +9593,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46012</v>
+        <v>45821</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9579,7 +9609,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9622,7 +9652,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9636,10 +9666,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46012</v>
+        <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9695,7 +9725,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9709,10 +9739,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45705</v>
+        <v>45509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9725,7 +9755,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9768,7 +9798,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9782,10 +9812,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45398</v>
+        <v>45825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9798,7 +9828,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9841,7 +9871,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9855,10 +9885,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46034</v>
+        <v>45436</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9871,7 +9901,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9914,7 +9944,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9928,10 +9958,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46034</v>
+        <v>45821</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9944,7 +9974,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9987,7 +10017,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10001,10 +10031,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46037</v>
+        <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10017,7 +10047,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10060,7 +10090,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10070,14 +10100,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45369</v>
+        <v>45679</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10090,7 +10120,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10133,7 +10163,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10147,10 +10177,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45337</v>
+        <v>44965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10163,7 +10193,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10206,7 +10236,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10220,10 +10250,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45947</v>
+        <v>45728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10236,7 +10266,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10279,7 +10309,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10293,10 +10323,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45075</v>
+        <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10309,7 +10339,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10352,7 +10382,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10366,10 +10396,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46059</v>
+        <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10412,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10425,7 +10455,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10439,10 +10469,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46062</v>
+        <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10485,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10498,7 +10528,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10512,10 +10542,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45548</v>
+        <v>45170</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10558,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10571,7 +10601,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10585,10 +10615,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46070</v>
+        <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10601,7 +10631,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10661,7 +10691,7 @@
         <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10717,7 +10747,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10731,10 +10761,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46070</v>
+        <v>45281</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10747,7 +10777,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10790,7 +10820,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10804,10 +10834,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46072</v>
+        <v>45111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10819,13 +10849,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10868,7 +10893,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10882,10 +10907,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46174</v>
+        <v>45744</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10898,7 +10923,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>9.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10941,7 +10966,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10955,10 +10980,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45559</v>
+        <v>45869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10971,7 +10996,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11014,7 +11039,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11028,10 +11053,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44893</v>
+        <v>44778</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11044,7 +11069,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11087,7 +11112,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11097,14 +11122,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46084</v>
+        <v>45729</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11116,13 +11141,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11165,7 +11185,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11179,10 +11199,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46086</v>
+        <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11195,7 +11215,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11238,7 +11258,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11252,10 +11272,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46086</v>
+        <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11268,7 +11288,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11311,7 +11331,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11325,10 +11345,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46085</v>
+        <v>45624</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11341,7 +11361,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11384,7 +11404,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11398,10 +11418,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46085</v>
+        <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11414,7 +11434,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11457,7 +11477,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11471,10 +11491,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46087</v>
+        <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11486,13 +11506,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11535,7 +11550,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11549,10 +11564,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46090</v>
+        <v>45720</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11565,7 +11580,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11608,7 +11623,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11622,10 +11637,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46094</v>
+        <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11638,7 +11653,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>13.5</v>
+        <v>3.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11681,7 +11696,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11695,10 +11710,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45679</v>
+        <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11711,7 +11726,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11754,7 +11769,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11768,10 +11783,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46100</v>
+        <v>45625</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11784,7 +11799,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11827,7 +11842,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11841,10 +11856,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45509</v>
+        <v>45337</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11857,7 +11872,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11900,7 +11915,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11914,10 +11929,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46106</v>
+        <v>44580</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11929,13 +11944,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11978,7 +11988,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11992,10 +12002,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46108</v>
+        <v>45881</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12007,13 +12017,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12056,7 +12061,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12070,10 +12075,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46108</v>
+        <v>45639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12086,7 +12091,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12129,7 +12134,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12143,10 +12148,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45763</v>
+        <v>45881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12159,7 +12164,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12202,7 +12207,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12216,10 +12221,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44880</v>
+        <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12275,7 +12280,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12289,10 +12294,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45296</v>
+        <v>46252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12304,8 +12309,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12358,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12362,10 +12372,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45720</v>
+        <v>46258</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12377,8 +12387,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12421,7 +12436,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12435,10 +12450,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45530</v>
+        <v>45702</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12451,7 +12466,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12494,7 +12509,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12508,10 +12523,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45531</v>
+        <v>46258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12524,7 +12539,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12567,7 +12582,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12581,10 +12596,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45436</v>
+        <v>46259</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12597,7 +12612,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12640,7 +12655,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12654,10 +12669,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45393</v>
+        <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12669,13 +12684,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12718,7 +12728,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12732,10 +12742,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45237</v>
+        <v>45253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12748,7 +12758,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12791,7 +12801,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12805,10 +12815,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46252</v>
+        <v>45251</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12820,13 +12830,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12869,7 +12874,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12883,10 +12888,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45714</v>
+        <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12899,7 +12904,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12942,7 +12947,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12956,10 +12961,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45001</v>
+        <v>45714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12972,7 +12977,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13015,7 +13020,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13029,10 +13034,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45594</v>
+        <v>44738</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,7 +13050,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13088,7 +13093,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13102,10 +13107,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45281</v>
+        <v>45728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13118,7 +13123,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13161,7 +13166,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13171,14 +13176,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44861</v>
+        <v>45299</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13191,7 +13196,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13234,7 +13239,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13248,10 +13253,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46258</v>
+        <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13263,13 +13268,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13326,10 +13326,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44977</v>
+        <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13385,7 +13385,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13399,10 +13399,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44977</v>
+        <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13458,7 +13458,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13472,10 +13472,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45170</v>
+        <v>45296</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13545,10 +13545,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46258</v>
+        <v>44847</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46259</v>
+        <v>45448</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13677,7 +13677,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13691,10 +13691,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45513</v>
+        <v>46282</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13750,7 +13750,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13764,10 +13764,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45146</v>
+        <v>44953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13823,7 +13823,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13837,10 +13837,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45146</v>
+        <v>44978</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13896,7 +13896,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13906,14 +13906,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45471</v>
+        <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13969,7 +13969,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13983,10 +13983,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45621</v>
+        <v>45155</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14042,7 +14042,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14056,10 +14056,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45567</v>
+        <v>45705</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14129,10 +14129,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45155</v>
+        <v>44977</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14202,10 +14202,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44879</v>
+        <v>44977</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14261,7 +14261,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 39502-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45448</v>
+        <v>46289</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14290,8 +14290,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14334,7 +14339,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 39519-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14348,10 +14353,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45146</v>
+        <v>46289</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14363,8 +14368,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14407,7 +14417,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14421,10 +14431,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45393</v>
+        <v>46247</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14438,11 +14448,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14485,7 +14495,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14499,10 +14509,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45170</v>
+        <v>44746</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14515,7 +14525,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14558,7 +14568,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14572,10 +14582,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46275</v>
+        <v>45513</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14588,7 +14598,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14631,7 +14641,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14645,10 +14655,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45728</v>
+        <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14661,7 +14671,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14704,7 +14714,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14718,10 +14728,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45575</v>
+        <v>44978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14734,7 +14744,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14777,7 +14787,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14791,10 +14801,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44746</v>
+        <v>44999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14807,7 +14817,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14850,7 +14860,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14864,10 +14874,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45569</v>
+        <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14880,7 +14890,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14923,7 +14933,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14937,10 +14947,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45436</v>
+        <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14953,7 +14963,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14996,7 +15006,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15010,10 +15020,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45720</v>
+        <v>45001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15026,7 +15036,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15069,7 +15079,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15083,10 +15093,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45721</v>
+        <v>45111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15099,7 +15109,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15142,7 +15152,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38922-2026</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15156,10 +15166,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46282</v>
+        <v>45365</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15172,7 +15182,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15215,7 +15225,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15229,10 +15239,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45713</v>
+        <v>45365</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15245,7 +15255,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15288,7 +15298,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15302,10 +15312,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45728</v>
+        <v>45146</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15318,7 +15328,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15361,7 +15371,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15375,10 +15385,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46247</v>
+        <v>45257</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15388,11 +15398,6 @@
       <c r="G196" t="inlineStr">
         <is>
           <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -15439,7 +15444,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15453,10 +15458,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45533</v>
+        <v>45252</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15469,7 +15474,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15512,7 +15517,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15522,14 +15527,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45735</v>
+        <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15542,7 +15547,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15585,7 +15590,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15599,10 +15604,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45737</v>
+        <v>45471</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15658,7 +15663,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15672,10 +15677,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45555</v>
+        <v>44832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15688,7 +15693,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15731,7 +15736,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15745,10 +15750,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45695</v>
+        <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15761,7 +15766,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15804,7 +15809,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15818,10 +15823,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45567</v>
+        <v>45258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15834,7 +15839,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15877,7 +15882,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15887,14 +15892,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46245</v>
+        <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15907,7 +15912,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15950,7 +15955,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,10 +15969,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44897</v>
+        <v>45321</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15980,7 +15985,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16023,7 +16028,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 39502-2026</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16037,10 +16042,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46289</v>
+        <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16052,13 +16057,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16101,7 +16101,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 39519-2026</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16115,10 +16115,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46289</v>
+        <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16130,13 +16130,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16179,7 +16174,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16193,10 +16188,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45812</v>
+        <v>45575</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16209,7 +16204,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16252,7 +16247,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16266,10 +16261,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45821</v>
+        <v>45705</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16282,7 +16277,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16325,7 +16320,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16339,10 +16334,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45820</v>
+        <v>45002</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16355,7 +16350,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16398,7 +16393,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16412,10 +16407,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45820</v>
+        <v>45393</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16427,8 +16422,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16471,7 +16471,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16485,10 +16485,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45820</v>
+        <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16544,7 +16544,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16558,10 +16558,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45825</v>
+        <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16617,7 +16617,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16631,10 +16631,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16690,7 +16690,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16704,10 +16704,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45728</v>
+        <v>45721</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>11.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16780,7 +16780,7 @@
         <v>44075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45625</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>44614</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44580</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45082</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44652</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44861</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44893</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45393</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45317</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44880</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45737</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>46012</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45597</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45735</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44897</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>45555</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>46034</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44819</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46037</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45272</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46059</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46062</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45917</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>46085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45931</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>46084</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46086</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>46087</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45597</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45559</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45569</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45947</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>46106</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46108</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46108</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45812</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44977</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45146</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45679</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45727</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>46000</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45337</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>45820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45821</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45436</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45821</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45679</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>44965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45170</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45281</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45744</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44778</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45729</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45624</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45720</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45625</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45337</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44580</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45881</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>46258</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45702</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>46258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46259</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45251</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44738</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45299</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45296</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44847</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45448</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>46282</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44978</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45155</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45705</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44977</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44977</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46289</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>46289</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>46247</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44746</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45513</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45365</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45365</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45146</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45257</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45252</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45471</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45321</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45575</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45705</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45002</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45393</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45721</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45625</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>44614</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44580</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45082</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45733</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44735</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>44883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44746</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44652</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>44795</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44861</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44893</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45393</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45317</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44880</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45737</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>46012</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45597</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45735</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44897</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>45555</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>46034</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44819</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46037</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45272</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46059</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46062</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45917</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>46070</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>46085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45931</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>46084</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46086</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>46087</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45597</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45559</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45569</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45947</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>46106</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46108</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46108</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45812</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44977</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45146</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45679</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45727</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>46000</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45337</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>45820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45821</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45436</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45821</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45679</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>44965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45170</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45281</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45744</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44778</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45729</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45624</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45720</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45625</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45337</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44580</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45881</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>46258</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45702</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>46258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46259</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45251</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44738</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45299</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45296</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44847</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45448</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>46282</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44978</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45155</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45705</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44977</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44977</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46289</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>46289</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>46247</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44746</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45513</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45111</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45365</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45365</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45146</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45257</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45252</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45471</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45321</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45575</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45705</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45002</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45393</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45721</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45625</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE218"/>
+  <dimension ref="A1:AE216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 8924-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45159</v>
+        <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,14 +958,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>21.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -974,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -983,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -995,160 +1000,155 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 8924-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44614</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 29176-2025</t>
+          <t>A 2637-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45821</v>
+        <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1743,270 +1743,269 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 12709-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 29176-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 2637-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44580</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2027,7 +2026,7 @@
         <v>45082</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2115,7 +2114,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12709-2025</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2129,10 +2128,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45733</v>
+        <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2144,8 +2143,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2157,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2173,51 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52568-2021</t>
+          <t>A 26333-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44466</v>
+        <v>44735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52572-2021</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44466</v>
+        <v>44883</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2954,7 +2954,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26333-2022</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44735</v>
+        <v>44614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2983,8 +2983,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3027,7 +3032,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3037,14 +3042,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44883</v>
+        <v>44746</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3057,7 +3062,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3100,7 +3105,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3114,10 +3119,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44614</v>
+        <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,7 +3140,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3178,7 +3183,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44746</v>
+        <v>44652</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,7 +3213,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3251,7 +3256,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3265,10 +3270,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44538</v>
+        <v>44621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3280,13 +3285,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44652</v>
+        <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44621</v>
+        <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3431,8 +3431,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3475,7 +3480,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44525</v>
+        <v>44795</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3505,7 +3510,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3548,7 +3553,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3562,10 +3567,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44616</v>
+        <v>45625</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3577,13 +3582,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44795</v>
+        <v>45625</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44861</v>
+        <v>45335</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44893</v>
+        <v>44797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45393</v>
+        <v>45280</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3874,13 +3874,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3923,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3937,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45317</v>
+        <v>45002</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3953,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3996,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4006,14 +4001,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44797</v>
+        <v>45097</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4026,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4069,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4083,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44880</v>
+        <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4099,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4142,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45737</v>
+        <v>46002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4172,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4215,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46012</v>
+        <v>46002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4288,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46012</v>
+        <v>46002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4318,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4361,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46012</v>
+        <v>44580</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4391,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4434,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45533</v>
+        <v>45720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4464,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45597</v>
+        <v>45721</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4537,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>11.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4594,10 +4589,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45735</v>
+        <v>45713</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4667,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45253</v>
+        <v>45728</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4726,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44897</v>
+        <v>45727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4756,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4799,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45555</v>
+        <v>45533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4829,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45695</v>
+        <v>45735</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4902,7 +4897,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46034</v>
+        <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4975,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5018,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46034</v>
+        <v>45555</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5048,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5091,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5105,10 +5100,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>45695</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5121,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5164,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5178,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44819</v>
+        <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5194,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5237,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5251,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46037</v>
+        <v>44897</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5267,7 +5262,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5327,7 +5322,7 @@
         <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5383,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5397,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44879</v>
+        <v>46013</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5413,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5456,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45280</v>
+        <v>45636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5486,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5529,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5543,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45272</v>
+        <v>46012</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5559,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5602,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5616,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46059</v>
+        <v>46012</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5632,7 +5627,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5675,7 +5670,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5689,10 +5684,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46062</v>
+        <v>46012</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5705,7 +5700,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5748,7 +5743,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45917</v>
+        <v>45629</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5778,7 +5773,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5821,7 +5816,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5835,10 +5830,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45917</v>
+        <v>44746</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5851,7 +5846,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5894,7 +5889,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5908,10 +5903,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46070</v>
+        <v>45812</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5924,7 +5919,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5967,7 +5962,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5981,10 +5976,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46070</v>
+        <v>45597</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5997,7 +5992,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6040,7 +6035,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46072</v>
+        <v>45917</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6069,13 +6064,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6118,7 +6108,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6128,14 +6118,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45930</v>
+        <v>45917</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6148,7 +6138,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6191,7 +6181,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6205,10 +6195,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44614</v>
+        <v>45821</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6220,13 +6210,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6269,7 +6254,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6283,10 +6268,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46085</v>
+        <v>45260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6299,7 +6284,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6342,7 +6327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6356,10 +6341,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45247</v>
+        <v>45820</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6372,7 +6357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6415,7 +6400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6429,10 +6414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45931</v>
+        <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6444,13 +6429,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6493,7 +6473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6503,14 +6483,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46084</v>
+        <v>45820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6522,13 +6502,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6571,7 +6546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6585,10 +6560,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46085</v>
+        <v>45258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6601,7 +6576,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6644,7 +6619,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6658,10 +6633,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46086</v>
+        <v>44738</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6674,7 +6649,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6717,7 +6692,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6731,10 +6706,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46086</v>
+        <v>45825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6747,7 +6722,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6790,7 +6765,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6804,10 +6779,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46087</v>
+        <v>45273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6819,13 +6794,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6868,7 +6838,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6878,14 +6848,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45594</v>
+        <v>45930</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6898,7 +6868,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6941,7 +6911,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6955,10 +6925,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45436</v>
+        <v>45931</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6970,8 +6940,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7014,7 +6989,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7024,14 +6999,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46090</v>
+        <v>45411</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7044,7 +7019,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7087,7 +7062,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7101,10 +7076,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45597</v>
+        <v>45947</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7117,7 +7092,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7160,7 +7135,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7174,10 +7149,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45559</v>
+        <v>45947</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7190,7 +7165,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7233,7 +7208,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7247,10 +7222,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46094</v>
+        <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7263,7 +7238,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.5</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7306,7 +7281,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7320,10 +7295,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45946</v>
+        <v>44832</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7336,7 +7311,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7379,7 +7354,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7393,10 +7368,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46100</v>
+        <v>45727</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7409,7 +7384,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7452,7 +7427,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7466,10 +7441,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45569</v>
+        <v>45728</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7482,7 +7457,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7525,7 +7500,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7539,10 +7514,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45947</v>
+        <v>45597</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7555,7 +7530,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7598,7 +7573,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7612,10 +7587,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45947</v>
+        <v>44953</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7628,7 +7603,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7671,7 +7646,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7685,10 +7660,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46106</v>
+        <v>45869</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7700,13 +7675,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7749,7 +7719,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7763,10 +7733,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46108</v>
+        <v>45624</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7778,13 +7748,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7827,7 +7792,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7837,14 +7802,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45411</v>
+        <v>45729</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7857,7 +7822,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7900,7 +7865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7914,10 +7879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46108</v>
+        <v>45744</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7930,7 +7895,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7973,7 +7938,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7987,10 +7952,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45812</v>
+        <v>45253</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8003,7 +7968,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8046,7 +8011,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8060,10 +8025,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45273</v>
+        <v>45146</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8076,7 +8041,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8119,7 +8084,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8133,10 +8098,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44977</v>
+        <v>46034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8149,7 +8114,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8192,7 +8157,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8206,10 +8171,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45567</v>
+        <v>46034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8222,7 +8187,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8265,7 +8230,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8279,10 +8244,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45146</v>
+        <v>45881</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8295,7 +8260,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8338,7 +8303,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8352,10 +8317,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45629</v>
+        <v>45881</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8368,7 +8333,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8411,7 +8376,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8425,10 +8390,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45162</v>
+        <v>45639</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8441,7 +8406,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8484,7 +8449,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8498,10 +8463,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45636</v>
+        <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8514,7 +8479,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8557,7 +8522,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8571,10 +8536,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45679</v>
+        <v>45272</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8587,7 +8552,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8630,7 +8595,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8644,10 +8609,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45035</v>
+        <v>45257</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8660,7 +8625,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8703,7 +8668,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8717,10 +8682,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45727</v>
+        <v>45281</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8733,7 +8698,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8776,7 +8741,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8790,10 +8755,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45629</v>
+        <v>44847</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8806,7 +8771,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8849,7 +8814,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8863,10 +8828,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>45317</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8879,7 +8844,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8922,7 +8887,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8936,10 +8901,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8952,7 +8917,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8995,7 +8960,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9009,10 +8974,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9025,7 +8990,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9068,7 +9033,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9082,10 +9047,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46002</v>
+        <v>44965</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9098,7 +9063,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9141,7 +9106,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9155,10 +9120,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45820</v>
+        <v>44965</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9214,7 +9179,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9228,10 +9193,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45820</v>
+        <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9244,7 +9209,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9287,7 +9252,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9301,10 +9266,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46013</v>
+        <v>46059</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9317,7 +9282,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9360,7 +9325,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9374,10 +9339,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45337</v>
+        <v>46062</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9390,7 +9355,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9433,7 +9398,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9447,10 +9412,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45820</v>
+        <v>44819</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9463,7 +9428,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9506,7 +9471,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9520,10 +9485,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45789</v>
+        <v>45252</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9536,7 +9501,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9579,7 +9544,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9593,10 +9558,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45821</v>
+        <v>46070</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9609,7 +9574,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9652,7 +9617,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9666,10 +9631,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45625</v>
+        <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9682,7 +9647,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9725,7 +9690,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9739,10 +9704,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45509</v>
+        <v>45251</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9755,7 +9720,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9798,7 +9763,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9812,10 +9777,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45825</v>
+        <v>45253</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9828,7 +9793,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9871,7 +9836,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9885,10 +9850,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45436</v>
+        <v>46072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,6 +9863,11 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -9944,7 +9914,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9954,14 +9924,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45821</v>
+        <v>45299</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9974,7 +9944,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10017,7 +9987,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10031,10 +10001,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45548</v>
+        <v>45321</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10047,7 +10017,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10090,7 +10060,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10104,10 +10074,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45679</v>
+        <v>45365</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10120,7 +10090,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10163,7 +10133,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10173,14 +10143,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44965</v>
+        <v>46084</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10190,6 +10160,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -10236,7 +10211,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10250,10 +10225,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45728</v>
+        <v>46086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10266,7 +10241,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10309,7 +10284,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10323,10 +10298,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45727</v>
+        <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10382,7 +10357,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10396,10 +10371,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45947</v>
+        <v>46085</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10412,7 +10387,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10455,7 +10430,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10469,10 +10444,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45335</v>
+        <v>46085</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10485,7 +10460,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10528,7 +10503,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10542,10 +10517,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45170</v>
+        <v>45035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10558,7 +10533,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10601,7 +10576,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10615,10 +10590,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46174</v>
+        <v>44977</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10631,7 +10606,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10674,7 +10649,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10688,10 +10663,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46174</v>
+        <v>45111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10704,7 +10679,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10747,7 +10722,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10761,10 +10736,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45281</v>
+        <v>44999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10777,7 +10752,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10820,7 +10795,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10834,10 +10809,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45111</v>
+        <v>46087</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10849,8 +10824,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10893,7 +10873,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10907,10 +10887,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45744</v>
+        <v>46090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10923,7 +10903,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10966,7 +10946,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10980,10 +10960,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45869</v>
+        <v>44978</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10996,7 +10976,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11039,7 +11019,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11053,10 +11033,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44778</v>
+        <v>45629</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11112,7 +11092,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11126,10 +11106,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45729</v>
+        <v>46094</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11142,7 +11122,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11185,7 +11165,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11199,10 +11179,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45146</v>
+        <v>44778</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11215,7 +11195,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11258,7 +11238,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11272,10 +11252,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45530</v>
+        <v>46100</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11288,7 +11268,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11331,7 +11311,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11345,10 +11325,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45624</v>
+        <v>46106</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11360,8 +11340,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11404,7 +11389,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11418,10 +11403,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45146</v>
+        <v>46108</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11433,8 +11418,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11477,7 +11467,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11491,10 +11481,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45075</v>
+        <v>45679</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11497,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11550,7 +11540,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11564,10 +11554,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45720</v>
+        <v>46108</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11570,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11623,7 +11613,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11637,10 +11627,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45398</v>
+        <v>45162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11643,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11696,7 +11686,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11710,10 +11700,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45625</v>
+        <v>45111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11716,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11769,7 +11759,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11783,10 +11773,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45625</v>
+        <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11798,8 +11788,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11842,7 +11837,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11856,10 +11851,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45337</v>
+        <v>45702</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11872,7 +11867,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11915,7 +11910,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11929,10 +11924,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44580</v>
+        <v>44978</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11945,7 +11940,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11988,7 +11983,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12002,10 +11997,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45881</v>
+        <v>45573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12018,7 +12013,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12061,7 +12056,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12075,10 +12070,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45639</v>
+        <v>45705</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12091,7 +12086,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12134,7 +12129,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12148,10 +12143,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45881</v>
+        <v>45337</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12164,7 +12159,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12207,7 +12202,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12221,10 +12216,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45170</v>
+        <v>45625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12237,7 +12232,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12280,7 +12275,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12294,10 +12289,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46252</v>
+        <v>45789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12309,13 +12304,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12358,7 +12348,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12372,10 +12362,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46258</v>
+        <v>45705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12387,13 +12377,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12436,7 +12421,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12450,10 +12435,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45702</v>
+        <v>45398</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12466,7 +12451,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12509,7 +12494,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12519,14 +12504,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46258</v>
+        <v>45369</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12539,7 +12524,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12582,7 +12567,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12596,10 +12581,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46259</v>
+        <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12612,7 +12597,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12655,7 +12640,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12669,10 +12654,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45763</v>
+        <v>45075</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12685,7 +12670,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12728,7 +12713,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12742,10 +12727,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45253</v>
+        <v>45821</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12758,7 +12743,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12801,7 +12786,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12815,10 +12800,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45251</v>
+        <v>45548</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12831,7 +12816,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12874,7 +12859,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12888,10 +12873,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44746</v>
+        <v>45559</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12904,7 +12889,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12947,7 +12932,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12961,10 +12946,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45714</v>
+        <v>44893</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12977,7 +12962,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13020,7 +13005,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13034,10 +13019,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44738</v>
+        <v>45947</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13050,7 +13035,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13093,7 +13078,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13107,10 +13092,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45728</v>
+        <v>45679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13123,7 +13108,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13166,7 +13151,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13176,14 +13161,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45299</v>
+        <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13239,7 +13224,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13253,10 +13238,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44861</v>
+        <v>45509</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13269,7 +13254,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13312,7 +13297,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13326,10 +13311,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45531</v>
+        <v>46174</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13342,7 +13327,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13385,7 +13370,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13399,10 +13384,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46275</v>
+        <v>45763</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13415,7 +13400,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13458,7 +13443,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13472,10 +13457,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45296</v>
+        <v>44880</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13488,7 +13473,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13531,7 +13516,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13545,10 +13530,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44847</v>
+        <v>45296</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13561,7 +13546,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13604,7 +13589,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13618,10 +13603,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45448</v>
+        <v>45530</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13634,7 +13619,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13677,7 +13662,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 38922-2026</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13691,10 +13676,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46282</v>
+        <v>45531</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13707,7 +13692,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13750,7 +13735,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13764,10 +13749,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44953</v>
+        <v>45436</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13780,7 +13765,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13823,7 +13808,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13837,10 +13822,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44978</v>
+        <v>45720</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13853,7 +13838,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13896,7 +13881,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13906,14 +13891,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46245</v>
+        <v>45393</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13925,8 +13910,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13969,7 +13959,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13983,10 +13973,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45155</v>
+        <v>45237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13999,7 +13989,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14042,7 +14032,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14056,10 +14046,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45705</v>
+        <v>45714</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14072,7 +14062,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14115,7 +14105,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14129,10 +14119,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44977</v>
+        <v>45001</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14145,7 +14135,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14188,7 +14178,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14202,10 +14192,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44977</v>
+        <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14217,8 +14207,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14261,7 +14256,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39502-2026</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14275,10 +14270,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46289</v>
+        <v>45594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14290,13 +14285,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14339,7 +14329,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39519-2026</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14353,10 +14343,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46289</v>
+        <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14368,13 +14358,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14417,7 +14402,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14431,10 +14416,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46247</v>
+        <v>44861</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14446,13 +14431,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14495,7 +14475,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14509,10 +14489,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44746</v>
+        <v>44977</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14525,7 +14505,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14568,7 +14548,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14582,10 +14562,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45513</v>
+        <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14598,7 +14578,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14641,7 +14621,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14655,10 +14635,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45237</v>
+        <v>45170</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14671,7 +14651,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14714,7 +14694,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14728,10 +14708,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44978</v>
+        <v>46258</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14743,8 +14723,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14787,7 +14772,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14801,10 +14786,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44999</v>
+        <v>45513</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14817,7 +14802,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>10.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14860,7 +14845,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14874,10 +14859,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45573</v>
+        <v>45146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14890,7 +14875,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14933,7 +14918,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14947,10 +14932,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45281</v>
+        <v>45146</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14963,7 +14948,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15006,7 +14991,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15020,10 +15005,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45001</v>
+        <v>45471</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15036,7 +15021,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15079,7 +15064,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15093,10 +15078,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45111</v>
+        <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15109,7 +15094,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15152,7 +15137,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15166,10 +15151,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45365</v>
+        <v>46259</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15182,7 +15167,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15225,7 +15210,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15239,10 +15224,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45365</v>
+        <v>45621</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15255,7 +15240,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15298,7 +15283,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15312,10 +15297,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45146</v>
+        <v>45567</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15328,7 +15313,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15371,7 +15356,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15385,10 +15370,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45257</v>
+        <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15401,7 +15386,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15444,7 +15429,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15458,10 +15443,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45252</v>
+        <v>44879</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15474,7 +15459,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15517,7 +15502,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15527,14 +15512,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45369</v>
+        <v>45448</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15547,7 +15532,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15590,7 +15575,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15604,10 +15589,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45471</v>
+        <v>45146</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15620,7 +15605,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15663,7 +15648,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15677,10 +15662,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44832</v>
+        <v>45393</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15692,8 +15677,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15736,7 +15726,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15750,10 +15740,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44965</v>
+        <v>45170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15766,7 +15756,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15809,7 +15799,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15823,10 +15813,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45258</v>
+        <v>45728</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15839,7 +15829,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15882,7 +15872,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15896,10 +15886,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45260</v>
+        <v>45575</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15912,7 +15902,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15955,7 +15945,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15969,10 +15959,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45321</v>
+        <v>44746</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15985,7 +15975,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16028,7 +16018,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16042,10 +16032,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45097</v>
+        <v>46275</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16058,7 +16048,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16101,7 +16091,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16115,10 +16105,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45621</v>
+        <v>45569</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16131,7 +16121,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16174,7 +16164,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16188,10 +16178,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45575</v>
+        <v>45436</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16204,7 +16194,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16247,7 +16237,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16261,10 +16251,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45705</v>
+        <v>46282</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16277,7 +16267,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16320,7 +16310,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16330,14 +16320,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45002</v>
+        <v>46245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16350,7 +16340,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16393,7 +16383,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 39502-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16407,10 +16397,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45393</v>
+        <v>46289</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16424,11 +16414,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16471,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 39519-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16485,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45713</v>
+        <v>46289</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16500,8 +16490,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16544,7 +16539,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16558,10 +16553,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45720</v>
+        <v>46247</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16573,8 +16568,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16617,24 +16617,24 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>S 1882-2020</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45728</v>
+        <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16690,24 +16690,24 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>S 5185-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45721</v>
+        <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16763,7 +16763,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>S 1882-2020</t>
+          <t>S 4944-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16773,14 +16773,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44075</v>
+        <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
       </c>
       <c r="V215" s="2" t="inlineStr"/>
     </row>
-    <row r="216" ht="15" customHeight="1">
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>S 5185-2022</t>
+          <t>S 5191-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16853,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16905,152 +16905,6 @@
         <v>0</v>
       </c>
       <c r="V216" s="2" t="inlineStr"/>
-    </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>S 4944-2024</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E217" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J217" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" t="n">
-        <v>0</v>
-      </c>
-      <c r="O217" t="n">
-        <v>0</v>
-      </c>
-      <c r="P217" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" t="n">
-        <v>0</v>
-      </c>
-      <c r="T217" t="n">
-        <v>0</v>
-      </c>
-      <c r="U217" t="n">
-        <v>0</v>
-      </c>
-      <c r="V217" s="2" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>S 5191-2022</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>44823</v>
-      </c>
-      <c r="E218" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I218" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J218" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" t="n">
-        <v>0</v>
-      </c>
-      <c r="O218" t="n">
-        <v>0</v>
-      </c>
-      <c r="P218" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" t="n">
-        <v>0</v>
-      </c>
-      <c r="T218" t="n">
-        <v>0</v>
-      </c>
-      <c r="U218" t="n">
-        <v>0</v>
-      </c>
-      <c r="V218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8924-2022</t>
+          <t>A 37767-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44614</v>
+        <v>45159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,19 +958,14 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -979,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -988,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1000,155 +995,160 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Pärluggla
+Sotlav
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 8924-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44614</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Åkergroda
 Vanlig groda
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 37767-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Pärluggla
-Sotlav
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2637-2022</t>
+          <t>A 12709-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44580</v>
+        <v>45733</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1749,267 +1749,267 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 29176-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45821</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2637-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44580</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12709-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45733</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 29176-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45821</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25554-2023</t>
+          <t>A 34738-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45082</v>
+        <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2038,17 +2038,22 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2063,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2072,155 +2077,150 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44496</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44883</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44746</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>44652</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>44621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44795</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56517-2024</t>
+          <t>A 50456-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45625</v>
+        <v>44861</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56531-2024</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45625</v>
+        <v>44893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5823-2024</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45335</v>
+        <v>45317</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44797</v>
+        <v>45393</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3801,8 +3801,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3845,7 +3850,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3855,14 +3860,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45280</v>
+        <v>44797</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3875,7 +3880,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3918,7 +3923,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13049-2023</t>
+          <t>A 53823-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3932,10 +3937,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45002</v>
+        <v>44880</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3948,7 +3953,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3991,7 +3996,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29203-2023</t>
+          <t>A 8953-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4005,10 +4010,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45097</v>
+        <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4021,7 +4026,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4064,7 +4069,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58832-2023</t>
+          <t>A 10389-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4078,10 +4083,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45247</v>
+        <v>45720</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4094,7 +4099,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61802-2025</t>
+          <t>A 11818-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46002</v>
+        <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4167,7 +4172,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4210,7 +4215,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61807-2025</t>
+          <t>A 10638-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46002</v>
+        <v>45721</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4283,7 +4288,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61803-2025</t>
+          <t>A 63405-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46002</v>
+        <v>46012</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4356,7 +4361,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2633-2022</t>
+          <t>A 63406-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44580</v>
+        <v>46012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4386,7 +4391,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4429,7 +4434,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 63407-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45720</v>
+        <v>46012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,7 +4464,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 13719-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45721</v>
+        <v>45737</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,7 +4537,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4575,7 +4580,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 35888-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4589,10 +4594,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45713</v>
+        <v>45533</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,7 +4610,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4648,7 +4653,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 13346-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45728</v>
+        <v>45735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4721,7 +4726,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11809-2025</t>
+          <t>A 49922-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45727</v>
+        <v>45597</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4751,7 +4756,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 59204-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45533</v>
+        <v>44897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4824,7 +4829,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 40530-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45735</v>
+        <v>45555</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45737</v>
+        <v>45253</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 5951-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45555</v>
+        <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5043,7 +5048,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5086,7 +5091,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 43105-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5100,10 +5105,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45695</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5159,7 +5164,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 23019-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45567</v>
+        <v>45790</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5189,7 +5194,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5232,7 +5237,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 39887-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5246,10 +5251,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44897</v>
+        <v>44819</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,7 +5267,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5305,7 +5310,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45790</v>
+        <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5378,7 +5383,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63556-2025</t>
+          <t>A 2314-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5392,10 +5397,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5408,7 +5413,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5451,7 +5456,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59193-2024</t>
+          <t>A 2315-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5465,10 +5470,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45636</v>
+        <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5481,7 +5486,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5524,7 +5529,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 27379-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5538,10 +5543,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46012</v>
+        <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5554,7 +5559,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5597,7 +5602,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5611,10 +5616,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46012</v>
+        <v>45280</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,7 +5632,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5670,7 +5675,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5684,10 +5689,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46012</v>
+        <v>45272</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5700,7 +5705,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57287-2024</t>
+          <t>A 2470-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5757,10 +5762,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45629</v>
+        <v>46037</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5773,7 +5778,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28097-2022</t>
+          <t>A 28933-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44746</v>
+        <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5846,7 +5851,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5889,7 +5894,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 28934-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,10 +5908,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45812</v>
+        <v>45820</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5919,7 +5924,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5962,7 +5967,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 28932-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5976,10 +5981,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45597</v>
+        <v>45820</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5992,7 +5997,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6035,7 +6040,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 29177-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6049,10 +6054,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45917</v>
+        <v>45821</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6065,7 +6070,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6108,7 +6113,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 44718-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6125,7 +6130,7 @@
         <v>45917</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6138,7 +6143,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6181,7 +6186,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 44720-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6195,10 +6200,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45821</v>
+        <v>45917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6211,7 +6216,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6254,7 +6259,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61289-2023</t>
+          <t>A 29815-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6268,10 +6273,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45260</v>
+        <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6284,7 +6289,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6327,7 +6332,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 8926-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6341,10 +6346,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45820</v>
+        <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6356,8 +6361,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6400,7 +6410,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 47189-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6410,14 +6420,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45820</v>
+        <v>45930</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6430,7 +6440,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6473,7 +6483,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6487,10 +6497,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45820</v>
+        <v>45247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6503,7 +6513,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6546,7 +6556,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60091-2023</t>
+          <t>A 47516-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6560,10 +6570,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45258</v>
+        <v>45931</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6575,8 +6585,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6619,7 +6634,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26441-2022</t>
+          <t>A 49118-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,10 +6648,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44738</v>
+        <v>45594</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6649,7 +6664,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6692,7 +6707,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 20545-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6706,10 +6721,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45825</v>
+        <v>45436</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6722,7 +6737,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6765,7 +6780,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63206-2023</t>
+          <t>A 11820-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,10 +6794,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45273</v>
+        <v>45728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6795,7 +6810,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6838,7 +6853,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 11805-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6848,14 +6863,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45930</v>
+        <v>45727</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6868,7 +6883,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6911,7 +6926,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47516-2025</t>
+          <t>A 49920-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6925,10 +6940,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45931</v>
+        <v>45597</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6940,13 +6955,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6989,7 +6999,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16910-2024</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6999,14 +7009,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45411</v>
+        <v>45559</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7019,7 +7029,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7062,7 +7072,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51076-2025</t>
+          <t>A 50736-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7076,10 +7086,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45947</v>
+        <v>45946</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7092,7 +7102,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7135,7 +7145,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51065-2025</t>
+          <t>A 43564-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7149,10 +7159,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45947</v>
+        <v>45569</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7165,7 +7175,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7208,7 +7218,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50736-2025</t>
+          <t>A 15147-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7222,10 +7232,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45946</v>
+        <v>45744</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7238,7 +7248,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7281,7 +7291,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42769-2022</t>
+          <t>A 51076-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7295,10 +7305,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44832</v>
+        <v>45947</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7311,7 +7321,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7354,7 +7364,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11805-2025</t>
+          <t>A 36581-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7368,10 +7378,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45727</v>
+        <v>45869</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7384,7 +7394,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7427,7 +7437,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11820-2025</t>
+          <t>A 51065-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7441,10 +7451,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45728</v>
+        <v>45947</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7457,7 +7467,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7500,7 +7510,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49920-2024</t>
+          <t>A 12215-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7514,10 +7524,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45597</v>
+        <v>45729</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7530,7 +7540,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7573,7 +7583,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4290-2023</t>
+          <t>A 56479-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7587,10 +7597,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44953</v>
+        <v>45624</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7603,7 +7613,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7646,7 +7656,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36581-2025</t>
+          <t>A 16910-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7656,14 +7666,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45869</v>
+        <v>45411</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7676,7 +7686,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7719,7 +7729,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56479-2024</t>
+          <t>A 37920-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7733,10 +7743,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45624</v>
+        <v>45881</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7749,7 +7759,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7792,7 +7802,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12215-2025</t>
+          <t>A 59864-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7806,10 +7816,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45729</v>
+        <v>45639</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7822,7 +7832,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7865,7 +7875,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15147-2025</t>
+          <t>A 37925-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7879,10 +7889,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45744</v>
+        <v>45881</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7895,7 +7905,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7938,7 +7948,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 63206-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7952,10 +7962,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45253</v>
+        <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7968,7 +7978,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8011,7 +8021,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35429-2023</t>
+          <t>A 7396-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8025,10 +8035,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45146</v>
+        <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8041,7 +8051,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8084,7 +8094,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 7818-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8098,10 +8108,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46034</v>
+        <v>46062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8114,7 +8124,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8157,7 +8167,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 9486-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8171,10 +8181,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46034</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8187,7 +8197,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8230,7 +8240,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37920-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8244,10 +8254,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45881</v>
+        <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8260,7 +8270,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8303,7 +8313,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37925-2025</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8317,10 +8327,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45881</v>
+        <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8333,7 +8343,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8376,7 +8386,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59864-2024</t>
+          <t>A 9226-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8390,10 +8400,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45639</v>
+        <v>46070</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8406,7 +8416,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8449,7 +8459,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 9221-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8463,10 +8473,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46037</v>
+        <v>46070</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8479,7 +8489,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8522,7 +8532,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 57289-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8536,10 +8546,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45272</v>
+        <v>45629</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8595,7 +8605,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59965-2023</t>
+          <t>A 39311-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8609,10 +8619,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45257</v>
+        <v>45162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8625,7 +8635,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8668,7 +8678,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64722-2023</t>
+          <t>A 9742-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8682,10 +8692,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45281</v>
+        <v>46072</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8697,8 +8707,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8741,7 +8756,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46480-2022</t>
+          <t>A 59193-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8755,10 +8770,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44847</v>
+        <v>45636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8771,7 +8786,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8814,7 +8829,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 3336-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8828,10 +8843,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45317</v>
+        <v>45679</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8844,7 +8859,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8887,7 +8902,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10416-2024</t>
+          <t>A 17388-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8901,10 +8916,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45365</v>
+        <v>45035</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8917,7 +8932,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8960,7 +8975,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61356-2025</t>
+          <t>A 11809-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8974,10 +8989,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46000</v>
+        <v>45727</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8990,7 +9005,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9033,7 +9048,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6360-2023</t>
+          <t>A 57287-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9047,10 +9062,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44965</v>
+        <v>45629</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9063,7 +9078,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9106,7 +9121,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6374-2023</t>
+          <t>A 11949-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9120,10 +9135,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44965</v>
+        <v>46085</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9136,7 +9151,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9179,7 +9194,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 50587-2022</t>
+          <t>A 61356-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9193,10 +9208,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44861</v>
+        <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9209,7 +9224,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9252,7 +9267,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7396-2026</t>
+          <t>A 11758-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9262,14 +9277,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46059</v>
+        <v>46084</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9281,8 +9296,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9325,7 +9345,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 7818-2026</t>
+          <t>A 61803-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9339,10 +9359,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46062</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9398,7 +9418,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 11957-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9412,10 +9432,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44819</v>
+        <v>46085</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9428,7 +9448,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9471,7 +9491,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58878-2023</t>
+          <t>A 12069-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9485,10 +9505,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45252</v>
+        <v>46086</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9501,7 +9521,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9544,7 +9564,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9221-2026</t>
+          <t>A 12070-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9558,10 +9578,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9574,7 +9594,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9617,7 +9637,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9226-2026</t>
+          <t>A 61802-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9631,10 +9651,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46070</v>
+        <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9647,7 +9667,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9690,7 +9710,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59191-2023</t>
+          <t>A 61807-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9704,10 +9724,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45251</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9720,7 +9740,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9763,7 +9783,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59231-2023</t>
+          <t>A 12272-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9777,10 +9797,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45253</v>
+        <v>46087</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9792,8 +9812,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9836,7 +9861,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9742-2026</t>
+          <t>A 12514-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9850,10 +9875,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46072</v>
+        <v>46090</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9865,13 +9890,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9914,7 +9934,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 650-2024</t>
+          <t>A 13623-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9924,14 +9944,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45299</v>
+        <v>46094</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9944,7 +9964,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9987,7 +10007,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3645-2024</t>
+          <t>A 63556-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10001,10 +10021,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45321</v>
+        <v>46013</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10017,7 +10037,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10060,7 +10080,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10419-2024</t>
+          <t>A 14535-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10074,10 +10094,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45365</v>
+        <v>46100</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10090,7 +10110,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10133,7 +10153,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11758-2026</t>
+          <t>A 6232-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10143,14 +10163,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46084</v>
+        <v>45337</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10162,13 +10182,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10211,7 +10226,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 12069-2026</t>
+          <t>A 31833-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10225,10 +10240,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46086</v>
+        <v>45509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10241,7 +10256,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10284,7 +10299,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12070-2026</t>
+          <t>A 15665-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10298,10 +10313,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46086</v>
+        <v>46106</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10313,8 +10328,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10357,7 +10377,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11949-2026</t>
+          <t>A 15989-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10371,10 +10391,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46085</v>
+        <v>46108</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10386,8 +10406,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10430,7 +10455,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11957-2026</t>
+          <t>A 16093-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10444,10 +10469,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46085</v>
+        <v>46108</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10460,7 +10485,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10503,7 +10528,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17388-2023</t>
+          <t>A 20542-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10517,10 +10542,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45035</v>
+        <v>45436</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10533,7 +10558,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10576,7 +10601,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9486-2023</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10590,10 +10615,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44977</v>
+        <v>45548</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10649,7 +10674,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32564-2023</t>
+          <t>A 3334-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10663,10 +10688,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45111</v>
+        <v>45679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10704,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10722,7 +10747,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12476-2023</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10736,10 +10761,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44999</v>
+        <v>44965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10752,7 +10777,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10795,7 +10820,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12272-2026</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10809,10 +10834,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46087</v>
+        <v>45335</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10824,13 +10849,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10873,7 +10893,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 12514-2026</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10887,10 +10907,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46090</v>
+        <v>45170</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10903,7 +10923,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10946,7 +10966,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 8792-2023</t>
+          <t>A 64725-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10960,10 +10980,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44978</v>
+        <v>45281</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10976,7 +10996,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11019,7 +11039,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 57289-2024</t>
+          <t>A 32564-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11033,10 +11053,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45629</v>
+        <v>45111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11049,7 +11069,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11092,7 +11112,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13623-2026</t>
+          <t>A 22750-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11106,10 +11126,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46094</v>
+        <v>45789</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11122,7 +11142,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11165,7 +11185,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31989-2022</t>
+          <t>A 56512-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11179,10 +11199,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44778</v>
+        <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11195,7 +11215,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11238,7 +11258,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14535-2026</t>
+          <t>A 31989-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11252,10 +11272,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46100</v>
+        <v>44778</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11268,7 +11288,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11311,7 +11331,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15665-2026</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11325,10 +11345,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46106</v>
+        <v>45146</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11340,13 +11360,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11389,7 +11404,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15989-2026</t>
+          <t>A 35186-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11403,10 +11418,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46108</v>
+        <v>45530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11418,13 +11433,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11467,7 +11477,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 3334-2025</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11481,10 +11491,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45679</v>
+        <v>45146</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11497,7 +11507,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11540,7 +11550,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16093-2026</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11554,10 +11564,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46108</v>
+        <v>45075</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11570,7 +11580,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11613,7 +11623,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39311-2023</t>
+          <t>A 14821-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11627,10 +11637,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45162</v>
+        <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11643,7 +11653,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11686,7 +11696,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32624-2023</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11700,10 +11710,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45111</v>
+        <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11716,7 +11726,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11759,7 +11769,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11773,10 +11783,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44614</v>
+        <v>45625</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11788,13 +11798,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11837,7 +11842,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 7323-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11851,10 +11856,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45702</v>
+        <v>45337</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11867,7 +11872,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11910,7 +11915,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8794-2023</t>
+          <t>A 2633-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11924,10 +11929,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44978</v>
+        <v>44580</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11940,7 +11945,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11983,7 +11988,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 44396-2024</t>
+          <t>A 40508-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11997,10 +12002,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45573</v>
+        <v>45170</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12013,7 +12018,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12056,7 +12061,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7640-2025</t>
+          <t>A 29167-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12070,10 +12075,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45705</v>
+        <v>45821</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12086,7 +12091,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12129,7 +12134,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6232-2024</t>
+          <t>A 7323-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12143,10 +12148,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45337</v>
+        <v>45702</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12159,7 +12164,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12202,7 +12207,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56512-2024</t>
+          <t>A 51179-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12216,10 +12221,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45625</v>
+        <v>45947</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12275,7 +12280,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22750-2025</t>
+          <t>A 18685-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12289,10 +12294,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45789</v>
+        <v>45763</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12305,7 +12310,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12353,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7596-2025</t>
+          <t>A 59231-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12362,10 +12367,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45705</v>
+        <v>45253</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12378,7 +12383,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12421,7 +12426,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14821-2024</t>
+          <t>A 59191-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12435,10 +12440,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45398</v>
+        <v>45251</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12451,7 +12456,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12494,7 +12499,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10732-2024</t>
+          <t>A 28097-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12504,14 +12509,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45369</v>
+        <v>44746</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12524,7 +12529,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12567,7 +12572,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6233-2024</t>
+          <t>A 24849-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12581,10 +12586,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45337</v>
+        <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12597,7 +12602,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12640,7 +12645,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23166-2023</t>
+          <t>A 24857-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12654,10 +12659,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45075</v>
+        <v>46174</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12670,7 +12675,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12713,7 +12718,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29167-2025</t>
+          <t>A 9243-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12727,10 +12732,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45821</v>
+        <v>45714</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,7 +12748,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12786,7 +12791,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39144-2024</t>
+          <t>A 26441-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12800,10 +12805,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45548</v>
+        <v>44738</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12859,7 +12864,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 41256-2024</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12873,10 +12878,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45559</v>
+        <v>45728</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12889,7 +12894,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12932,7 +12937,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 650-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12942,14 +12947,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44893</v>
+        <v>45299</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12962,7 +12967,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13005,7 +13010,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 51179-2025</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13019,10 +13024,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45947</v>
+        <v>44861</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13035,7 +13040,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13078,7 +13083,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3336-2025</t>
+          <t>A 35366-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13092,10 +13097,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45679</v>
+        <v>45531</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13108,7 +13113,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.4</v>
+        <v>14</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13151,7 +13156,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24857-2026</t>
+          <t>A 10388-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13165,10 +13170,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46174</v>
+        <v>45720</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13181,7 +13186,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13224,7 +13229,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31833-2024</t>
+          <t>A 455-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13238,10 +13243,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45509</v>
+        <v>45296</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13254,7 +13259,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13297,7 +13302,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24849-2026</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13311,10 +13316,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46174</v>
+        <v>44847</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13327,7 +13332,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13370,7 +13375,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 18685-2025</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13384,10 +13389,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45763</v>
+        <v>45448</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13400,7 +13405,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13443,7 +13448,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 4290-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13457,10 +13462,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44880</v>
+        <v>44953</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13473,7 +13478,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13516,7 +13521,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 455-2024</t>
+          <t>A 8792-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13530,10 +13535,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45296</v>
+        <v>44978</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13546,7 +13551,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13589,7 +13594,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 35186-2024</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13603,10 +13608,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45530</v>
+        <v>45155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13619,7 +13624,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13662,7 +13667,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35366-2024</t>
+          <t>A 7640-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13676,10 +13681,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45531</v>
+        <v>45705</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13692,7 +13697,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13735,7 +13740,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20542-2024</t>
+          <t>A 9481-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13749,10 +13754,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45436</v>
+        <v>44977</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13765,7 +13770,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13808,7 +13813,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10388-2025</t>
+          <t>A 9483-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13822,10 +13827,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45720</v>
+        <v>44977</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13838,7 +13843,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13881,7 +13886,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14325-2024</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13895,10 +13900,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45393</v>
+        <v>44746</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13910,13 +13915,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55163-2023</t>
+          <t>A 34711-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13973,10 +13973,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45237</v>
+        <v>46258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13988,8 +13988,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14032,7 +14037,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 9243-2025</t>
+          <t>A 35111-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14046,10 +14051,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45714</v>
+        <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14062,7 +14067,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14105,7 +14110,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 12889-2023</t>
+          <t>A 35143-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14119,10 +14124,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45001</v>
+        <v>46259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14135,7 +14140,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>8.800000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14178,7 +14183,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 33951-2026</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14192,10 +14197,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46252</v>
+        <v>45513</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14207,13 +14212,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>10.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14256,7 +14256,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 49118-2024</t>
+          <t>A 55163-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14270,10 +14270,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45594</v>
+        <v>45237</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14329,7 +14329,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 64725-2023</t>
+          <t>A 8794-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14343,10 +14343,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45281</v>
+        <v>44978</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14402,7 +14402,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 12476-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44861</v>
+        <v>44999</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14475,7 +14475,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 9481-2023</t>
+          <t>A 44396-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14489,10 +14489,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44977</v>
+        <v>45573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14548,7 +14548,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 9483-2023</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14562,10 +14562,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44977</v>
+        <v>45281</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 40508-2023</t>
+          <t>A 12889-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45170</v>
+        <v>45001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34711-2026</t>
+          <t>A 32624-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46258</v>
+        <v>45111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14723,13 +14723,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14772,7 +14767,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32548-2024</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14786,10 +14781,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45513</v>
+        <v>45365</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14802,7 +14797,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14845,7 +14840,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 35426-2023</t>
+          <t>A 10419-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14859,10 +14854,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45146</v>
+        <v>45365</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14875,7 +14870,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14918,7 +14913,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 35433-2023</t>
+          <t>A 37493-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14932,10 +14927,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45146</v>
+        <v>46275</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14948,7 +14943,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14991,7 +14986,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27260-2024</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15005,10 +15000,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45471</v>
+        <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15021,7 +15016,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15064,7 +15059,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35111-2026</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15078,10 +15073,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46258</v>
+        <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15094,7 +15089,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15137,7 +15132,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35143-2026</t>
+          <t>A 58878-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15151,10 +15146,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46259</v>
+        <v>45252</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15167,7 +15162,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15210,7 +15205,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 55145-2024</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15220,14 +15215,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45621</v>
+        <v>45369</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15240,7 +15235,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15283,7 +15278,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 43097-2024</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15297,10 +15292,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45567</v>
+        <v>45471</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15313,7 +15308,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15356,7 +15351,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37197-2023</t>
+          <t>A 42769-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15370,10 +15365,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45155</v>
+        <v>44832</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15386,7 +15381,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15429,7 +15424,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 38922-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15443,10 +15438,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44879</v>
+        <v>46282</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15502,7 +15497,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 22925-2024</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15516,10 +15511,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45448</v>
+        <v>44965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15532,7 +15527,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15575,7 +15570,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 35435-2023</t>
+          <t>A 60091-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15589,10 +15584,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45146</v>
+        <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15605,7 +15600,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15648,7 +15643,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 61289-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15662,10 +15657,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45393</v>
+        <v>45260</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15677,13 +15672,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15726,7 +15716,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40505-2023</t>
+          <t>A 3645-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15740,10 +15730,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45170</v>
+        <v>45321</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15756,7 +15746,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15799,7 +15789,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11827-2025</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15813,10 +15803,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45728</v>
+        <v>45097</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15829,7 +15819,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15872,7 +15862,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 45002-2024</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15886,10 +15876,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45575</v>
+        <v>45621</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15902,7 +15892,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15945,7 +15935,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28200-2022</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15959,10 +15949,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44746</v>
+        <v>45575</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15975,7 +15965,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16018,7 +16008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37493-2026</t>
+          <t>A 7596-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16032,10 +16022,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46275</v>
+        <v>45705</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16048,7 +16038,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16091,7 +16081,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 43564-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16105,10 +16095,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45569</v>
+        <v>45002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16121,7 +16111,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16164,7 +16154,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20545-2024</t>
+          <t>A 33139-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16174,14 +16164,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45436</v>
+        <v>46245</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16194,7 +16184,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16237,7 +16227,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 38922-2026</t>
+          <t>A 14325-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16251,10 +16241,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46282</v>
+        <v>45393</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16266,8 +16256,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16310,7 +16305,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 33139-2026</t>
+          <t>A 39502-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16320,14 +16315,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46245</v>
+        <v>46289</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16339,8 +16334,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 39502-2026</t>
+          <t>A 39519-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16400,7 +16400,7 @@
         <v>46289</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16461,7 +16461,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 39519-2026</t>
+          <t>A 33479-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16475,10 +16475,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46289</v>
+        <v>46247</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16539,7 +16539,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33479-2026</t>
+          <t>A 33951-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16553,10 +16553,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16634,7 +16634,7 @@
         <v>44075</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>44823</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt GULLSPÅNG.xlsx
+++ b/Översikt GULLSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>44923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45821</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37767-2023</t>
+          <t>A 8924-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45159</v>
+        <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -958,14 +958,19 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>21.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -974,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -983,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -995,160 +1000,155 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 37767-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Sotlav
 Nattskärra</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 37767-2023 artfynd.xlsx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 37767-2023 karta.png", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 37767-2023 georefererad karta.tif", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 37767-2023 FSC-klagomål.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 37767-2023 FSC-klagomål mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 37767-2023 tillsynsbegäran.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 37767-2023 tillsynsbegäran mail.docx", "A 37767-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/fåglar/A 37767-2023 prioriterade fågelarter.docx", "A 37767-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 8924-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44614</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 8924-2022 artfynd.xlsx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 8924-2022 karta.png", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 8924-2022 georefererad karta.tif", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 8924-2022 FSC-klagomål.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 8924-2022 FSC-klagomål mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 8924-2022 tillsynsbegäran.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 8924-2022 tillsynsbegäran mail.docx", "A 8924-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45754</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>45664</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12709-2025</t>
+          <t>A 2637-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45733</v>
+        <v>44580</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1749,478 +1749,478 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 12709-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>8</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 12709-2025 artfynd.xlsx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 12709-2025 karta.png", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 12709-2025 georefererad karta.tif", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 12709-2025 karta knärot.png", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 12709-2025 FSC-klagomål.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 12709-2025 FSC-klagomål mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 12709-2025 tillsynsbegäran.docx", "A 12709-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 12709-2025 tillsynsbegäran mail.docx", "A 12709-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 25554-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45082</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 29176-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45821</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 29176-2025 artfynd.xlsx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 29176-2025 karta.png", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 29176-2025 georefererad karta.tif", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 29176-2025 FSC-klagomål.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 29176-2025 FSC-klagomål mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 29176-2025 tillsynsbegäran.docx", "A 29176-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 29176-2025 tillsynsbegäran mail.docx", "A 29176-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2637-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44580</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 34738-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GULLSPÅNG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 2637-2022 artfynd.xlsx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 2637-2022 karta.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 2637-2022 georefererad karta.tif", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/knärot/A 2637-2022 karta knärot.png", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 2637-2022 FSC-klagomål.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 2637-2022 FSC-klagomål mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 2637-2022 tillsynsbegäran.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 2637-2022 tillsynsbegäran mail.docx", "A 2637-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 34738-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 34738-2026 artfynd.xlsx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 34738-2026 karta.png", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 34738-2026 georefererad karta.tif", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 34738-2026 FSC-klagomål.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 34738-2026 FSC-klagomål mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 34738-2026 tillsynsbegäran.docx", "A 34738-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 34738-2026 tillsynsbegäran mail.docx", "A 34738-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25554-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45082</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GULLSPÅNG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/artfynd/A 25554-2023 artfynd.xlsx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor/A 25554-2023 karta.png", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/kartor_geotiff/A 25554-2023 georefererad karta.tif", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomål/A 25554-2023 FSC-klagomål.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/klagomålsmail/A 25554-2023 FSC-klagomål mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsyn/A 25554-2023 tillsynsbegäran.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1447/tillsynsmail/A 25554-2023 tillsynsbegäran mail.docx", "A 25554-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>44881</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44686</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>44519</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60681-2021</t>
+          <t>A 2640-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44496</v>
+        <v>44580</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2640-2022</t>
+          <t>A 71009-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44580</v>
+        <v>44538</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2764,8 +2764,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2808,7 +2813,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26333-2022</t>
+          <t>A 60681-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,14 +2823,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44735</v>
+        <v>44496</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2881,7 +2886,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55624-2022</t>
+          <t>A 26333-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2895,10 +2900,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44883</v>
+        <v>44735</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2911,7 +2916,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2954,7 +2959,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8910-2022</t>
+          <t>A 14406-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2968,10 +2973,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44614</v>
+        <v>44652</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2983,13 +2988,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28101-2022</t>
+          <t>A 68517-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44746</v>
+        <v>44525</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 71009-2021</t>
+          <t>A 10056-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44538</v>
+        <v>44621</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3134,13 +3134,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3183,7 +3178,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14406-2022</t>
+          <t>A 9423-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44652</v>
+        <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3212,8 +3207,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10056-2022</t>
+          <t>A 55624-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,14 +3266,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44621</v>
+        <v>44883</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 68517-2021</t>
+          <t>A 34589-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44525</v>
+        <v>44795</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9423-2022</t>
+          <t>A 8910-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44616</v>
+        <v>44614</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34589-2022</t>
+          <t>A 28101-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44795</v>
+        <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50456-2022</t>
+          <t>A 10732-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44861</v>
+        <v>45369</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56711-2022</t>
+          <t>A 59373-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44893</v>
+        <v>45253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3313-2024</t>
+          <t>A 35429-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45317</v>
+        <v>45146</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14309-2024</t>
+          <t>A 32548-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45393</v>
+        <v>45513</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3801,13 +3801,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3850,7 +3845,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35149-2022</t>
+          <t>A 35426-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3860,14 +3855,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44797</v>
+        <v>45146</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3880,7 +3875,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3923,7 +3918,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53823-2022</t>
+          <t>A 35433-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3937,10 +3932,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44880</v>
+        <v>45146</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3953,7 +3948,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3996,7 +3991,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8953-2025</t>
+          <t>A 27260-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4010,10 +4005,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45713</v>
+        <v>45471</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4026,7 +4021,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4069,7 +4064,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10389-2025</t>
+          <t>A 55145-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4083,10 +4078,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45720</v>
+        <v>45621</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4099,7 +4094,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4142,7 +4137,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11818-2025</t>
+          <t>A 56517-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45728</v>
+        <v>45625</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4172,7 +4167,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4215,7 +4210,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10638-2025</t>
+          <t>A 56531-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45721</v>
+        <v>45625</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>11.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4288,7 +4283,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63405-2025</t>
+          <t>A 5823-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46012</v>
+        <v>45335</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4318,7 +4313,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4361,7 +4356,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63406-2025</t>
+          <t>A 6233-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46012</v>
+        <v>45337</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4391,7 +4386,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4434,7 +4429,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63407-2025</t>
+          <t>A 23166-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46012</v>
+        <v>45075</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4464,7 +4459,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13719-2025</t>
+          <t>A 43097-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45737</v>
+        <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4537,7 +4532,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35888-2024</t>
+          <t>A 35149-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4590,14 +4585,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45533</v>
+        <v>44797</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13346-2025</t>
+          <t>A 64350-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4667,10 +4662,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45735</v>
+        <v>45280</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4726,7 +4721,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49922-2024</t>
+          <t>A 58832-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45597</v>
+        <v>45247</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4756,7 +4751,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4799,7 +4794,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59204-2022</t>
+          <t>A 37197-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44897</v>
+        <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4829,7 +4824,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40530-2024</t>
+          <t>A 13049-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45555</v>
+        <v>45002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4902,7 +4897,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59373-2023</t>
+          <t>A 29203-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45253</v>
+        <v>45097</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4975,7 +4970,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5018,7 +5013,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5951-2025</t>
+          <t>A 63039-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45695</v>
+        <v>45272</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5048,7 +5043,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5091,7 +5086,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43105-2024</t>
+          <t>A 53360-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5105,10 +5100,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>44879</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5121,7 +5116,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5164,7 +5159,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23019-2025</t>
+          <t>A 39144-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5178,10 +5173,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45790</v>
+        <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5194,7 +5189,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5237,7 +5232,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39887-2022</t>
+          <t>A 59965-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5251,10 +5246,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44819</v>
+        <v>45257</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5267,7 +5262,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5310,7 +5305,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53360-2022</t>
+          <t>A 64722-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5324,10 +5319,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44879</v>
+        <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5383,7 +5378,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2314-2026</t>
+          <t>A 22925-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5397,10 +5392,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46034</v>
+        <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5413,7 +5408,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5456,7 +5451,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2315-2026</t>
+          <t>A 35435-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46034</v>
+        <v>45146</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5486,7 +5481,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5529,7 +5524,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27379-2025</t>
+          <t>A 46480-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5543,10 +5538,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45812</v>
+        <v>44847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5559,7 +5554,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5602,7 +5597,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64350-2023</t>
+          <t>A 14309-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5616,10 +5611,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45280</v>
+        <v>45393</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5631,8 +5626,13 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63039-2023</t>
+          <t>A 40505-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45272</v>
+        <v>45170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2470-2026</t>
+          <t>A 11827-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46037</v>
+        <v>45728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28933-2025</t>
+          <t>A 41256-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45820</v>
+        <v>45559</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28934-2025</t>
+          <t>A 3313-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45820</v>
+        <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5967,7 +5967,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28932-2025</t>
+          <t>A 10416-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45820</v>
+        <v>45365</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6040,7 +6040,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29177-2025</t>
+          <t>A 56711-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45821</v>
+        <v>44893</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44718-2025</t>
+          <t>A 45002-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45917</v>
+        <v>45575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6186,7 +6186,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44720-2025</t>
+          <t>A 6360-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45917</v>
+        <v>44965</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29815-2025</t>
+          <t>A 6374-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45825</v>
+        <v>44965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6332,7 +6332,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8926-2022</t>
+          <t>A 50587-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44614</v>
+        <v>44861</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6361,13 +6361,8 @@
           <t>GULLSPÅNG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6410,7 +6405,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47189-2025</t>
+          <t>A 28200-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6420,14 +6415,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <